--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354017</t>
+          <t>2026-03-02T04:10:34.094704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354033</t>
+          <t>2026-03-02T04:10:34.094719</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354037</t>
+          <t>2026-03-02T04:10:34.094723</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354040</t>
+          <t>2026-03-02T04:10:34.094727</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354044</t>
+          <t>2026-03-02T04:10:34.094730</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354047</t>
+          <t>2026-03-02T04:10:34.094733</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354050</t>
+          <t>2026-03-02T04:10:34.094736</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354054</t>
+          <t>2026-03-02T04:10:34.094740</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354057</t>
+          <t>2026-03-02T04:10:34.094743</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354063</t>
+          <t>2026-03-02T04:10:34.094749</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354066</t>
+          <t>2026-03-02T04:10:34.094752</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354069</t>
+          <t>2026-03-02T04:10:34.094755</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354072</t>
+          <t>2026-03-02T04:10:34.094758</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354075</t>
+          <t>2026-03-02T04:10:34.094761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354077</t>
+          <t>2026-03-02T04:10:34.094763</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354080</t>
+          <t>2026-03-02T04:10:34.094766</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354083</t>
+          <t>2026-03-02T04:10:34.094769</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354086</t>
+          <t>2026-03-02T04:10:34.094772</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354089</t>
+          <t>2026-03-02T04:10:34.094775</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354094</t>
+          <t>2026-03-02T04:10:34.094780</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354097</t>
+          <t>2026-03-02T04:10:34.094782</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354100</t>
+          <t>2026-03-02T04:10:34.094785</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354102</t>
+          <t>2026-03-02T04:10:34.094788</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354105</t>
+          <t>2026-03-02T04:10:34.094790</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354108</t>
+          <t>2026-03-02T04:10:34.094793</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354111</t>
+          <t>2026-03-02T04:10:34.094796</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354114</t>
+          <t>2026-03-02T04:10:34.094799</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354116</t>
+          <t>2026-03-02T04:10:34.094801</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354119</t>
+          <t>2026-03-02T04:10:34.094804</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354124</t>
+          <t>2026-03-02T04:10:34.094811</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354127</t>
+          <t>2026-03-02T04:10:34.094814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354130</t>
+          <t>2026-03-02T04:10:34.094817</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354133</t>
+          <t>2026-03-02T04:10:34.094819</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354136</t>
+          <t>2026-03-02T04:10:34.094822</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354140</t>
+          <t>2026-03-02T04:10:34.094825</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354143</t>
+          <t>2026-03-02T04:10:34.094828</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354146</t>
+          <t>2026-03-02T04:10:34.094830</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354149</t>
+          <t>2026-03-02T04:10:34.094833</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,14 +3017,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354152</t>
+          <t>2026-03-02T04:10:34.094836</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1423.00</t>
+          <t>1304.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354154</t>
+          <t>2026-03-02T04:10:34.094838</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1425.00</t>
+          <t>1306.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1425</v>
+        <v>1306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354157</t>
+          <t>2026-03-02T04:10:34.094841</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1418</v>
+        <v>1300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:54.354160</t>
+          <t>2026-03-02T04:10:34.094844</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198085</t>
+          <t>2026-03-02T04:10:34.999713</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198099</t>
+          <t>2026-03-02T04:10:34.999727</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198103</t>
+          <t>2026-03-02T04:10:34.999731</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198106</t>
+          <t>2026-03-02T04:10:34.999734</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198112</t>
+          <t>2026-03-02T04:10:34.999741</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198115</t>
+          <t>2026-03-02T04:10:34.999744</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198118</t>
+          <t>2026-03-02T04:10:34.999746</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198121</t>
+          <t>2026-03-02T04:10:34.999749</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198123</t>
+          <t>2026-03-02T04:10:34.999752</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198126</t>
+          <t>2026-03-02T04:10:34.999755</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198129</t>
+          <t>2026-03-02T04:10:34.999758</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198132</t>
+          <t>2026-03-02T04:10:34.999760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198135</t>
+          <t>2026-03-02T04:10:34.999763</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198137</t>
+          <t>2026-03-02T04:10:34.999766</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198146</t>
+          <t>2026-03-02T04:10:34.999771</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198151</t>
+          <t>2026-03-02T04:10:34.999774</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198154</t>
+          <t>2026-03-02T04:10:34.999778</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198157</t>
+          <t>2026-03-02T04:10:34.999781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198159</t>
+          <t>2026-03-02T04:10:34.999784</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198162</t>
+          <t>2026-03-02T04:10:34.999788</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198165</t>
+          <t>2026-03-02T04:10:34.999791</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198168</t>
+          <t>2026-03-02T04:10:34.999793</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198171</t>
+          <t>2026-03-02T04:10:34.999796</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198173</t>
+          <t>2026-03-02T04:10:34.999799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198177</t>
+          <t>2026-03-02T04:10:34.999802</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198179</t>
+          <t>2026-03-02T04:10:34.999805</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198182</t>
+          <t>2026-03-02T04:10:34.999807</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198185</t>
+          <t>2026-03-02T04:10:34.999810</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198188</t>
+          <t>2026-03-02T04:10:34.999813</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198190</t>
+          <t>2026-03-02T04:10:34.999816</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198193</t>
+          <t>2026-03-02T04:10:34.999818</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198196</t>
+          <t>2026-03-02T04:10:34.999821</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198198</t>
+          <t>2026-03-02T04:10:34.999824</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198201</t>
+          <t>2026-03-02T04:10:34.999826</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198204</t>
+          <t>2026-03-02T04:10:34.999829</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198206</t>
+          <t>2026-03-02T04:10:34.999832</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1518.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198209</t>
+          <t>2026-03-02T04:10:34.999835</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198212</t>
+          <t>2026-03-02T04:10:34.999837</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198215</t>
+          <t>2026-03-02T04:10:34.999840</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198217</t>
+          <t>2026-03-02T04:10:34.999842</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198220</t>
+          <t>2026-03-02T04:10:34.999845</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198223</t>
+          <t>2026-03-02T04:10:34.999848</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1499.00</t>
+          <t>1518.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1499</v>
+        <v>1518</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198226</t>
+          <t>2026-03-02T04:10:34.999851</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1497.00</t>
+          <t>1543.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1497</v>
+        <v>1543</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198228</t>
+          <t>2026-03-02T04:10:34.999854</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1497.00</t>
+          <t>1543.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1497</v>
+        <v>1543</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198231</t>
+          <t>2026-03-02T04:10:34.999856</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1505.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198234</t>
+          <t>2026-03-02T04:10:34.999859</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1499.00</t>
+          <t>1545.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1499</v>
+        <v>1545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198237</t>
+          <t>2026-03-02T04:10:34.999862</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1502</v>
+        <v>1550</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198240</t>
+          <t>2026-03-02T04:10:34.999864</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>1502.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198242</t>
+          <t>2026-03-02T04:10:34.999867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1502</v>
+        <v>1492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198245</t>
+          <t>2026-03-02T04:10:34.999870</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206463</t>
+          <t>2026-03-02T04:10:35.824117</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206477</t>
+          <t>2026-03-02T04:10:35.824131</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206481</t>
+          <t>2026-03-02T04:10:35.824135</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206484</t>
+          <t>2026-03-02T04:10:35.824138</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206487</t>
+          <t>2026-03-02T04:10:35.824141</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206490</t>
+          <t>2026-03-02T04:10:35.824144</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206493</t>
+          <t>2026-03-02T04:10:35.824147</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206496</t>
+          <t>2026-03-02T04:10:35.824149</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206498</t>
+          <t>2026-03-02T04:10:35.824152</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206501</t>
+          <t>2026-03-02T04:10:35.824155</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206504</t>
+          <t>2026-03-02T04:10:35.824158</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206507</t>
+          <t>2026-03-02T04:10:35.824161</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206509</t>
+          <t>2026-03-02T04:10:35.824164</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206512</t>
+          <t>2026-03-02T04:10:35.824166</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206516</t>
+          <t>2026-03-02T04:10:35.824170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206519</t>
+          <t>2026-03-02T04:10:35.824173</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206521</t>
+          <t>2026-03-02T04:10:35.824176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206524</t>
+          <t>2026-03-02T04:10:35.824179</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206528</t>
+          <t>2026-03-02T04:10:35.824182</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206532</t>
+          <t>2026-03-02T04:10:35.824185</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206535</t>
+          <t>2026-03-02T04:10:35.824187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206539</t>
+          <t>2026-03-02T04:10:35.824204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206541</t>
+          <t>2026-03-02T04:10:35.824208</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206544</t>
+          <t>2026-03-02T04:10:35.824211</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206547</t>
+          <t>2026-03-02T04:10:35.824213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206550</t>
+          <t>2026-03-02T04:10:35.824216</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206553</t>
+          <t>2026-03-02T04:10:35.824228</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206555</t>
+          <t>2026-03-02T04:10:35.824233</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206558</t>
+          <t>2026-03-02T04:10:35.824239</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206561</t>
+          <t>2026-03-02T04:10:35.824243</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206564</t>
+          <t>2026-03-02T04:10:35.824246</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206575</t>
+          <t>2026-03-02T04:10:35.824248</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8726,11 +8726,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206578</t>
+          <t>2026-03-02T04:10:35.824251</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8791,11 +8791,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206581</t>
+          <t>2026-03-02T04:10:35.824254</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8856,11 +8856,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206583</t>
+          <t>2026-03-02T04:10:35.824257</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8921,11 +8921,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206586</t>
+          <t>2026-03-02T04:10:35.824259</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206589</t>
+          <t>2026-03-02T04:10:35.824262</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9094,14 +9094,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206592</t>
+          <t>2026-03-02T04:10:35.824265</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9159,14 +9159,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206594</t>
+          <t>2026-03-02T04:10:35.824267</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1423.00</t>
+          <t>1304.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1423</v>
+        <v>1304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9224,14 +9224,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206597</t>
+          <t>2026-03-02T04:10:35.824270</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1425.00</t>
+          <t>1306.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1425</v>
+        <v>1306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206600</t>
+          <t>2026-03-02T04:10:35.824273</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9311,11 +9311,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1300.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1418</v>
+        <v>1300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:56.206603</t>
+          <t>2026-03-02T04:10:35.824275</t>
         </is>
       </c>
     </row>
@@ -9415,14 +9415,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1350.809523809524</v>
+        <v>1351.380952380952</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1550.5</v>
+        <v>1564.7</v>
       </c>
     </row>
     <row r="4">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1350.809523809524</v>
+        <v>1351.380952380952</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094704</t>
+          <t>2026-03-03T04:11:29.852609</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094719</t>
+          <t>2026-03-03T04:11:29.852624</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094723</t>
+          <t>2026-03-03T04:11:29.852628</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094727</t>
+          <t>2026-03-03T04:11:29.852631</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094730</t>
+          <t>2026-03-03T04:11:29.852634</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094733</t>
+          <t>2026-03-03T04:11:29.852637</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094736</t>
+          <t>2026-03-03T04:11:29.852640</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094740</t>
+          <t>2026-03-03T04:11:29.852644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094743</t>
+          <t>2026-03-03T04:11:29.852646</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094749</t>
+          <t>2026-03-03T04:11:29.852651</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094752</t>
+          <t>2026-03-03T04:11:29.852654</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094755</t>
+          <t>2026-03-03T04:11:29.852657</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094758</t>
+          <t>2026-03-03T04:11:29.852660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094761</t>
+          <t>2026-03-03T04:11:29.852662</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094763</t>
+          <t>2026-03-03T04:11:29.852665</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094766</t>
+          <t>2026-03-03T04:11:29.852668</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094769</t>
+          <t>2026-03-03T04:11:29.852671</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094772</t>
+          <t>2026-03-03T04:11:29.852673</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094775</t>
+          <t>2026-03-03T04:11:29.852676</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094780</t>
+          <t>2026-03-03T04:11:29.852681</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094782</t>
+          <t>2026-03-03T04:11:29.852683</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094785</t>
+          <t>2026-03-03T04:11:29.852686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094788</t>
+          <t>2026-03-03T04:11:29.852689</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094790</t>
+          <t>2026-03-03T04:11:29.852692</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094793</t>
+          <t>2026-03-03T04:11:29.852694</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094796</t>
+          <t>2026-03-03T04:11:29.852697</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094799</t>
+          <t>2026-03-03T04:11:29.852700</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094801</t>
+          <t>2026-03-03T04:11:29.852703</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094804</t>
+          <t>2026-03-03T04:11:29.852705</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094811</t>
+          <t>2026-03-03T04:11:29.852709</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094814</t>
+          <t>2026-03-03T04:11:29.852712</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094817</t>
+          <t>2026-03-03T04:11:29.852715</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094819</t>
+          <t>2026-03-03T04:11:29.852718</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094822</t>
+          <t>2026-03-03T04:11:29.852720</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094825</t>
+          <t>2026-03-03T04:11:29.852723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094828</t>
+          <t>2026-03-03T04:11:29.852726</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094830</t>
+          <t>2026-03-03T04:11:29.852728</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094833</t>
+          <t>2026-03-03T04:11:29.852731</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3017,14 +3017,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094836</t>
+          <t>2026-03-03T04:11:29.852734</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094838</t>
+          <t>2026-03-03T04:11:29.852738</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094841</t>
+          <t>2026-03-03T04:11:29.852741</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.094844</t>
+          <t>2026-03-03T04:11:29.852744</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999713</t>
+          <t>2026-03-03T04:11:30.822997</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999727</t>
+          <t>2026-03-03T04:11:30.823010</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999731</t>
+          <t>2026-03-03T04:11:30.823014</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999734</t>
+          <t>2026-03-03T04:11:30.823017</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999741</t>
+          <t>2026-03-03T04:11:30.823021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999744</t>
+          <t>2026-03-03T04:11:30.823024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999746</t>
+          <t>2026-03-03T04:11:30.823027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999749</t>
+          <t>2026-03-03T04:11:30.823030</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999752</t>
+          <t>2026-03-03T04:11:30.823033</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999755</t>
+          <t>2026-03-03T04:11:30.823036</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999758</t>
+          <t>2026-03-03T04:11:30.823039</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999760</t>
+          <t>2026-03-03T04:11:30.823042</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999763</t>
+          <t>2026-03-03T04:11:30.823044</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999766</t>
+          <t>2026-03-03T04:11:30.823047</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999771</t>
+          <t>2026-03-03T04:11:30.823052</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999774</t>
+          <t>2026-03-03T04:11:30.823055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999778</t>
+          <t>2026-03-03T04:11:30.823058</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999781</t>
+          <t>2026-03-03T04:11:30.823061</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999784</t>
+          <t>2026-03-03T04:11:30.823064</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999788</t>
+          <t>2026-03-03T04:11:30.823067</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999791</t>
+          <t>2026-03-03T04:11:30.823069</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999793</t>
+          <t>2026-03-03T04:11:30.823073</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999796</t>
+          <t>2026-03-03T04:11:30.823078</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999799</t>
+          <t>2026-03-03T04:11:30.823083</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999802</t>
+          <t>2026-03-03T04:11:30.823088</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999805</t>
+          <t>2026-03-03T04:11:30.823093</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999807</t>
+          <t>2026-03-03T04:11:30.823097</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999810</t>
+          <t>2026-03-03T04:11:30.823102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999813</t>
+          <t>2026-03-03T04:11:30.823110</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999816</t>
+          <t>2026-03-03T04:11:30.823114</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999818</t>
+          <t>2026-03-03T04:11:30.823117</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999821</t>
+          <t>2026-03-03T04:11:30.823120</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999824</t>
+          <t>2026-03-03T04:11:30.823123</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999826</t>
+          <t>2026-03-03T04:11:30.823126</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999829</t>
+          <t>2026-03-03T04:11:30.823145</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999832</t>
+          <t>2026-03-03T04:11:30.823156</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999835</t>
+          <t>2026-03-03T04:11:30.823160</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999837</t>
+          <t>2026-03-03T04:11:30.823163</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999840</t>
+          <t>2026-03-03T04:11:30.823166</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999842</t>
+          <t>2026-03-03T04:11:30.823169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999845</t>
+          <t>2026-03-03T04:11:30.823172</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999848</t>
+          <t>2026-03-03T04:11:30.823175</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1518.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999851</t>
+          <t>2026-03-03T04:11:30.823178</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999854</t>
+          <t>2026-03-03T04:11:30.823181</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999856</t>
+          <t>2026-03-03T04:11:30.823184</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999859</t>
+          <t>2026-03-03T04:11:30.823187</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999862</t>
+          <t>2026-03-03T04:11:30.823190</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999864</t>
+          <t>2026-03-03T04:11:30.823193</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1502</v>
+        <v>1550</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999867</t>
+          <t>2026-03-03T04:11:30.823195</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1505.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999870</t>
+          <t>2026-03-03T04:11:30.823198</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824117</t>
+          <t>2026-03-03T04:11:31.643734</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824131</t>
+          <t>2026-03-03T04:11:31.643749</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824135</t>
+          <t>2026-03-03T04:11:31.643753</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824138</t>
+          <t>2026-03-03T04:11:31.643756</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824141</t>
+          <t>2026-03-03T04:11:31.643759</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824144</t>
+          <t>2026-03-03T04:11:31.643763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824147</t>
+          <t>2026-03-03T04:11:31.643766</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824149</t>
+          <t>2026-03-03T04:11:31.643769</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824152</t>
+          <t>2026-03-03T04:11:31.643772</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824155</t>
+          <t>2026-03-03T04:11:31.643776</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824158</t>
+          <t>2026-03-03T04:11:31.643779</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824161</t>
+          <t>2026-03-03T04:11:31.643782</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824164</t>
+          <t>2026-03-03T04:11:31.643785</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824166</t>
+          <t>2026-03-03T04:11:31.643789</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824170</t>
+          <t>2026-03-03T04:11:31.643792</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824173</t>
+          <t>2026-03-03T04:11:31.643796</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824176</t>
+          <t>2026-03-03T04:11:31.643799</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824179</t>
+          <t>2026-03-03T04:11:31.643802</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824182</t>
+          <t>2026-03-03T04:11:31.643806</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824185</t>
+          <t>2026-03-03T04:11:31.643809</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824187</t>
+          <t>2026-03-03T04:11:31.643812</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824204</t>
+          <t>2026-03-03T04:11:31.643816</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824208</t>
+          <t>2026-03-03T04:11:31.643819</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824211</t>
+          <t>2026-03-03T04:11:31.643822</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824213</t>
+          <t>2026-03-03T04:11:31.643825</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824216</t>
+          <t>2026-03-03T04:11:31.643829</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824228</t>
+          <t>2026-03-03T04:11:31.643832</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824233</t>
+          <t>2026-03-03T04:11:31.643836</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824239</t>
+          <t>2026-03-03T04:11:31.643839</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824243</t>
+          <t>2026-03-03T04:11:31.643843</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824246</t>
+          <t>2026-03-03T04:11:31.643854</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824248</t>
+          <t>2026-03-03T04:11:31.643857</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8726,11 +8726,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824251</t>
+          <t>2026-03-03T04:11:31.643860</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8791,11 +8791,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824254</t>
+          <t>2026-03-03T04:11:31.643863</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8856,11 +8856,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824257</t>
+          <t>2026-03-03T04:11:31.643867</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8921,11 +8921,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824259</t>
+          <t>2026-03-03T04:11:31.643870</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824262</t>
+          <t>2026-03-03T04:11:31.643873</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9094,14 +9094,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824265</t>
+          <t>2026-03-03T04:11:31.643876</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9159,14 +9159,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824267</t>
+          <t>2026-03-03T04:11:31.643879</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1304.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -9224,14 +9224,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824270</t>
+          <t>2026-03-03T04:11:31.643882</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1306.00</t>
+          <t>1312.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824273</t>
+          <t>2026-03-03T04:11:31.643885</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9311,11 +9311,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1300.00</t>
+          <t>1315.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1300</v>
+        <v>1315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:35.824275</t>
+          <t>2026-03-03T04:11:31.643889</t>
         </is>
       </c>
     </row>
@@ -9415,14 +9415,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1351.380952380952</v>
+        <v>1361.904761904762</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1564.7</v>
+        <v>1578.42</v>
       </c>
     </row>
     <row r="4">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1351.380952380952</v>
+        <v>1361.904761904762</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852609</t>
+          <t>2026-03-04T04:05:06.836062</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852624</t>
+          <t>2026-03-04T04:05:06.836075</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852628</t>
+          <t>2026-03-04T04:05:06.836079</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852631</t>
+          <t>2026-03-04T04:05:06.836083</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852634</t>
+          <t>2026-03-04T04:05:06.836086</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852637</t>
+          <t>2026-03-04T04:05:06.836089</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852640</t>
+          <t>2026-03-04T04:05:06.836092</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852644</t>
+          <t>2026-03-04T04:05:06.836096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852646</t>
+          <t>2026-03-04T04:05:06.836099</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852651</t>
+          <t>2026-03-04T04:05:06.836105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852654</t>
+          <t>2026-03-04T04:05:06.836108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852657</t>
+          <t>2026-03-04T04:05:06.836111</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852660</t>
+          <t>2026-03-04T04:05:06.836114</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852662</t>
+          <t>2026-03-04T04:05:06.836117</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852665</t>
+          <t>2026-03-04T04:05:06.836119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852668</t>
+          <t>2026-03-04T04:05:06.836122</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852671</t>
+          <t>2026-03-04T04:05:06.836125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852673</t>
+          <t>2026-03-04T04:05:06.836128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852676</t>
+          <t>2026-03-04T04:05:06.836130</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852681</t>
+          <t>2026-03-04T04:05:06.836135</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852683</t>
+          <t>2026-03-04T04:05:06.836138</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852686</t>
+          <t>2026-03-04T04:05:06.836141</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852689</t>
+          <t>2026-03-04T04:05:06.836143</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852692</t>
+          <t>2026-03-04T04:05:06.836146</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852694</t>
+          <t>2026-03-04T04:05:06.836149</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852697</t>
+          <t>2026-03-04T04:05:06.836152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852700</t>
+          <t>2026-03-04T04:05:06.836154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852703</t>
+          <t>2026-03-04T04:05:06.836157</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852705</t>
+          <t>2026-03-04T04:05:06.836160</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852709</t>
+          <t>2026-03-04T04:05:06.836165</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852712</t>
+          <t>2026-03-04T04:05:06.836168</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852715</t>
+          <t>2026-03-04T04:05:06.836170</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852718</t>
+          <t>2026-03-04T04:05:06.836173</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852720</t>
+          <t>2026-03-04T04:05:06.836176</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852723</t>
+          <t>2026-03-04T04:05:06.836179</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852726</t>
+          <t>2026-03-04T04:05:06.836181</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852728</t>
+          <t>2026-03-04T04:05:06.836184</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852731</t>
+          <t>2026-03-04T04:05:06.836187</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,14 +3017,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852734</t>
+          <t>2026-03-04T04:05:06.836190</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852738</t>
+          <t>2026-03-04T04:05:06.836192</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852741</t>
+          <t>2026-03-04T04:05:06.836195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:29.852744</t>
+          <t>2026-03-04T04:05:06.836198</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.822997</t>
+          <t>2026-03-04T04:05:07.980078</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823010</t>
+          <t>2026-03-04T04:05:07.980092</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823014</t>
+          <t>2026-03-04T04:05:07.980095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823017</t>
+          <t>2026-03-04T04:05:07.980100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823021</t>
+          <t>2026-03-04T04:05:07.980111</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823024</t>
+          <t>2026-03-04T04:05:07.980114</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823027</t>
+          <t>2026-03-04T04:05:07.980117</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823030</t>
+          <t>2026-03-04T04:05:07.980120</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823033</t>
+          <t>2026-03-04T04:05:07.980123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823036</t>
+          <t>2026-03-04T04:05:07.980126</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823039</t>
+          <t>2026-03-04T04:05:07.980129</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823042</t>
+          <t>2026-03-04T04:05:07.980131</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823044</t>
+          <t>2026-03-04T04:05:07.980134</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823047</t>
+          <t>2026-03-04T04:05:07.980137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823052</t>
+          <t>2026-03-04T04:05:07.980141</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823055</t>
+          <t>2026-03-04T04:05:07.980145</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823058</t>
+          <t>2026-03-04T04:05:07.980148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823061</t>
+          <t>2026-03-04T04:05:07.980150</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823064</t>
+          <t>2026-03-04T04:05:07.980153</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823067</t>
+          <t>2026-03-04T04:05:07.980156</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823069</t>
+          <t>2026-03-04T04:05:07.980159</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823073</t>
+          <t>2026-03-04T04:05:07.980161</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823078</t>
+          <t>2026-03-04T04:05:07.980164</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823083</t>
+          <t>2026-03-04T04:05:07.980167</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823088</t>
+          <t>2026-03-04T04:05:07.980170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823093</t>
+          <t>2026-03-04T04:05:07.980173</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823097</t>
+          <t>2026-03-04T04:05:07.980175</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823102</t>
+          <t>2026-03-04T04:05:07.980178</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823110</t>
+          <t>2026-03-04T04:05:07.980181</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823114</t>
+          <t>2026-03-04T04:05:07.980184</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823117</t>
+          <t>2026-03-04T04:05:07.980186</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823120</t>
+          <t>2026-03-04T04:05:07.980189</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823123</t>
+          <t>2026-03-04T04:05:07.980191</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823126</t>
+          <t>2026-03-04T04:05:07.980194</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823145</t>
+          <t>2026-03-04T04:05:07.980197</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823156</t>
+          <t>2026-03-04T04:05:07.980200</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823160</t>
+          <t>2026-03-04T04:05:07.980202</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823163</t>
+          <t>2026-03-04T04:05:07.980205</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823166</t>
+          <t>2026-03-04T04:05:07.980208</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823169</t>
+          <t>2026-03-04T04:05:07.980210</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823172</t>
+          <t>2026-03-04T04:05:07.980213</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823175</t>
+          <t>2026-03-04T04:05:07.980216</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823178</t>
+          <t>2026-03-04T04:05:07.980219</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823181</t>
+          <t>2026-03-04T04:05:07.980221</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823184</t>
+          <t>2026-03-04T04:05:07.980224</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823187</t>
+          <t>2026-03-04T04:05:07.980227</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823190</t>
+          <t>2026-03-04T04:05:07.980230</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823193</t>
+          <t>2026-03-04T04:05:07.980232</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823195</t>
+          <t>2026-03-04T04:05:07.980235</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823198</t>
+          <t>2026-03-04T04:05:07.980238</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643734</t>
+          <t>2026-03-04T04:05:09.006766</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643749</t>
+          <t>2026-03-04T04:05:09.006784</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643753</t>
+          <t>2026-03-04T04:05:09.006790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643756</t>
+          <t>2026-03-04T04:05:09.006796</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643759</t>
+          <t>2026-03-04T04:05:09.006803</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643763</t>
+          <t>2026-03-04T04:05:09.006809</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643766</t>
+          <t>2026-03-04T04:05:09.006813</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643769</t>
+          <t>2026-03-04T04:05:09.006816</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643772</t>
+          <t>2026-03-04T04:05:09.006819</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643776</t>
+          <t>2026-03-04T04:05:09.006822</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643779</t>
+          <t>2026-03-04T04:05:09.006825</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643782</t>
+          <t>2026-03-04T04:05:09.006827</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643785</t>
+          <t>2026-03-04T04:05:09.006830</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643789</t>
+          <t>2026-03-04T04:05:09.006833</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643792</t>
+          <t>2026-03-04T04:05:09.006837</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643796</t>
+          <t>2026-03-04T04:05:09.006840</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643799</t>
+          <t>2026-03-04T04:05:09.006843</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643802</t>
+          <t>2026-03-04T04:05:09.006845</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643806</t>
+          <t>2026-03-04T04:05:09.006849</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643809</t>
+          <t>2026-03-04T04:05:09.006853</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643812</t>
+          <t>2026-03-04T04:05:09.006856</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643816</t>
+          <t>2026-03-04T04:05:09.006859</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643819</t>
+          <t>2026-03-04T04:05:09.006862</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643822</t>
+          <t>2026-03-04T04:05:09.006865</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643825</t>
+          <t>2026-03-04T04:05:09.006867</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8271,11 +8271,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643829</t>
+          <t>2026-03-04T04:05:09.006870</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643832</t>
+          <t>2026-03-04T04:05:09.006874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643836</t>
+          <t>2026-03-04T04:05:09.006876</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643839</t>
+          <t>2026-03-04T04:05:09.006880</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643843</t>
+          <t>2026-03-04T04:05:09.006883</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643854</t>
+          <t>2026-03-04T04:05:09.006893</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643857</t>
+          <t>2026-03-04T04:05:09.006896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643860</t>
+          <t>2026-03-04T04:05:09.006899</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8791,11 +8791,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643863</t>
+          <t>2026-03-04T04:05:09.006902</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8856,11 +8856,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643867</t>
+          <t>2026-03-04T04:05:09.006905</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8921,11 +8921,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643870</t>
+          <t>2026-03-04T04:05:09.006908</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643873</t>
+          <t>2026-03-04T04:05:09.006910</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9094,14 +9094,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643876</t>
+          <t>2026-03-04T04:05:09.006913</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9159,14 +9159,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643879</t>
+          <t>2026-03-04T04:05:09.006916</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1310</v>
+        <v>1373</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9224,14 +9224,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643882</t>
+          <t>2026-03-04T04:05:09.006919</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1312.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1375</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643885</t>
+          <t>2026-03-04T04:05:09.006921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9311,11 +9311,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1315.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1315</v>
+        <v>1378</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:31.643889</t>
+          <t>2026-03-04T04:05:09.006924</t>
         </is>
       </c>
     </row>
@@ -9415,14 +9415,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1361.904761904762</v>
+        <v>1368.261904761905</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1578.42</v>
+        <v>1585.08</v>
       </c>
     </row>
     <row r="4">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1361.904761904762</v>
+        <v>1368.261904761905</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836062</t>
+          <t>2026-03-05T04:09:02.075980</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836075</t>
+          <t>2026-03-05T04:09:02.075995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836079</t>
+          <t>2026-03-05T04:09:02.075999</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836083</t>
+          <t>2026-03-05T04:09:02.076002</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836086</t>
+          <t>2026-03-05T04:09:02.076005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836089</t>
+          <t>2026-03-05T04:09:02.076009</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836092</t>
+          <t>2026-03-05T04:09:02.076012</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836096</t>
+          <t>2026-03-05T04:09:02.076015</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836099</t>
+          <t>2026-03-05T04:09:02.076018</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836105</t>
+          <t>2026-03-05T04:09:02.076024</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836108</t>
+          <t>2026-03-05T04:09:02.076027</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836111</t>
+          <t>2026-03-05T04:09:02.076030</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836114</t>
+          <t>2026-03-05T04:09:02.076033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836117</t>
+          <t>2026-03-05T04:09:02.076036</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836119</t>
+          <t>2026-03-05T04:09:02.076039</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836122</t>
+          <t>2026-03-05T04:09:02.076042</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836125</t>
+          <t>2026-03-05T04:09:02.076044</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836128</t>
+          <t>2026-03-05T04:09:02.076047</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836130</t>
+          <t>2026-03-05T04:09:02.076050</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836135</t>
+          <t>2026-03-05T04:09:02.076055</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836138</t>
+          <t>2026-03-05T04:09:02.076058</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836141</t>
+          <t>2026-03-05T04:09:02.076061</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836143</t>
+          <t>2026-03-05T04:09:02.076064</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836146</t>
+          <t>2026-03-05T04:09:02.076067</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836149</t>
+          <t>2026-03-05T04:09:02.076069</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836152</t>
+          <t>2026-03-05T04:09:02.076072</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836154</t>
+          <t>2026-03-05T04:09:02.076075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836157</t>
+          <t>2026-03-05T04:09:02.076078</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836160</t>
+          <t>2026-03-05T04:09:02.076081</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836165</t>
+          <t>2026-03-05T04:09:02.076086</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836168</t>
+          <t>2026-03-05T04:09:02.076088</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836170</t>
+          <t>2026-03-05T04:09:02.076091</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836173</t>
+          <t>2026-03-05T04:09:02.076094</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836176</t>
+          <t>2026-03-05T04:09:02.076097</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836179</t>
+          <t>2026-03-05T04:09:02.076099</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836181</t>
+          <t>2026-03-05T04:09:02.076102</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836184</t>
+          <t>2026-03-05T04:09:02.076105</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836187</t>
+          <t>2026-03-05T04:09:02.076108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3017,14 +3017,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836190</t>
+          <t>2026-03-05T04:09:02.076110</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836192</t>
+          <t>2026-03-05T04:09:02.076113</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836195</t>
+          <t>2026-03-05T04:09:02.076116</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:06.836198</t>
+          <t>2026-03-05T04:09:02.076119</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980078</t>
+          <t>2026-03-05T04:09:02.928761</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980092</t>
+          <t>2026-03-05T04:09:02.928774</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980095</t>
+          <t>2026-03-05T04:09:02.928778</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980100</t>
+          <t>2026-03-05T04:09:02.928781</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980111</t>
+          <t>2026-03-05T04:09:02.928787</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980114</t>
+          <t>2026-03-05T04:09:02.928790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980117</t>
+          <t>2026-03-05T04:09:02.928793</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980120</t>
+          <t>2026-03-05T04:09:02.928796</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980123</t>
+          <t>2026-03-05T04:09:02.928799</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980126</t>
+          <t>2026-03-05T04:09:02.928802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980129</t>
+          <t>2026-03-05T04:09:02.928804</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980131</t>
+          <t>2026-03-05T04:09:02.928807</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980134</t>
+          <t>2026-03-05T04:09:02.928810</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980137</t>
+          <t>2026-03-05T04:09:02.928813</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980141</t>
+          <t>2026-03-05T04:09:02.928818</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980145</t>
+          <t>2026-03-05T04:09:02.928821</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980148</t>
+          <t>2026-03-05T04:09:02.928824</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980150</t>
+          <t>2026-03-05T04:09:02.928827</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980153</t>
+          <t>2026-03-05T04:09:02.928830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980156</t>
+          <t>2026-03-05T04:09:02.928833</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980159</t>
+          <t>2026-03-05T04:09:02.928835</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980161</t>
+          <t>2026-03-05T04:09:02.928838</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980164</t>
+          <t>2026-03-05T04:09:02.928841</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980167</t>
+          <t>2026-03-05T04:09:02.928844</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980170</t>
+          <t>2026-03-05T04:09:02.928847</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980173</t>
+          <t>2026-03-05T04:09:02.928850</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980175</t>
+          <t>2026-03-05T04:09:02.928853</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980178</t>
+          <t>2026-03-05T04:09:02.928855</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980181</t>
+          <t>2026-03-05T04:09:02.928858</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980184</t>
+          <t>2026-03-05T04:09:02.928861</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980186</t>
+          <t>2026-03-05T04:09:02.928864</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980189</t>
+          <t>2026-03-05T04:09:02.928866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980191</t>
+          <t>2026-03-05T04:09:02.928869</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980194</t>
+          <t>2026-03-05T04:09:02.928872</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980197</t>
+          <t>2026-03-05T04:09:02.928875</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980200</t>
+          <t>2026-03-05T04:09:02.928877</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980202</t>
+          <t>2026-03-05T04:09:02.928880</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980205</t>
+          <t>2026-03-05T04:09:02.928883</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980208</t>
+          <t>2026-03-05T04:09:02.928885</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980210</t>
+          <t>2026-03-05T04:09:02.928888</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980213</t>
+          <t>2026-03-05T04:09:02.928891</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980216</t>
+          <t>2026-03-05T04:09:02.928893</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980219</t>
+          <t>2026-03-05T04:09:02.928896</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980221</t>
+          <t>2026-03-05T04:09:02.928899</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980224</t>
+          <t>2026-03-05T04:09:02.928902</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980227</t>
+          <t>2026-03-05T04:09:02.928905</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980230</t>
+          <t>2026-03-05T04:09:02.928907</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980232</t>
+          <t>2026-03-05T04:09:02.928910</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980235</t>
+          <t>2026-03-05T04:09:02.928913</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980238</t>
+          <t>2026-03-05T04:09:02.928916</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006766</t>
+          <t>2026-03-05T04:09:03.882129</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006784</t>
+          <t>2026-03-05T04:09:03.882142</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006790</t>
+          <t>2026-03-05T04:09:03.882146</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006796</t>
+          <t>2026-03-05T04:09:03.882149</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006803</t>
+          <t>2026-03-05T04:09:03.882152</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006809</t>
+          <t>2026-03-05T04:09:03.882156</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006813</t>
+          <t>2026-03-05T04:09:03.882158</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006816</t>
+          <t>2026-03-05T04:09:03.882161</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006819</t>
+          <t>2026-03-05T04:09:03.882164</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006822</t>
+          <t>2026-03-05T04:09:03.882167</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006825</t>
+          <t>2026-03-05T04:09:03.882170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006827</t>
+          <t>2026-03-05T04:09:03.882173</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006830</t>
+          <t>2026-03-05T04:09:03.882176</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006833</t>
+          <t>2026-03-05T04:09:03.882180</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006837</t>
+          <t>2026-03-05T04:09:03.882186</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006840</t>
+          <t>2026-03-05T04:09:03.882190</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006843</t>
+          <t>2026-03-05T04:09:03.882192</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006845</t>
+          <t>2026-03-05T04:09:03.882195</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006849</t>
+          <t>2026-03-05T04:09:03.882198</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006853</t>
+          <t>2026-03-05T04:09:03.882201</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006856</t>
+          <t>2026-03-05T04:09:03.882204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006859</t>
+          <t>2026-03-05T04:09:03.882206</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006862</t>
+          <t>2026-03-05T04:09:03.882209</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006865</t>
+          <t>2026-03-05T04:09:03.882212</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006867</t>
+          <t>2026-03-05T04:09:03.882215</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006870</t>
+          <t>2026-03-05T04:09:03.882218</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006874</t>
+          <t>2026-03-05T04:09:03.882221</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006876</t>
+          <t>2026-03-05T04:09:03.882223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006880</t>
+          <t>2026-03-05T04:09:03.882227</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006883</t>
+          <t>2026-03-05T04:09:03.882230</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006893</t>
+          <t>2026-03-05T04:09:03.882232</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006896</t>
+          <t>2026-03-05T04:09:03.882243</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006899</t>
+          <t>2026-03-05T04:09:03.882246</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006902</t>
+          <t>2026-03-05T04:09:03.882249</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006905</t>
+          <t>2026-03-05T04:09:03.882252</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006908</t>
+          <t>2026-03-05T04:09:03.882255</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006910</t>
+          <t>2026-03-05T04:09:03.882258</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9094,14 +9094,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006913</t>
+          <t>2026-03-05T04:09:03.882260</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9159,14 +9159,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006916</t>
+          <t>2026-03-05T04:09:03.882263</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1373</v>
+        <v>1361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -9224,14 +9224,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006919</t>
+          <t>2026-03-05T04:09:03.882266</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006921</t>
+          <t>2026-03-05T04:09:03.882268</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9311,11 +9311,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1378</v>
+        <v>1366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:09.006924</t>
+          <t>2026-03-05T04:09:03.882271</t>
         </is>
       </c>
     </row>
@@ -9415,14 +9415,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1368.261904761905</v>
+        <v>1370.142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1585.08</v>
+        <v>1589.74</v>
       </c>
     </row>
     <row r="4">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1368.261904761905</v>
+        <v>1370.142857142857</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075980</t>
+          <t>2026-03-06T04:06:04.365846</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075995</t>
+          <t>2026-03-06T04:06:04.365859</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.075999</t>
+          <t>2026-03-06T04:06:04.365864</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076002</t>
+          <t>2026-03-06T04:06:04.365867</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076005</t>
+          <t>2026-03-06T04:06:04.365870</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076009</t>
+          <t>2026-03-06T04:06:04.365873</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076012</t>
+          <t>2026-03-06T04:06:04.365877</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076015</t>
+          <t>2026-03-06T04:06:04.365880</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076018</t>
+          <t>2026-03-06T04:06:04.365883</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076024</t>
+          <t>2026-03-06T04:06:04.365890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076027</t>
+          <t>2026-03-06T04:06:04.365892</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076030</t>
+          <t>2026-03-06T04:06:04.365895</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076033</t>
+          <t>2026-03-06T04:06:04.365898</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076036</t>
+          <t>2026-03-06T04:06:04.365901</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076039</t>
+          <t>2026-03-06T04:06:04.365904</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076042</t>
+          <t>2026-03-06T04:06:04.365907</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076044</t>
+          <t>2026-03-06T04:06:04.365909</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076047</t>
+          <t>2026-03-06T04:06:04.365912</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076050</t>
+          <t>2026-03-06T04:06:04.365915</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076055</t>
+          <t>2026-03-06T04:06:04.365920</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076058</t>
+          <t>2026-03-06T04:06:04.365923</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076061</t>
+          <t>2026-03-06T04:06:04.365926</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076064</t>
+          <t>2026-03-06T04:06:04.365928</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076067</t>
+          <t>2026-03-06T04:06:04.365931</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076069</t>
+          <t>2026-03-06T04:06:04.365934</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076072</t>
+          <t>2026-03-06T04:06:04.365937</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076075</t>
+          <t>2026-03-06T04:06:04.365939</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076078</t>
+          <t>2026-03-06T04:06:04.365942</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076081</t>
+          <t>2026-03-06T04:06:04.365945</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076086</t>
+          <t>2026-03-06T04:06:04.365950</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076088</t>
+          <t>2026-03-06T04:06:04.365952</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076091</t>
+          <t>2026-03-06T04:06:04.365955</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076094</t>
+          <t>2026-03-06T04:06:04.365958</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076097</t>
+          <t>2026-03-06T04:06:04.365961</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076099</t>
+          <t>2026-03-06T04:06:04.365963</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076102</t>
+          <t>2026-03-06T04:06:04.365966</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076105</t>
+          <t>2026-03-06T04:06:04.365969</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076108</t>
+          <t>2026-03-06T04:06:04.365972</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3017,14 +3017,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076110</t>
+          <t>2026-03-06T04:06:04.365974</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076113</t>
+          <t>2026-03-06T04:06:04.365977</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076116</t>
+          <t>2026-03-06T04:06:04.365980</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.076119</t>
+          <t>2026-03-06T04:06:04.365983</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928761</t>
+          <t>2026-03-06T04:06:05.174366</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928774</t>
+          <t>2026-03-06T04:06:05.174382</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928778</t>
+          <t>2026-03-06T04:06:05.174385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928781</t>
+          <t>2026-03-06T04:06:05.174388</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928787</t>
+          <t>2026-03-06T04:06:05.174395</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928790</t>
+          <t>2026-03-06T04:06:05.174398</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928793</t>
+          <t>2026-03-06T04:06:05.174401</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928796</t>
+          <t>2026-03-06T04:06:05.174404</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928799</t>
+          <t>2026-03-06T04:06:05.174407</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928802</t>
+          <t>2026-03-06T04:06:05.174410</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928804</t>
+          <t>2026-03-06T04:06:05.174412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928807</t>
+          <t>2026-03-06T04:06:05.174415</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928810</t>
+          <t>2026-03-06T04:06:05.174418</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928813</t>
+          <t>2026-03-06T04:06:05.174421</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928818</t>
+          <t>2026-03-06T04:06:05.174426</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928821</t>
+          <t>2026-03-06T04:06:05.174429</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928824</t>
+          <t>2026-03-06T04:06:05.174432</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928827</t>
+          <t>2026-03-06T04:06:05.174435</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928830</t>
+          <t>2026-03-06T04:06:05.174438</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928833</t>
+          <t>2026-03-06T04:06:05.174441</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928835</t>
+          <t>2026-03-06T04:06:05.174443</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928838</t>
+          <t>2026-03-06T04:06:05.174446</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928841</t>
+          <t>2026-03-06T04:06:05.174449</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928844</t>
+          <t>2026-03-06T04:06:05.174452</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928847</t>
+          <t>2026-03-06T04:06:05.174455</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928850</t>
+          <t>2026-03-06T04:06:05.174458</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928853</t>
+          <t>2026-03-06T04:06:05.174461</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928855</t>
+          <t>2026-03-06T04:06:05.174464</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928858</t>
+          <t>2026-03-06T04:06:05.174466</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928861</t>
+          <t>2026-03-06T04:06:05.174469</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928864</t>
+          <t>2026-03-06T04:06:05.174472</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928866</t>
+          <t>2026-03-06T04:06:05.174476</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928869</t>
+          <t>2026-03-06T04:06:05.174480</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928872</t>
+          <t>2026-03-06T04:06:05.174483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928875</t>
+          <t>2026-03-06T04:06:05.174486</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928877</t>
+          <t>2026-03-06T04:06:05.174488</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928880</t>
+          <t>2026-03-06T04:06:05.174491</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928883</t>
+          <t>2026-03-06T04:06:05.174494</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928885</t>
+          <t>2026-03-06T04:06:05.174497</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928888</t>
+          <t>2026-03-06T04:06:05.174499</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928891</t>
+          <t>2026-03-06T04:06:05.174502</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928893</t>
+          <t>2026-03-06T04:06:05.174505</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928896</t>
+          <t>2026-03-06T04:06:05.174508</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928899</t>
+          <t>2026-03-06T04:06:05.174511</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928902</t>
+          <t>2026-03-06T04:06:05.174514</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928905</t>
+          <t>2026-03-06T04:06:05.174517</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928907</t>
+          <t>2026-03-06T04:06:05.174519</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928910</t>
+          <t>2026-03-06T04:06:05.174522</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928913</t>
+          <t>2026-03-06T04:06:05.174525</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928916</t>
+          <t>2026-03-06T04:06:05.174528</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882129</t>
+          <t>2026-03-06T04:06:05.863917</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882142</t>
+          <t>2026-03-06T04:06:05.863931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882146</t>
+          <t>2026-03-06T04:06:05.863935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882149</t>
+          <t>2026-03-06T04:06:05.863938</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882152</t>
+          <t>2026-03-06T04:06:05.863941</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882156</t>
+          <t>2026-03-06T04:06:05.863944</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882158</t>
+          <t>2026-03-06T04:06:05.863947</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882161</t>
+          <t>2026-03-06T04:06:05.863950</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882164</t>
+          <t>2026-03-06T04:06:05.863953</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882167</t>
+          <t>2026-03-06T04:06:05.863956</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882170</t>
+          <t>2026-03-06T04:06:05.863959</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882173</t>
+          <t>2026-03-06T04:06:05.863962</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882176</t>
+          <t>2026-03-06T04:06:05.863964</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882180</t>
+          <t>2026-03-06T04:06:05.863967</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882186</t>
+          <t>2026-03-06T04:06:05.863971</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882190</t>
+          <t>2026-03-06T04:06:05.863974</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882192</t>
+          <t>2026-03-06T04:06:05.863976</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882195</t>
+          <t>2026-03-06T04:06:05.863979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882198</t>
+          <t>2026-03-06T04:06:05.863982</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882201</t>
+          <t>2026-03-06T04:06:05.863985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882204</t>
+          <t>2026-03-06T04:06:05.863988</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882206</t>
+          <t>2026-03-06T04:06:05.863992</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882209</t>
+          <t>2026-03-06T04:06:05.863996</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882212</t>
+          <t>2026-03-06T04:06:05.864000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882215</t>
+          <t>2026-03-06T04:06:05.864003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882218</t>
+          <t>2026-03-06T04:06:05.864005</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882221</t>
+          <t>2026-03-06T04:06:05.864008</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882223</t>
+          <t>2026-03-06T04:06:05.864011</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882227</t>
+          <t>2026-03-06T04:06:05.864014</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882230</t>
+          <t>2026-03-06T04:06:05.864017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882232</t>
+          <t>2026-03-06T04:06:05.864020</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882243</t>
+          <t>2026-03-06T04:06:05.864023</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8726,11 +8726,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882246</t>
+          <t>2026-03-06T04:06:05.864025</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882249</t>
+          <t>2026-03-06T04:06:05.864028</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882252</t>
+          <t>2026-03-06T04:06:05.864031</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882255</t>
+          <t>2026-03-06T04:06:05.864034</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882258</t>
+          <t>2026-03-06T04:06:05.864037</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9094,14 +9094,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882260</t>
+          <t>2026-03-06T04:06:05.864040</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9159,14 +9159,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882263</t>
+          <t>2026-03-06T04:06:05.864042</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1361</v>
+        <v>1297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9224,14 +9224,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882266</t>
+          <t>2026-03-06T04:06:05.864054</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1363</v>
+        <v>1299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882268</t>
+          <t>2026-03-06T04:06:05.864057</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9311,11 +9311,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1366</v>
+        <v>1297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:03.882271</t>
+          <t>2026-03-06T04:06:05.864060</t>
         </is>
       </c>
     </row>
@@ -9415,14 +9415,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1370.142857142857</v>
+        <v>1371.571428571429</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1589.74</v>
+        <v>1591.08</v>
       </c>
     </row>
     <row r="4">
@@ -9467,14 +9467,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1370.142857142857</v>
+        <v>1371.571428571429</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365846</t>
+          <t>2026-03-07T03:57:00.438508</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365859</t>
+          <t>2026-03-07T03:57:00.438519</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365864</t>
+          <t>2026-03-07T03:57:00.438524</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365867</t>
+          <t>2026-03-07T03:57:00.438527</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365870</t>
+          <t>2026-03-07T03:57:00.438530</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365873</t>
+          <t>2026-03-07T03:57:00.438533</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365877</t>
+          <t>2026-03-07T03:57:00.438536</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365880</t>
+          <t>2026-03-07T03:57:00.438543</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365883</t>
+          <t>2026-03-07T03:57:00.438546</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365890</t>
+          <t>2026-03-07T03:57:00.438549</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365892</t>
+          <t>2026-03-07T03:57:00.438552</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365895</t>
+          <t>2026-03-07T03:57:00.438555</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365898</t>
+          <t>2026-03-07T03:57:00.438558</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365901</t>
+          <t>2026-03-07T03:57:00.438561</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365904</t>
+          <t>2026-03-07T03:57:00.438563</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365907</t>
+          <t>2026-03-07T03:57:00.438566</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365909</t>
+          <t>2026-03-07T03:57:00.438569</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365912</t>
+          <t>2026-03-07T03:57:00.438573</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365915</t>
+          <t>2026-03-07T03:57:00.438576</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365920</t>
+          <t>2026-03-07T03:57:00.438579</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365923</t>
+          <t>2026-03-07T03:57:00.438582</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365926</t>
+          <t>2026-03-07T03:57:00.438584</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365928</t>
+          <t>2026-03-07T03:57:00.438587</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365931</t>
+          <t>2026-03-07T03:57:00.438590</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365934</t>
+          <t>2026-03-07T03:57:00.438593</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365937</t>
+          <t>2026-03-07T03:57:00.438595</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365939</t>
+          <t>2026-03-07T03:57:00.438598</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365942</t>
+          <t>2026-03-07T03:57:00.438603</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365945</t>
+          <t>2026-03-07T03:57:00.438606</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365950</t>
+          <t>2026-03-07T03:57:00.438608</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365952</t>
+          <t>2026-03-07T03:57:00.438611</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365955</t>
+          <t>2026-03-07T03:57:00.438614</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365958</t>
+          <t>2026-03-07T03:57:00.438617</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365961</t>
+          <t>2026-03-07T03:57:00.438619</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365963</t>
+          <t>2026-03-07T03:57:00.438622</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365966</t>
+          <t>2026-03-07T03:57:00.438625</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365969</t>
+          <t>2026-03-07T03:57:00.438628</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365972</t>
+          <t>2026-03-07T03:57:00.438631</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3017,202 +3017,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:04.365974</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365977</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365980</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:04.365983</t>
+          <t>2026-03-07T03:57:00.438633</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3163,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174366</t>
+          <t>2026-03-07T03:57:01.332924</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3380,11 +3185,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1577</v>
+        <v>1555</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3423,7 +3228,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174382</t>
+          <t>2026-03-07T03:57:01.332935</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3240,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3445,11 +3250,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3488,7 +3293,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174385</t>
+          <t>2026-03-07T03:57:01.332938</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3305,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3510,11 +3315,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1577</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3553,7 +3358,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174388</t>
+          <t>2026-03-07T03:57:01.332941</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3370,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3575,11 +3380,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3618,7 +3423,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174395</t>
+          <t>2026-03-07T03:57:01.332944</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3435,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3640,11 +3445,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3683,7 +3488,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174398</t>
+          <t>2026-03-07T03:57:01.332951</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3500,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3705,11 +3510,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3748,7 +3553,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174401</t>
+          <t>2026-03-07T03:57:01.332954</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3565,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3770,11 +3575,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3813,7 +3618,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174404</t>
+          <t>2026-03-07T03:57:01.332957</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3835,11 +3640,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1590</v>
+        <v>1597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3858,7 +3663,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3878,7 +3683,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174407</t>
+          <t>2026-03-07T03:57:01.332959</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3900,11 +3705,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3943,7 +3748,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174410</t>
+          <t>2026-03-07T03:57:01.332962</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3760,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3965,11 +3770,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4008,7 +3813,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174412</t>
+          <t>2026-03-07T03:57:01.332965</t>
         </is>
       </c>
     </row>
@@ -4020,7 +3825,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4030,11 +3835,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4053,7 +3858,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4073,7 +3878,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174415</t>
+          <t>2026-03-07T03:57:01.332968</t>
         </is>
       </c>
     </row>
@@ -4085,7 +3890,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4095,11 +3900,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1565</v>
+        <v>1597</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4138,7 +3943,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174418</t>
+          <t>2026-03-07T03:57:01.332971</t>
         </is>
       </c>
     </row>
@@ -4150,7 +3955,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4160,11 +3965,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4203,7 +4008,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174421</t>
+          <t>2026-03-07T03:57:01.332974</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4020,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4225,11 +4030,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1597</v>
+        <v>1565</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4268,7 +4073,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174426</t>
+          <t>2026-03-07T03:57:01.332976</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4085,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4290,11 +4095,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4333,7 +4138,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174429</t>
+          <t>2026-03-07T03:57:01.332996</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4150,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4355,11 +4160,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4398,7 +4203,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174432</t>
+          <t>2026-03-07T03:57:01.333000</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4268,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174435</t>
+          <t>2026-03-07T03:57:01.333003</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4280,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4485,11 +4290,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1642</v>
+        <v>1585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4508,7 +4313,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4528,7 +4333,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174438</t>
+          <t>2026-03-07T03:57:01.333006</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4398,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174441</t>
+          <t>2026-03-07T03:57:01.333009</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4410,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4615,11 +4420,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4658,7 +4463,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174443</t>
+          <t>2026-03-07T03:57:01.333012</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4475,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4680,11 +4485,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4723,7 +4528,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174446</t>
+          <t>2026-03-07T03:57:01.333014</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4540,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4745,11 +4550,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4788,7 +4593,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174449</t>
+          <t>2026-03-07T03:57:01.333018</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4605,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4810,11 +4615,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1585</v>
+        <v>1650</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4833,7 +4638,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4853,7 +4658,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174452</t>
+          <t>2026-03-07T03:57:01.333021</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4670,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4875,11 +4680,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4918,7 +4723,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174455</t>
+          <t>2026-03-07T03:57:01.333025</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4735,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4940,11 +4745,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1622</v>
+        <v>1585</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4983,7 +4788,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174458</t>
+          <t>2026-03-07T03:57:01.333029</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4800,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5005,11 +4810,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5048,7 +4853,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174461</t>
+          <t>2026-03-07T03:57:01.333032</t>
         </is>
       </c>
     </row>
@@ -5060,7 +4865,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5070,11 +4875,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1585</v>
+        <v>1620</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5113,7 +4918,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174464</t>
+          <t>2026-03-07T03:57:01.333035</t>
         </is>
       </c>
     </row>
@@ -5125,7 +4930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5135,11 +4940,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5178,7 +4983,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174466</t>
+          <t>2026-03-07T03:57:01.333037</t>
         </is>
       </c>
     </row>
@@ -5190,7 +4995,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5200,11 +5005,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5243,7 +5048,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174469</t>
+          <t>2026-03-07T03:57:01.333040</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5060,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5265,11 +5070,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1555</v>
+        <v>1606</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5308,7 +5113,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174472</t>
+          <t>2026-03-07T03:57:01.333043</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5330,11 +5135,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5373,7 +5178,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174476</t>
+          <t>2026-03-07T03:57:01.333045</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5243,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174480</t>
+          <t>2026-03-07T03:57:01.333048</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5255,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5460,11 +5265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5503,7 +5308,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174483</t>
+          <t>2026-03-07T03:57:01.333051</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5320,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5568,7 +5373,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174486</t>
+          <t>2026-03-07T03:57:01.333053</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5385,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5590,11 +5395,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1608</v>
+        <v>1555</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5633,7 +5438,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174488</t>
+          <t>2026-03-07T03:57:01.333056</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5503,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174491</t>
+          <t>2026-03-07T03:57:01.333059</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5515,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5720,11 +5525,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5763,7 +5568,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174494</t>
+          <t>2026-03-07T03:57:01.333062</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5580,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5785,11 +5590,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5808,7 +5613,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,7 +5633,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174497</t>
+          <t>2026-03-07T03:57:01.333064</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5645,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5850,11 +5655,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5893,7 +5698,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174499</t>
+          <t>2026-03-07T03:57:01.333067</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5763,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174502</t>
+          <t>2026-03-07T03:57:01.333070</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5775,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5980,11 +5785,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6003,7 +5808,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6023,7 +5828,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174505</t>
+          <t>2026-03-07T03:57:01.333072</t>
         </is>
       </c>
     </row>
@@ -6035,7 +5840,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6045,11 +5850,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6068,7 +5873,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6088,7 +5893,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174508</t>
+          <t>2026-03-07T03:57:01.333075</t>
         </is>
       </c>
     </row>
@@ -6100,7 +5905,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6110,11 +5915,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1574</v>
+        <v>1535</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6133,7 +5938,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6153,7 +5958,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174511</t>
+          <t>2026-03-07T03:57:01.333078</t>
         </is>
       </c>
     </row>
@@ -6165,7 +5970,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6175,11 +5980,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6198,7 +6003,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6218,7 +6023,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174514</t>
+          <t>2026-03-07T03:57:01.333080</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6035,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6240,11 +6045,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1535</v>
+        <v>1574</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6263,7 +6068,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,7 +6088,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174517</t>
+          <t>2026-03-07T03:57:01.333083</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6153,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174519</t>
+          <t>2026-03-07T03:57:01.333086</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6165,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6370,11 +6175,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6413,7 +6218,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174522</t>
+          <t>2026-03-07T03:57:01.333089</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6283,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174525</t>
+          <t>2026-03-07T03:57:01.333092</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6295,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6500,11 +6305,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1535</v>
+        <v>1568</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6523,7 +6328,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6348,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174528</t>
+          <t>2026-03-07T03:57:01.333094</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6636,7 +6441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6646,11 +6451,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6689,7 +6494,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863917</t>
+          <t>2026-03-07T03:57:02.160704</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6711,11 +6516,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6754,7 +6559,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863931</t>
+          <t>2026-03-07T03:57:02.160716</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6571,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6776,11 +6581,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6819,7 +6624,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863935</t>
+          <t>2026-03-07T03:57:02.160720</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6841,11 +6646,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6884,7 +6689,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863938</t>
+          <t>2026-03-07T03:57:02.160723</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6701,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6906,11 +6711,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6929,7 +6734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,7 +6754,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863941</t>
+          <t>2026-03-07T03:57:02.160726</t>
         </is>
       </c>
     </row>
@@ -6961,7 +6766,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6994,7 +6799,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,7 +6819,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863944</t>
+          <t>2026-03-07T03:57:02.160744</t>
         </is>
       </c>
     </row>
@@ -7079,7 +6884,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863947</t>
+          <t>2026-03-07T03:57:02.160751</t>
         </is>
       </c>
     </row>
@@ -7144,7 +6949,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863950</t>
+          <t>2026-03-07T03:57:02.160759</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7014,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863953</t>
+          <t>2026-03-07T03:57:02.160765</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863956</t>
+          <t>2026-03-07T03:57:02.160770</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7144,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863959</t>
+          <t>2026-03-07T03:57:02.160775</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7209,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863962</t>
+          <t>2026-03-07T03:57:02.160781</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7274,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863964</t>
+          <t>2026-03-07T03:57:02.160788</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7339,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863967</t>
+          <t>2026-03-07T03:57:02.160795</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7404,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863971</t>
+          <t>2026-03-07T03:57:02.160801</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7469,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863974</t>
+          <t>2026-03-07T03:57:02.160808</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7534,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863976</t>
+          <t>2026-03-07T03:57:02.160811</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7599,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863979</t>
+          <t>2026-03-07T03:57:02.160814</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7664,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863982</t>
+          <t>2026-03-07T03:57:02.160817</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7729,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863985</t>
+          <t>2026-03-07T03:57:02.160820</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7794,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863988</t>
+          <t>2026-03-07T03:57:02.160823</t>
         </is>
       </c>
     </row>
@@ -8001,7 +7806,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8011,11 +7816,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8034,7 +7839,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8054,7 +7859,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863992</t>
+          <t>2026-03-07T03:57:02.160825</t>
         </is>
       </c>
     </row>
@@ -8066,7 +7871,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8076,11 +7881,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8119,7 +7924,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.863996</t>
+          <t>2026-03-07T03:57:02.160828</t>
         </is>
       </c>
     </row>
@@ -8131,7 +7936,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8141,11 +7946,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8164,7 +7969,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8184,7 +7989,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864000</t>
+          <t>2026-03-07T03:57:02.160831</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8001,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8249,7 +8054,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864003</t>
+          <t>2026-03-07T03:57:02.160833</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8119,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864005</t>
+          <t>2026-03-07T03:57:02.160836</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8131,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8379,7 +8184,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864008</t>
+          <t>2026-03-07T03:57:02.160839</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8249,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864011</t>
+          <t>2026-03-07T03:57:02.160842</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8261,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8509,7 +8314,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864014</t>
+          <t>2026-03-07T03:57:02.160845</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8326,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8574,7 +8379,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864017</t>
+          <t>2026-03-07T03:57:02.160847</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8391,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8596,11 +8401,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8639,7 +8444,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864020</t>
+          <t>2026-03-07T03:57:02.160850</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8456,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8661,11 +8466,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8704,7 +8509,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864023</t>
+          <t>2026-03-07T03:57:02.160854</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8574,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864025</t>
+          <t>2026-03-07T03:57:02.160857</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8586,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8791,11 +8596,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8834,7 +8639,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864028</t>
+          <t>2026-03-07T03:57:02.160859</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8651,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8899,7 +8704,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864031</t>
+          <t>2026-03-07T03:57:02.160862</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8716,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8921,11 +8726,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8964,7 +8769,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864034</t>
+          <t>2026-03-07T03:57:02.160865</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8781,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9029,7 +8834,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864037</t>
+          <t>2026-03-07T03:57:02.160868</t>
         </is>
       </c>
     </row>
@@ -9041,7 +8846,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9051,11 +8856,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1297.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9094,7 +8899,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864040</t>
+          <t>2026-03-07T03:57:02.160870</t>
         </is>
       </c>
     </row>
@@ -9106,7 +8911,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9116,11 +8921,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1299.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9159,202 +8964,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.864042</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864054</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864057</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-06T04:06:05.864060</t>
+          <t>2026-03-07T03:57:02.160873</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9021,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9422,7 +9032,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1371.571428571429</v>
+        <v>1377.25641025641</v>
       </c>
     </row>
     <row r="3">
@@ -9448,7 +9058,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1591.08</v>
+        <v>1591.74</v>
       </c>
     </row>
     <row r="4">
@@ -9463,7 +9073,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9474,7 +9084,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1371.571428571429</v>
+        <v>1377.25641025641</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438508</t>
+          <t>2026-03-08T04:07:50.583982</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438519</t>
+          <t>2026-03-08T04:07:50.583996</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438524</t>
+          <t>2026-03-08T04:07:50.584001</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438527</t>
+          <t>2026-03-08T04:07:50.584004</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438530</t>
+          <t>2026-03-08T04:07:50.584007</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438533</t>
+          <t>2026-03-08T04:07:50.584010</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438536</t>
+          <t>2026-03-08T04:07:50.584013</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438543</t>
+          <t>2026-03-08T04:07:50.584020</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438546</t>
+          <t>2026-03-08T04:07:50.584024</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438549</t>
+          <t>2026-03-08T04:07:50.584027</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438552</t>
+          <t>2026-03-08T04:07:50.584030</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438555</t>
+          <t>2026-03-08T04:07:50.584033</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438558</t>
+          <t>2026-03-08T04:07:50.584036</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438561</t>
+          <t>2026-03-08T04:07:50.584038</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438563</t>
+          <t>2026-03-08T04:07:50.584041</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438566</t>
+          <t>2026-03-08T04:07:50.584044</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438569</t>
+          <t>2026-03-08T04:07:50.584046</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438573</t>
+          <t>2026-03-08T04:07:50.584052</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438576</t>
+          <t>2026-03-08T04:07:50.584055</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438579</t>
+          <t>2026-03-08T04:07:50.584057</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438582</t>
+          <t>2026-03-08T04:07:50.584060</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438584</t>
+          <t>2026-03-08T04:07:50.584063</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438587</t>
+          <t>2026-03-08T04:07:50.584065</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438590</t>
+          <t>2026-03-08T04:07:50.584068</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438593</t>
+          <t>2026-03-08T04:07:50.584071</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438595</t>
+          <t>2026-03-08T04:07:50.584074</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438598</t>
+          <t>2026-03-08T04:07:50.584077</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438603</t>
+          <t>2026-03-08T04:07:50.584082</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438606</t>
+          <t>2026-03-08T04:07:50.584084</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438608</t>
+          <t>2026-03-08T04:07:50.584087</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438611</t>
+          <t>2026-03-08T04:07:50.584090</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438614</t>
+          <t>2026-03-08T04:07:50.584092</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438617</t>
+          <t>2026-03-08T04:07:50.584095</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438619</t>
+          <t>2026-03-08T04:07:50.584098</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438622</t>
+          <t>2026-03-08T04:07:50.584101</t>
         </is>
       </c>
     </row>
@@ -2822,202 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:00.438625</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438628</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438631</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>首饰黄金</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>jewelry</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:00.438633</t>
+          <t>2026-03-08T04:07:50.584104</t>
         </is>
       </c>
     </row>
@@ -3105,7 +2910,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3120,11 +2925,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3143,7 +2948,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3163,14 +2968,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332924</t>
+          <t>2026-03-08T04:07:51.386085</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3208,7 +3013,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3228,14 +3033,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332935</t>
+          <t>2026-03-08T04:07:51.386100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3250,11 +3055,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3273,7 +3078,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3293,14 +3098,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332938</t>
+          <t>2026-03-08T04:07:51.386103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3315,11 +3120,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3338,7 +3143,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3358,14 +3163,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332941</t>
+          <t>2026-03-08T04:07:51.386107</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3380,11 +3185,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3403,7 +3208,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3423,14 +3228,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332944</t>
+          <t>2026-03-08T04:07:51.386110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3445,11 +3250,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3468,7 +3273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3488,14 +3293,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332951</t>
+          <t>2026-03-08T04:07:51.386112</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3510,11 +3315,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3533,7 +3338,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3553,14 +3358,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332954</t>
+          <t>2026-03-08T04:07:51.386116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3575,11 +3380,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3598,7 +3403,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3618,14 +3423,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332957</t>
+          <t>2026-03-08T04:07:51.386118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3640,11 +3445,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3663,7 +3468,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3683,14 +3488,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332959</t>
+          <t>2026-03-08T04:07:51.386124</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3705,11 +3510,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3728,7 +3533,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3748,14 +3553,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332962</t>
+          <t>2026-03-08T04:07:51.386127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3770,11 +3575,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3793,7 +3598,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3813,14 +3618,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332965</t>
+          <t>2026-03-08T04:07:51.386130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3835,11 +3640,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3878,14 +3683,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332968</t>
+          <t>2026-03-08T04:07:51.386132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3923,7 +3728,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3943,14 +3748,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332971</t>
+          <t>2026-03-08T04:07:51.386135</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3988,7 +3793,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4008,14 +3813,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332974</t>
+          <t>2026-03-08T04:07:51.386138</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4053,7 +3858,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4073,14 +3878,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332976</t>
+          <t>2026-03-08T04:07:51.386141</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4118,7 +3923,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4138,14 +3943,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332996</t>
+          <t>2026-03-08T04:07:51.386144</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4160,11 +3965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4203,14 +4008,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333000</t>
+          <t>2026-03-08T04:07:51.386146</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4248,7 +4053,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4268,14 +4073,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333003</t>
+          <t>2026-03-08T04:07:51.386149</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4290,11 +4095,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4313,7 +4118,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4333,14 +4138,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333006</t>
+          <t>2026-03-08T04:07:51.386155</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4355,11 +4160,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4378,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4398,14 +4203,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333009</t>
+          <t>2026-03-08T04:07:51.386158</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4420,11 +4225,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4443,7 +4248,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4463,14 +4268,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333012</t>
+          <t>2026-03-08T04:07:51.386160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4485,11 +4290,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4508,7 +4313,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4528,14 +4333,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333014</t>
+          <t>2026-03-08T04:07:51.386164</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4550,11 +4355,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4573,7 +4378,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4593,14 +4398,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333018</t>
+          <t>2026-03-08T04:07:51.386166</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4615,11 +4420,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4638,7 +4443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4658,14 +4463,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333021</t>
+          <t>2026-03-08T04:07:51.386169</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4680,11 +4485,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4723,14 +4528,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333025</t>
+          <t>2026-03-08T04:07:51.386172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4768,7 +4573,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4788,14 +4593,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333029</t>
+          <t>2026-03-08T04:07:51.386175</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4810,11 +4615,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4853,14 +4658,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333032</t>
+          <t>2026-03-08T04:07:51.386178</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4875,11 +4680,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4918,14 +4723,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333035</t>
+          <t>2026-03-08T04:07:51.386180</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4940,11 +4745,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4983,14 +4788,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333037</t>
+          <t>2026-03-08T04:07:51.386183</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5005,11 +4810,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5048,14 +4853,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333040</t>
+          <t>2026-03-08T04:07:51.386186</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5070,11 +4875,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5113,14 +4918,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333043</t>
+          <t>2026-03-08T04:07:51.386189</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5135,11 +4940,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5178,14 +4983,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333045</t>
+          <t>2026-03-08T04:07:51.386192</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5200,11 +5005,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5243,14 +5048,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333048</t>
+          <t>2026-03-08T04:07:51.386195</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5265,11 +5070,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5308,14 +5113,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333051</t>
+          <t>2026-03-08T04:07:51.386198</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5330,11 +5135,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5373,14 +5178,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333053</t>
+          <t>2026-03-08T04:07:51.386201</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5395,11 +5200,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5438,14 +5243,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333056</t>
+          <t>2026-03-08T04:07:51.386203</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5460,11 +5265,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5483,7 +5288,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5503,14 +5308,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333059</t>
+          <t>2026-03-08T04:07:51.386206</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5525,11 +5330,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5548,7 +5353,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5568,14 +5373,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333062</t>
+          <t>2026-03-08T04:07:51.386209</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5590,11 +5395,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5613,7 +5418,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5633,14 +5438,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333064</t>
+          <t>2026-03-08T04:07:51.386212</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5655,11 +5460,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5678,7 +5483,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5698,14 +5503,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333067</t>
+          <t>2026-03-08T04:07:51.386214</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5720,11 +5525,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5743,7 +5548,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5763,14 +5568,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333070</t>
+          <t>2026-03-08T04:07:51.386217</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5785,11 +5590,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5828,14 +5633,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333072</t>
+          <t>2026-03-08T04:07:51.386220</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5873,7 +5678,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5893,14 +5698,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333075</t>
+          <t>2026-03-08T04:07:51.386223</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5958,14 +5763,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333078</t>
+          <t>2026-03-08T04:07:51.386225</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5980,11 +5785,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6003,7 +5808,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6023,14 +5828,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333080</t>
+          <t>2026-03-08T04:07:51.386228</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6068,7 +5873,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6088,14 +5893,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333083</t>
+          <t>2026-03-08T04:07:51.386231</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6133,7 +5938,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6153,14 +5958,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333086</t>
+          <t>2026-03-08T04:07:51.386234</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6218,14 +6023,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333089</t>
+          <t>2026-03-08T04:07:51.386237</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6263,7 +6068,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6283,14 +6088,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333092</t>
+          <t>2026-03-08T04:07:51.386239</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6305,11 +6110,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6153,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333094</t>
+          <t>2026-03-08T04:07:51.386242</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6494,7 +6299,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160704</t>
+          <t>2026-03-08T04:07:52.125602</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6364,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160716</t>
+          <t>2026-03-08T04:07:52.125617</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6429,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160720</t>
+          <t>2026-03-08T04:07:52.125621</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6494,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160723</t>
+          <t>2026-03-08T04:07:52.125625</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6559,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160726</t>
+          <t>2026-03-08T04:07:52.125628</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6624,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160744</t>
+          <t>2026-03-08T04:07:52.125631</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6689,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160751</t>
+          <t>2026-03-08T04:07:52.125634</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6754,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160759</t>
+          <t>2026-03-08T04:07:52.125636</t>
         </is>
       </c>
     </row>
@@ -7014,7 +6819,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160765</t>
+          <t>2026-03-08T04:07:52.125639</t>
         </is>
       </c>
     </row>
@@ -7079,7 +6884,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160770</t>
+          <t>2026-03-08T04:07:52.125642</t>
         </is>
       </c>
     </row>
@@ -7144,7 +6949,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160775</t>
+          <t>2026-03-08T04:07:52.125645</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7014,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160781</t>
+          <t>2026-03-08T04:07:52.125647</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7079,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160788</t>
+          <t>2026-03-08T04:07:52.125650</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7144,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160795</t>
+          <t>2026-03-08T04:07:52.125653</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7209,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160801</t>
+          <t>2026-03-08T04:07:52.125656</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7221,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7426,11 +7231,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7469,7 +7274,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160808</t>
+          <t>2026-03-08T04:07:52.125658</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7491,11 +7296,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7534,7 +7339,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160811</t>
+          <t>2026-03-08T04:07:52.125661</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7351,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7556,11 +7361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7599,7 +7404,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160814</t>
+          <t>2026-03-08T04:07:52.125664</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7416,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7621,11 +7426,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7664,7 +7469,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160817</t>
+          <t>2026-03-08T04:07:52.125668</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7481,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7686,11 +7491,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7729,7 +7534,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160820</t>
+          <t>2026-03-08T04:07:52.125671</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7599,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160823</t>
+          <t>2026-03-08T04:07:52.125675</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7611,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7816,11 +7621,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7839,7 +7644,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7859,7 +7664,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160825</t>
+          <t>2026-03-08T04:07:52.125679</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7729,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160828</t>
+          <t>2026-03-08T04:07:52.125702</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7741,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7946,11 +7751,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7969,7 +7774,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7989,7 +7794,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160831</t>
+          <t>2026-03-08T04:07:52.125706</t>
         </is>
       </c>
     </row>
@@ -8001,7 +7806,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8011,11 +7816,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8054,7 +7859,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160833</t>
+          <t>2026-03-08T04:07:52.125708</t>
         </is>
       </c>
     </row>
@@ -8066,7 +7871,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8076,11 +7881,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8119,7 +7924,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160836</t>
+          <t>2026-03-08T04:07:52.125711</t>
         </is>
       </c>
     </row>
@@ -8184,7 +7989,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160839</t>
+          <t>2026-03-08T04:07:52.125714</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8054,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160842</t>
+          <t>2026-03-08T04:07:52.125717</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8119,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160845</t>
+          <t>2026-03-08T04:07:52.125720</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8184,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160847</t>
+          <t>2026-03-08T04:07:52.125722</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8249,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160850</t>
+          <t>2026-03-08T04:07:52.125725</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8261,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8466,11 +8271,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8509,7 +8314,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160854</t>
+          <t>2026-03-08T04:07:52.125728</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8326,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8531,11 +8336,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8574,7 +8379,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160857</t>
+          <t>2026-03-08T04:07:52.125731</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8391,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8639,7 +8444,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160859</t>
+          <t>2026-03-08T04:07:52.125734</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8456,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8704,7 +8509,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160862</t>
+          <t>2026-03-08T04:07:52.125737</t>
         </is>
       </c>
     </row>
@@ -8769,202 +8574,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:02.160865</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>周生生</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160868</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>六福</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1297.00</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1297</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160870</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周大福</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>金条金价(内地)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1299.00</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1299</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>跌</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>金条</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>gold_bar</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-03-07T03:57:02.160873</t>
+          <t>2026-03-08T04:07:52.125740</t>
         </is>
       </c>
     </row>
@@ -9021,7 +8631,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9032,7 +8642,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1377.25641025641</v>
+        <v>1383.888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -9051,14 +8661,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1591.74</v>
+        <v>1593.98</v>
       </c>
     </row>
     <row r="4">
@@ -9073,7 +8683,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -9084,7 +8694,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1377.25641025641</v>
+        <v>1383.888888888889</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.583982</t>
+          <t>2026-03-09T04:13:10.124860</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.583996</t>
+          <t>2026-03-09T04:13:10.124875</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584001</t>
+          <t>2026-03-09T04:13:10.124879</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584004</t>
+          <t>2026-03-09T04:13:10.124882</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584007</t>
+          <t>2026-03-09T04:13:10.124885</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584010</t>
+          <t>2026-03-09T04:13:10.124889</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584013</t>
+          <t>2026-03-09T04:13:10.124892</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584020</t>
+          <t>2026-03-09T04:13:10.124899</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584024</t>
+          <t>2026-03-09T04:13:10.124902</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584027</t>
+          <t>2026-03-09T04:13:10.124905</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584030</t>
+          <t>2026-03-09T04:13:10.124908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584033</t>
+          <t>2026-03-09T04:13:10.124911</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584036</t>
+          <t>2026-03-09T04:13:10.124914</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584038</t>
+          <t>2026-03-09T04:13:10.124917</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584041</t>
+          <t>2026-03-09T04:13:10.124919</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584044</t>
+          <t>2026-03-09T04:13:10.124922</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584046</t>
+          <t>2026-03-09T04:13:10.124925</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584052</t>
+          <t>2026-03-09T04:13:10.124930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584055</t>
+          <t>2026-03-09T04:13:10.124933</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584057</t>
+          <t>2026-03-09T04:13:10.124935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584060</t>
+          <t>2026-03-09T04:13:10.124938</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584063</t>
+          <t>2026-03-09T04:13:10.124941</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584065</t>
+          <t>2026-03-09T04:13:10.124944</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584068</t>
+          <t>2026-03-09T04:13:10.124946</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584071</t>
+          <t>2026-03-09T04:13:10.124949</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584074</t>
+          <t>2026-03-09T04:13:10.124952</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584077</t>
+          <t>2026-03-09T04:13:10.124955</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584082</t>
+          <t>2026-03-09T04:13:10.124960</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584084</t>
+          <t>2026-03-09T04:13:10.124962</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584087</t>
+          <t>2026-03-09T04:13:10.124965</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584090</t>
+          <t>2026-03-09T04:13:10.124968</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584092</t>
+          <t>2026-03-09T04:13:10.124971</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584095</t>
+          <t>2026-03-09T04:13:10.124973</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584098</t>
+          <t>2026-03-09T04:13:10.124976</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584101</t>
+          <t>2026-03-09T04:13:10.124979</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:50.584104</t>
+          <t>2026-03-09T04:13:10.124982</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2925,11 +2925,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386085</t>
+          <t>2026-03-09T04:13:11.031932</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2990,11 +2990,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386100</t>
+          <t>2026-03-09T04:13:11.031945</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3055,11 +3055,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386103</t>
+          <t>2026-03-09T04:13:11.031949</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386107</t>
+          <t>2026-03-09T04:13:11.031952</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386110</t>
+          <t>2026-03-09T04:13:11.031955</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386112</t>
+          <t>2026-03-09T04:13:11.031958</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386116</t>
+          <t>2026-03-09T04:13:11.031961</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386118</t>
+          <t>2026-03-09T04:13:11.031963</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386124</t>
+          <t>2026-03-09T04:13:11.031969</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386127</t>
+          <t>2026-03-09T04:13:11.031972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386130</t>
+          <t>2026-03-09T04:13:11.031975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386132</t>
+          <t>2026-03-09T04:13:11.031977</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386135</t>
+          <t>2026-03-09T04:13:11.031980</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386138</t>
+          <t>2026-03-09T04:13:11.031983</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386141</t>
+          <t>2026-03-09T04:13:11.031986</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386144</t>
+          <t>2026-03-09T04:13:11.031988</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386146</t>
+          <t>2026-03-09T04:13:11.031991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386149</t>
+          <t>2026-03-09T04:13:11.031997</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386155</t>
+          <t>2026-03-09T04:13:11.032008</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386158</t>
+          <t>2026-03-09T04:13:11.032011</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386160</t>
+          <t>2026-03-09T04:13:11.032013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386164</t>
+          <t>2026-03-09T04:13:11.032016</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386166</t>
+          <t>2026-03-09T04:13:11.032019</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386169</t>
+          <t>2026-03-09T04:13:11.032022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386172</t>
+          <t>2026-03-09T04:13:11.032025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386175</t>
+          <t>2026-03-09T04:13:11.032028</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386178</t>
+          <t>2026-03-09T04:13:11.032030</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386180</t>
+          <t>2026-03-09T04:13:11.032033</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386183</t>
+          <t>2026-03-09T04:13:11.032036</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386186</t>
+          <t>2026-03-09T04:13:11.032039</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386189</t>
+          <t>2026-03-09T04:13:11.032042</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386192</t>
+          <t>2026-03-09T04:13:11.032044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386195</t>
+          <t>2026-03-09T04:13:11.032047</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386198</t>
+          <t>2026-03-09T04:13:11.032050</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386201</t>
+          <t>2026-03-09T04:13:11.032052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386203</t>
+          <t>2026-03-09T04:13:11.032055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386206</t>
+          <t>2026-03-09T04:13:11.032058</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386209</t>
+          <t>2026-03-09T04:13:11.032060</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386212</t>
+          <t>2026-03-09T04:13:11.032063</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386214</t>
+          <t>2026-03-09T04:13:11.032066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386217</t>
+          <t>2026-03-09T04:13:11.032068</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386220</t>
+          <t>2026-03-09T04:13:11.032071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386223</t>
+          <t>2026-03-09T04:13:11.032074</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386225</t>
+          <t>2026-03-09T04:13:11.032077</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386228</t>
+          <t>2026-03-09T04:13:11.032079</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386231</t>
+          <t>2026-03-09T04:13:11.032082</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386234</t>
+          <t>2026-03-09T04:13:11.032085</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386237</t>
+          <t>2026-03-09T04:13:11.032087</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386239</t>
+          <t>2026-03-09T04:13:11.032090</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386242</t>
+          <t>2026-03-09T04:13:11.032093</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6256,11 +6256,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6299,14 +6299,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125602</t>
+          <t>2026-03-09T04:13:11.803683</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6364,14 +6364,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125617</t>
+          <t>2026-03-09T04:13:11.803697</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6429,14 +6429,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125621</t>
+          <t>2026-03-09T04:13:11.803701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6494,14 +6494,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125625</t>
+          <t>2026-03-09T04:13:11.803704</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6516,11 +6516,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125628</t>
+          <t>2026-03-09T04:13:11.803707</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125631</t>
+          <t>2026-03-09T04:13:11.803710</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125634</t>
+          <t>2026-03-09T04:13:11.803713</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125636</t>
+          <t>2026-03-09T04:13:11.803716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125639</t>
+          <t>2026-03-09T04:13:11.803718</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125642</t>
+          <t>2026-03-09T04:13:11.803722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125645</t>
+          <t>2026-03-09T04:13:11.803724</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125647</t>
+          <t>2026-03-09T04:13:11.803727</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125650</t>
+          <t>2026-03-09T04:13:11.803730</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125653</t>
+          <t>2026-03-09T04:13:11.803737</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125656</t>
+          <t>2026-03-09T04:13:11.803740</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125658</t>
+          <t>2026-03-09T04:13:11.803744</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125661</t>
+          <t>2026-03-09T04:13:11.803746</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125664</t>
+          <t>2026-03-09T04:13:11.803749</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125668</t>
+          <t>2026-03-09T04:13:11.803753</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125671</t>
+          <t>2026-03-09T04:13:11.803757</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125675</t>
+          <t>2026-03-09T04:13:11.803760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125679</t>
+          <t>2026-03-09T04:13:11.803763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125702</t>
+          <t>2026-03-09T04:13:11.803765</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125706</t>
+          <t>2026-03-09T04:13:11.803768</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125708</t>
+          <t>2026-03-09T04:13:11.803771</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125711</t>
+          <t>2026-03-09T04:13:11.803774</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125714</t>
+          <t>2026-03-09T04:13:11.803777</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125717</t>
+          <t>2026-03-09T04:13:11.803780</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125720</t>
+          <t>2026-03-09T04:13:11.803782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125722</t>
+          <t>2026-03-09T04:13:11.803785</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125725</t>
+          <t>2026-03-09T04:13:11.803788</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125728</t>
+          <t>2026-03-09T04:13:11.803791</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125731</t>
+          <t>2026-03-09T04:13:11.803793</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125734</t>
+          <t>2026-03-09T04:13:11.803810</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1297.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1297</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125737</t>
+          <t>2026-03-09T04:13:11.803814</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1299.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1299</v>
+        <v>1367</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:52.125740</t>
+          <t>2026-03-09T04:13:11.803817</t>
         </is>
       </c>
     </row>
@@ -8635,14 +8635,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1383.888888888889</v>
+        <v>1390.333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1593.98</v>
+        <v>1594.04</v>
       </c>
     </row>
     <row r="4">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1383.888888888889</v>
+        <v>1390.333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124860</t>
+          <t>2026-03-10T04:05:19.857120</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124875</t>
+          <t>2026-03-10T04:05:19.857134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124879</t>
+          <t>2026-03-10T04:05:19.857138</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124882</t>
+          <t>2026-03-10T04:05:19.857142</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124885</t>
+          <t>2026-03-10T04:05:19.857145</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124889</t>
+          <t>2026-03-10T04:05:19.857148</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124892</t>
+          <t>2026-03-10T04:05:19.857151</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124899</t>
+          <t>2026-03-10T04:05:19.857158</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124902</t>
+          <t>2026-03-10T04:05:19.857161</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124905</t>
+          <t>2026-03-10T04:05:19.857164</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124908</t>
+          <t>2026-03-10T04:05:19.857167</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124911</t>
+          <t>2026-03-10T04:05:19.857170</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124914</t>
+          <t>2026-03-10T04:05:19.857173</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124917</t>
+          <t>2026-03-10T04:05:19.857176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124919</t>
+          <t>2026-03-10T04:05:19.857179</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124922</t>
+          <t>2026-03-10T04:05:19.857181</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124925</t>
+          <t>2026-03-10T04:05:19.857184</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124930</t>
+          <t>2026-03-10T04:05:19.857189</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124933</t>
+          <t>2026-03-10T04:05:19.857192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124935</t>
+          <t>2026-03-10T04:05:19.857195</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124938</t>
+          <t>2026-03-10T04:05:19.857197</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124941</t>
+          <t>2026-03-10T04:05:19.857200</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124944</t>
+          <t>2026-03-10T04:05:19.857203</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124946</t>
+          <t>2026-03-10T04:05:19.857206</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124949</t>
+          <t>2026-03-10T04:05:19.857208</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124952</t>
+          <t>2026-03-10T04:05:19.857211</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124955</t>
+          <t>2026-03-10T04:05:19.857214</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124960</t>
+          <t>2026-03-10T04:05:19.857219</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124962</t>
+          <t>2026-03-10T04:05:19.857222</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124965</t>
+          <t>2026-03-10T04:05:19.857224</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124968</t>
+          <t>2026-03-10T04:05:19.857227</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124971</t>
+          <t>2026-03-10T04:05:19.857230</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124973</t>
+          <t>2026-03-10T04:05:19.857233</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124976</t>
+          <t>2026-03-10T04:05:19.857235</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124979</t>
+          <t>2026-03-10T04:05:19.857238</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:10.124982</t>
+          <t>2026-03-10T04:05:19.857241</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2925,11 +2925,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031932</t>
+          <t>2026-03-10T04:05:20.818878</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031945</t>
+          <t>2026-03-10T04:05:20.818892</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3055,11 +3055,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031949</t>
+          <t>2026-03-10T04:05:20.818896</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031952</t>
+          <t>2026-03-10T04:05:20.818899</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031955</t>
+          <t>2026-03-10T04:05:20.818902</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031958</t>
+          <t>2026-03-10T04:05:20.818905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031961</t>
+          <t>2026-03-10T04:05:20.818908</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031963</t>
+          <t>2026-03-10T04:05:20.818911</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031969</t>
+          <t>2026-03-10T04:05:20.818917</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031972</t>
+          <t>2026-03-10T04:05:20.818920</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031975</t>
+          <t>2026-03-10T04:05:20.818922</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031977</t>
+          <t>2026-03-10T04:05:20.818925</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031980</t>
+          <t>2026-03-10T04:05:20.818928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031983</t>
+          <t>2026-03-10T04:05:20.818931</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031986</t>
+          <t>2026-03-10T04:05:20.818933</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031988</t>
+          <t>2026-03-10T04:05:20.818936</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031991</t>
+          <t>2026-03-10T04:05:20.818939</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031997</t>
+          <t>2026-03-10T04:05:20.818942</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032008</t>
+          <t>2026-03-10T04:05:20.818947</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032011</t>
+          <t>2026-03-10T04:05:20.818950</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032013</t>
+          <t>2026-03-10T04:05:20.818952</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032016</t>
+          <t>2026-03-10T04:05:20.818956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032019</t>
+          <t>2026-03-10T04:05:20.818959</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032022</t>
+          <t>2026-03-10T04:05:20.818961</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032025</t>
+          <t>2026-03-10T04:05:20.818964</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032028</t>
+          <t>2026-03-10T04:05:20.818967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032030</t>
+          <t>2026-03-10T04:05:20.818970</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032033</t>
+          <t>2026-03-10T04:05:20.818973</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032036</t>
+          <t>2026-03-10T04:05:20.818976</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032039</t>
+          <t>2026-03-10T04:05:20.818979</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032042</t>
+          <t>2026-03-10T04:05:20.818982</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032044</t>
+          <t>2026-03-10T04:05:20.818984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032047</t>
+          <t>2026-03-10T04:05:20.818987</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032050</t>
+          <t>2026-03-10T04:05:20.818990</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032052</t>
+          <t>2026-03-10T04:05:20.818993</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032055</t>
+          <t>2026-03-10T04:05:20.818995</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032058</t>
+          <t>2026-03-10T04:05:20.818998</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032060</t>
+          <t>2026-03-10T04:05:20.819001</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032063</t>
+          <t>2026-03-10T04:05:20.819003</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032066</t>
+          <t>2026-03-10T04:05:20.819006</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032068</t>
+          <t>2026-03-10T04:05:20.819009</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032071</t>
+          <t>2026-03-10T04:05:20.819012</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032074</t>
+          <t>2026-03-10T04:05:20.819015</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032077</t>
+          <t>2026-03-10T04:05:20.819017</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032079</t>
+          <t>2026-03-10T04:05:20.819020</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032082</t>
+          <t>2026-03-10T04:05:20.819023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032085</t>
+          <t>2026-03-10T04:05:20.819027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032087</t>
+          <t>2026-03-10T04:05:20.819030</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032090</t>
+          <t>2026-03-10T04:05:20.819033</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032093</t>
+          <t>2026-03-10T04:05:20.819036</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6256,11 +6256,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6299,14 +6299,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803683</t>
+          <t>2026-03-10T04:05:21.738186</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803697</t>
+          <t>2026-03-10T04:05:21.738200</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803701</t>
+          <t>2026-03-10T04:05:21.738204</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6494,14 +6494,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803704</t>
+          <t>2026-03-10T04:05:21.738207</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6516,11 +6516,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6559,14 +6559,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803707</t>
+          <t>2026-03-10T04:05:21.738210</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6624,14 +6624,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803710</t>
+          <t>2026-03-10T04:05:21.738213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803713</t>
+          <t>2026-03-10T04:05:21.738216</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803716</t>
+          <t>2026-03-10T04:05:21.738218</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803718</t>
+          <t>2026-03-10T04:05:21.738222</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803722</t>
+          <t>2026-03-10T04:05:21.738224</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803724</t>
+          <t>2026-03-10T04:05:21.738227</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803727</t>
+          <t>2026-03-10T04:05:21.738230</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803730</t>
+          <t>2026-03-10T04:05:21.738233</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803737</t>
+          <t>2026-03-10T04:05:21.738235</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803740</t>
+          <t>2026-03-10T04:05:21.738238</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803744</t>
+          <t>2026-03-10T04:05:21.738241</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803746</t>
+          <t>2026-03-10T04:05:21.738243</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803749</t>
+          <t>2026-03-10T04:05:21.738246</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803753</t>
+          <t>2026-03-10T04:05:21.738250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803757</t>
+          <t>2026-03-10T04:05:21.738253</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803760</t>
+          <t>2026-03-10T04:05:21.738259</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803763</t>
+          <t>2026-03-10T04:05:21.738266</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803765</t>
+          <t>2026-03-10T04:05:21.738273</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803768</t>
+          <t>2026-03-10T04:05:21.738280</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803771</t>
+          <t>2026-03-10T04:05:21.738285</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803774</t>
+          <t>2026-03-10T04:05:21.738291</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803777</t>
+          <t>2026-03-10T04:05:21.738296</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803780</t>
+          <t>2026-03-10T04:05:21.738302</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803782</t>
+          <t>2026-03-10T04:05:21.738309</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803785</t>
+          <t>2026-03-10T04:05:21.738315</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803788</t>
+          <t>2026-03-10T04:05:21.738318</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803791</t>
+          <t>2026-03-10T04:05:21.738321</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803793</t>
+          <t>2026-03-10T04:05:21.738324</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803810</t>
+          <t>2026-03-10T04:05:21.738326</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803814</t>
+          <t>2026-03-10T04:05:21.738330</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.803817</t>
+          <t>2026-03-10T04:05:21.738333</t>
         </is>
       </c>
     </row>
@@ -8635,14 +8635,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1390.333333333333</v>
+        <v>1392.25</v>
       </c>
     </row>
     <row r="3">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1594.04</v>
+        <v>1593.02</v>
       </c>
     </row>
     <row r="4">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1390.333333333333</v>
+        <v>1392.25</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857120</t>
+          <t>2026-03-11T04:06:20.499363</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857134</t>
+          <t>2026-03-11T04:06:20.499377</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857138</t>
+          <t>2026-03-11T04:06:20.499382</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857142</t>
+          <t>2026-03-11T04:06:20.499385</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857145</t>
+          <t>2026-03-11T04:06:20.499388</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857148</t>
+          <t>2026-03-11T04:06:20.499391</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857151</t>
+          <t>2026-03-11T04:06:20.499394</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857158</t>
+          <t>2026-03-11T04:06:20.499401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857161</t>
+          <t>2026-03-11T04:06:20.499405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857164</t>
+          <t>2026-03-11T04:06:20.499408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857167</t>
+          <t>2026-03-11T04:06:20.499410</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857170</t>
+          <t>2026-03-11T04:06:20.499413</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857173</t>
+          <t>2026-03-11T04:06:20.499416</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857176</t>
+          <t>2026-03-11T04:06:20.499419</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857179</t>
+          <t>2026-03-11T04:06:20.499422</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857181</t>
+          <t>2026-03-11T04:06:20.499425</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857184</t>
+          <t>2026-03-11T04:06:20.499427</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857189</t>
+          <t>2026-03-11T04:06:20.499433</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857192</t>
+          <t>2026-03-11T04:06:20.499435</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857195</t>
+          <t>2026-03-11T04:06:20.499438</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857197</t>
+          <t>2026-03-11T04:06:20.499441</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857200</t>
+          <t>2026-03-11T04:06:20.499444</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857203</t>
+          <t>2026-03-11T04:06:20.499446</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857206</t>
+          <t>2026-03-11T04:06:20.499449</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857208</t>
+          <t>2026-03-11T04:06:20.499452</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857211</t>
+          <t>2026-03-11T04:06:20.499455</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857214</t>
+          <t>2026-03-11T04:06:20.499458</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857219</t>
+          <t>2026-03-11T04:06:20.499462</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857222</t>
+          <t>2026-03-11T04:06:20.499465</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857224</t>
+          <t>2026-03-11T04:06:20.499468</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857227</t>
+          <t>2026-03-11T04:06:20.499470</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857230</t>
+          <t>2026-03-11T04:06:20.499473</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857233</t>
+          <t>2026-03-11T04:06:20.499476</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857235</t>
+          <t>2026-03-11T04:06:20.499479</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857238</t>
+          <t>2026-03-11T04:06:20.499481</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:19.857241</t>
+          <t>2026-03-11T04:06:20.499484</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2925,11 +2925,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2968,14 +2968,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818878</t>
+          <t>2026-03-11T04:06:21.483686</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818892</t>
+          <t>2026-03-11T04:06:21.483706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3055,11 +3055,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3098,14 +3098,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818896</t>
+          <t>2026-03-11T04:06:21.483710</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3163,14 +3163,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818899</t>
+          <t>2026-03-11T04:06:21.483713</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3228,14 +3228,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818902</t>
+          <t>2026-03-11T04:06:21.483716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818905</t>
+          <t>2026-03-11T04:06:21.483719</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818908</t>
+          <t>2026-03-11T04:06:21.483722</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818911</t>
+          <t>2026-03-11T04:06:21.483725</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818917</t>
+          <t>2026-03-11T04:06:21.483731</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818920</t>
+          <t>2026-03-11T04:06:21.483734</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818922</t>
+          <t>2026-03-11T04:06:21.483737</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818925</t>
+          <t>2026-03-11T04:06:21.483739</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818928</t>
+          <t>2026-03-11T04:06:21.483742</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818931</t>
+          <t>2026-03-11T04:06:21.483745</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818933</t>
+          <t>2026-03-11T04:06:21.483748</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818936</t>
+          <t>2026-03-11T04:06:21.483750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818939</t>
+          <t>2026-03-11T04:06:21.483753</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818942</t>
+          <t>2026-03-11T04:06:21.483756</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818947</t>
+          <t>2026-03-11T04:06:21.483761</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818950</t>
+          <t>2026-03-11T04:06:21.483764</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818952</t>
+          <t>2026-03-11T04:06:21.483767</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818956</t>
+          <t>2026-03-11T04:06:21.483770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818959</t>
+          <t>2026-03-11T04:06:21.483773</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818961</t>
+          <t>2026-03-11T04:06:21.483776</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818964</t>
+          <t>2026-03-11T04:06:21.483779</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818967</t>
+          <t>2026-03-11T04:06:21.483781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818970</t>
+          <t>2026-03-11T04:06:21.483784</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818973</t>
+          <t>2026-03-11T04:06:21.483787</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818976</t>
+          <t>2026-03-11T04:06:21.483790</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818979</t>
+          <t>2026-03-11T04:06:21.483793</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818982</t>
+          <t>2026-03-11T04:06:21.483796</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818984</t>
+          <t>2026-03-11T04:06:21.483799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818987</t>
+          <t>2026-03-11T04:06:21.483801</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818990</t>
+          <t>2026-03-11T04:06:21.483804</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818993</t>
+          <t>2026-03-11T04:06:21.483807</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818995</t>
+          <t>2026-03-11T04:06:21.483810</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818998</t>
+          <t>2026-03-11T04:06:21.483813</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819001</t>
+          <t>2026-03-11T04:06:21.483815</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819003</t>
+          <t>2026-03-11T04:06:21.483818</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819006</t>
+          <t>2026-03-11T04:06:21.483821</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819009</t>
+          <t>2026-03-11T04:06:21.483824</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819012</t>
+          <t>2026-03-11T04:06:21.483827</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819015</t>
+          <t>2026-03-11T04:06:21.483830</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819017</t>
+          <t>2026-03-11T04:06:21.483833</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819020</t>
+          <t>2026-03-11T04:06:21.483835</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819023</t>
+          <t>2026-03-11T04:06:21.483838</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819027</t>
+          <t>2026-03-11T04:06:21.483841</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819030</t>
+          <t>2026-03-11T04:06:21.483843</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819033</t>
+          <t>2026-03-11T04:06:21.483846</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819036</t>
+          <t>2026-03-11T04:06:21.483849</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6256,11 +6256,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6299,14 +6299,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738186</t>
+          <t>2026-03-11T04:06:22.487669</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6364,14 +6364,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738200</t>
+          <t>2026-03-11T04:06:22.487682</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6429,14 +6429,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738204</t>
+          <t>2026-03-11T04:06:22.487686</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6494,14 +6494,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738207</t>
+          <t>2026-03-11T04:06:22.487689</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6516,11 +6516,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6559,14 +6559,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738210</t>
+          <t>2026-03-11T04:06:22.487692</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738213</t>
+          <t>2026-03-11T04:06:22.487695</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738216</t>
+          <t>2026-03-11T04:06:22.487698</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738218</t>
+          <t>2026-03-11T04:06:22.487701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738222</t>
+          <t>2026-03-11T04:06:22.487704</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738224</t>
+          <t>2026-03-11T04:06:22.487707</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738227</t>
+          <t>2026-03-11T04:06:22.487709</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738230</t>
+          <t>2026-03-11T04:06:22.487712</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738233</t>
+          <t>2026-03-11T04:06:22.487715</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738235</t>
+          <t>2026-03-11T04:06:22.487718</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738238</t>
+          <t>2026-03-11T04:06:22.487720</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738241</t>
+          <t>2026-03-11T04:06:22.487723</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738243</t>
+          <t>2026-03-11T04:06:22.487726</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738246</t>
+          <t>2026-03-11T04:06:22.487729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738250</t>
+          <t>2026-03-11T04:06:22.487733</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738253</t>
+          <t>2026-03-11T04:06:22.487736</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738259</t>
+          <t>2026-03-11T04:06:22.487739</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738266</t>
+          <t>2026-03-11T04:06:22.487741</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738273</t>
+          <t>2026-03-11T04:06:22.487744</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738280</t>
+          <t>2026-03-11T04:06:22.487747</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738285</t>
+          <t>2026-03-11T04:06:22.487750</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738291</t>
+          <t>2026-03-11T04:06:22.487752</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738296</t>
+          <t>2026-03-11T04:06:22.487755</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738302</t>
+          <t>2026-03-11T04:06:22.487758</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738309</t>
+          <t>2026-03-11T04:06:22.487761</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738315</t>
+          <t>2026-03-11T04:06:22.487764</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738318</t>
+          <t>2026-03-11T04:06:22.487766</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8271,11 +8271,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738321</t>
+          <t>2026-03-11T04:06:22.487769</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738324</t>
+          <t>2026-03-11T04:06:22.487772</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738326</t>
+          <t>2026-03-11T04:06:22.487775</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738330</t>
+          <t>2026-03-11T04:06:22.487778</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:21.738333</t>
+          <t>2026-03-11T04:06:22.487781</t>
         </is>
       </c>
     </row>
@@ -8635,14 +8635,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1392.25</v>
+        <v>1395.222222222222</v>
       </c>
     </row>
     <row r="3">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1593.02</v>
+        <v>1590.38</v>
       </c>
     </row>
     <row r="4">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1392.25</v>
+        <v>1395.222222222222</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499363</t>
+          <t>2026-03-12T04:10:06.569143</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499377</t>
+          <t>2026-03-12T04:10:06.569164</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499382</t>
+          <t>2026-03-12T04:10:06.569170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499385</t>
+          <t>2026-03-12T04:10:06.569173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499388</t>
+          <t>2026-03-12T04:10:06.569176</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499391</t>
+          <t>2026-03-12T04:10:06.569180</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499394</t>
+          <t>2026-03-12T04:10:06.569183</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499401</t>
+          <t>2026-03-12T04:10:06.569190</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499405</t>
+          <t>2026-03-12T04:10:06.569193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499408</t>
+          <t>2026-03-12T04:10:06.569196</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499410</t>
+          <t>2026-03-12T04:10:06.569199</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499413</t>
+          <t>2026-03-12T04:10:06.569202</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499416</t>
+          <t>2026-03-12T04:10:06.569205</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499419</t>
+          <t>2026-03-12T04:10:06.569208</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499422</t>
+          <t>2026-03-12T04:10:06.569211</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499425</t>
+          <t>2026-03-12T04:10:06.569213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499427</t>
+          <t>2026-03-12T04:10:06.569216</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499433</t>
+          <t>2026-03-12T04:10:06.569221</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499435</t>
+          <t>2026-03-12T04:10:06.569224</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499438</t>
+          <t>2026-03-12T04:10:06.569227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499441</t>
+          <t>2026-03-12T04:10:06.569230</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499444</t>
+          <t>2026-03-12T04:10:06.569232</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499446</t>
+          <t>2026-03-12T04:10:06.569235</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499449</t>
+          <t>2026-03-12T04:10:06.569238</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499452</t>
+          <t>2026-03-12T04:10:06.569240</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499455</t>
+          <t>2026-03-12T04:10:06.569243</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499458</t>
+          <t>2026-03-12T04:10:06.569246</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499462</t>
+          <t>2026-03-12T04:10:06.569253</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499465</t>
+          <t>2026-03-12T04:10:06.569257</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499468</t>
+          <t>2026-03-12T04:10:06.569260</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499470</t>
+          <t>2026-03-12T04:10:06.569264</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499473</t>
+          <t>2026-03-12T04:10:06.569267</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499476</t>
+          <t>2026-03-12T04:10:06.569270</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499479</t>
+          <t>2026-03-12T04:10:06.569272</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499481</t>
+          <t>2026-03-12T04:10:06.569275</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:20.499484</t>
+          <t>2026-03-12T04:10:06.569278</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2925,11 +2925,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483686</t>
+          <t>2026-03-12T04:10:07.487021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483706</t>
+          <t>2026-03-12T04:10:07.487033</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3055,11 +3055,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3098,14 +3098,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483710</t>
+          <t>2026-03-12T04:10:07.487036</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3163,14 +3163,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483713</t>
+          <t>2026-03-12T04:10:07.487040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3228,14 +3228,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483716</t>
+          <t>2026-03-12T04:10:07.487043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3293,14 +3293,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483719</t>
+          <t>2026-03-12T04:10:07.487046</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483722</t>
+          <t>2026-03-12T04:10:07.487049</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483725</t>
+          <t>2026-03-12T04:10:07.487052</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483731</t>
+          <t>2026-03-12T04:10:07.487077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483734</t>
+          <t>2026-03-12T04:10:07.487080</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483737</t>
+          <t>2026-03-12T04:10:07.487083</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483739</t>
+          <t>2026-03-12T04:10:07.487086</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483742</t>
+          <t>2026-03-12T04:10:07.487089</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483745</t>
+          <t>2026-03-12T04:10:07.487091</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483748</t>
+          <t>2026-03-12T04:10:07.487094</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483750</t>
+          <t>2026-03-12T04:10:07.487097</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483753</t>
+          <t>2026-03-12T04:10:07.487100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483756</t>
+          <t>2026-03-12T04:10:07.487103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483761</t>
+          <t>2026-03-12T04:10:07.487108</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483764</t>
+          <t>2026-03-12T04:10:07.487110</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483767</t>
+          <t>2026-03-12T04:10:07.487113</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483770</t>
+          <t>2026-03-12T04:10:07.487116</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483773</t>
+          <t>2026-03-12T04:10:07.487119</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483776</t>
+          <t>2026-03-12T04:10:07.487122</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483779</t>
+          <t>2026-03-12T04:10:07.487125</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483781</t>
+          <t>2026-03-12T04:10:07.487127</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483784</t>
+          <t>2026-03-12T04:10:07.487130</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483787</t>
+          <t>2026-03-12T04:10:07.487133</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483790</t>
+          <t>2026-03-12T04:10:07.487137</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483793</t>
+          <t>2026-03-12T04:10:07.487140</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483796</t>
+          <t>2026-03-12T04:10:07.487143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483799</t>
+          <t>2026-03-12T04:10:07.487146</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483801</t>
+          <t>2026-03-12T04:10:07.487148</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483804</t>
+          <t>2026-03-12T04:10:07.487151</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483807</t>
+          <t>2026-03-12T04:10:07.487154</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483810</t>
+          <t>2026-03-12T04:10:07.487156</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483813</t>
+          <t>2026-03-12T04:10:07.487159</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483815</t>
+          <t>2026-03-12T04:10:07.487162</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483818</t>
+          <t>2026-03-12T04:10:07.487165</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483821</t>
+          <t>2026-03-12T04:10:07.487167</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483824</t>
+          <t>2026-03-12T04:10:07.487170</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483827</t>
+          <t>2026-03-12T04:10:07.487173</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483830</t>
+          <t>2026-03-12T04:10:07.487175</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483833</t>
+          <t>2026-03-12T04:10:07.487178</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483835</t>
+          <t>2026-03-12T04:10:07.487181</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483838</t>
+          <t>2026-03-12T04:10:07.487183</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483841</t>
+          <t>2026-03-12T04:10:07.487186</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483843</t>
+          <t>2026-03-12T04:10:07.487189</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483846</t>
+          <t>2026-03-12T04:10:07.487192</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483849</t>
+          <t>2026-03-12T04:10:07.487195</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6256,11 +6256,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6299,14 +6299,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487669</t>
+          <t>2026-03-12T04:10:08.099875</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6321,11 +6321,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6364,14 +6364,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487682</t>
+          <t>2026-03-12T04:10:08.099885</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,11 +6386,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6429,14 +6429,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487686</t>
+          <t>2026-03-12T04:10:08.099889</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6494,14 +6494,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487689</t>
+          <t>2026-03-12T04:10:08.099892</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6516,11 +6516,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6559,14 +6559,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487692</t>
+          <t>2026-03-12T04:10:08.099895</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6624,14 +6624,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487695</t>
+          <t>2026-03-12T04:10:08.099898</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6646,11 +6646,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -6689,14 +6689,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487698</t>
+          <t>2026-03-12T04:10:08.099901</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6711,11 +6711,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6754,14 +6754,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487701</t>
+          <t>2026-03-12T04:10:08.099904</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -6819,14 +6819,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487704</t>
+          <t>2026-03-12T04:10:08.099907</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6841,11 +6841,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6884,14 +6884,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487707</t>
+          <t>2026-03-12T04:10:08.099910</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6906,11 +6906,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6949,14 +6949,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487709</t>
+          <t>2026-03-12T04:10:08.099912</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6971,11 +6971,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487712</t>
+          <t>2026-03-12T04:10:08.099915</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7036,11 +7036,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7079,14 +7079,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487715</t>
+          <t>2026-03-12T04:10:08.099918</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7101,11 +7101,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487718</t>
+          <t>2026-03-12T04:10:08.099921</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487720</t>
+          <t>2026-03-12T04:10:08.099923</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7274,14 +7274,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487723</t>
+          <t>2026-03-12T04:10:08.099926</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487726</t>
+          <t>2026-03-12T04:10:08.099929</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487729</t>
+          <t>2026-03-12T04:10:08.099932</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7469,14 +7469,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487733</t>
+          <t>2026-03-12T04:10:08.099935</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487736</t>
+          <t>2026-03-12T04:10:08.099938</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487739</t>
+          <t>2026-03-12T04:10:08.099941</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7664,14 +7664,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487741</t>
+          <t>2026-03-12T04:10:08.099944</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487744</t>
+          <t>2026-03-12T04:10:08.099947</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7794,14 +7794,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487747</t>
+          <t>2026-03-12T04:10:08.099949</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487750</t>
+          <t>2026-03-12T04:10:08.099952</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487752</t>
+          <t>2026-03-12T04:10:08.099955</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487755</t>
+          <t>2026-03-12T04:10:08.099958</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487758</t>
+          <t>2026-03-12T04:10:08.099960</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8119,14 +8119,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487761</t>
+          <t>2026-03-12T04:10:08.099963</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8184,14 +8184,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487764</t>
+          <t>2026-03-12T04:10:08.099966</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487766</t>
+          <t>2026-03-12T04:10:08.099969</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8271,11 +8271,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8314,14 +8314,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487769</t>
+          <t>2026-03-12T04:10:08.099971</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8379,14 +8379,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487772</t>
+          <t>2026-03-12T04:10:08.099974</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1365</v>
+        <v>1378</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8444,14 +8444,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487775</t>
+          <t>2026-03-12T04:10:08.099977</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1377.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1377</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487778</t>
+          <t>2026-03-12T04:10:08.099980</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1367</v>
+        <v>1380</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:22.487781</t>
+          <t>2026-03-12T04:10:08.099983</t>
         </is>
       </c>
     </row>
@@ -8635,14 +8635,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1395.222222222222</v>
+        <v>1397.083333333333</v>
       </c>
     </row>
     <row r="3">
@@ -8661,14 +8661,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1590.38</v>
+        <v>1584.1</v>
       </c>
     </row>
     <row r="4">
@@ -8687,14 +8687,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1395.222222222222</v>
+        <v>1397.083333333333</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569143</t>
+          <t>2026-03-13T04:08:47.727099</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,14 +612,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569164</t>
+          <t>2026-03-13T04:08:47.727128</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569170</t>
+          <t>2026-03-13T04:08:47.727135</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569173</t>
+          <t>2026-03-13T04:08:47.727141</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569176</t>
+          <t>2026-03-13T04:08:47.727147</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569180</t>
+          <t>2026-03-13T04:08:47.727153</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569183</t>
+          <t>2026-03-13T04:08:47.727159</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569190</t>
+          <t>2026-03-13T04:08:47.727171</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569193</t>
+          <t>2026-03-13T04:08:47.727177</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569196</t>
+          <t>2026-03-13T04:08:47.727183</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569199</t>
+          <t>2026-03-13T04:08:47.727189</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569202</t>
+          <t>2026-03-13T04:08:47.727195</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569205</t>
+          <t>2026-03-13T04:08:47.727201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569208</t>
+          <t>2026-03-13T04:08:47.727206</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1457,19 +1457,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569211</t>
+          <t>2026-03-13T04:08:47.727212</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,19 +1522,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569213</t>
+          <t>2026-03-13T04:08:47.727217</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569216</t>
+          <t>2026-03-13T04:08:47.727223</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569221</t>
+          <t>2026-03-13T04:08:47.727231</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569224</t>
+          <t>2026-03-13T04:08:47.727237</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569227</t>
+          <t>2026-03-13T04:08:47.727243</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,19 +1847,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569230</t>
+          <t>2026-03-13T04:08:47.727248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569232</t>
+          <t>2026-03-13T04:08:47.727253</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,19 +1977,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569235</t>
+          <t>2026-03-13T04:08:47.727257</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569238</t>
+          <t>2026-03-13T04:08:47.727262</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,19 +2107,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569240</t>
+          <t>2026-03-13T04:08:47.727266</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569243</t>
+          <t>2026-03-13T04:08:47.727271</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569246</t>
+          <t>2026-03-13T04:08:47.727277</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569253</t>
+          <t>2026-03-13T04:08:47.727283</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569257</t>
+          <t>2026-03-13T04:08:47.727286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569260</t>
+          <t>2026-03-13T04:08:47.727289</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,19 +2497,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569264</t>
+          <t>2026-03-13T04:08:47.727292</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,19 +2562,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569267</t>
+          <t>2026-03-13T04:08:47.727294</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569270</t>
+          <t>2026-03-13T04:08:47.727297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,19 +2692,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569272</t>
+          <t>2026-03-13T04:08:47.727300</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,72 +2757,267 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:06.569275</t>
+          <t>2026-03-13T04:08:47.727303</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727306</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727308</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727311</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E40" t="n">
         <v>1380</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>首饰黄金</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>jewelry</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-12T04:10:06.569278</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:47.727315</t>
         </is>
       </c>
     </row>
@@ -2910,7 +3105,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2925,11 +3120,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2968,14 +3163,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487021</t>
+          <t>2026-03-13T04:08:49.151563</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2990,11 +3185,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3013,7 +3208,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3033,14 +3228,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487033</t>
+          <t>2026-03-13T04:08:49.151583</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3055,11 +3250,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3098,14 +3293,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487036</t>
+          <t>2026-03-13T04:08:49.151586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3120,11 +3315,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3163,14 +3358,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487040</t>
+          <t>2026-03-13T04:08:49.151589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3185,11 +3380,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3228,14 +3423,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487043</t>
+          <t>2026-03-13T04:08:49.151593</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3250,11 +3445,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3293,14 +3488,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487046</t>
+          <t>2026-03-13T04:08:49.151598</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3315,11 +3510,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3338,7 +3533,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3358,14 +3553,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487049</t>
+          <t>2026-03-13T04:08:49.151601</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3380,11 +3575,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3403,7 +3598,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3423,14 +3618,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487052</t>
+          <t>2026-03-13T04:08:49.151604</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3445,11 +3640,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3468,7 +3663,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3488,14 +3683,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487077</t>
+          <t>2026-03-13T04:08:49.151607</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3510,11 +3705,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3533,7 +3728,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3553,14 +3748,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487080</t>
+          <t>2026-03-13T04:08:49.151610</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3618,14 +3813,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487083</t>
+          <t>2026-03-13T04:08:49.151613</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3640,11 +3835,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3663,7 +3858,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3683,14 +3878,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487086</t>
+          <t>2026-03-13T04:08:49.151616</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3705,11 +3900,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3748,14 +3943,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487089</t>
+          <t>2026-03-13T04:08:49.151619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3770,11 +3965,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3813,14 +4008,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487091</t>
+          <t>2026-03-13T04:08:49.151622</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3878,14 +4073,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487094</t>
+          <t>2026-03-13T04:08:49.151624</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3900,11 +4095,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3943,14 +4138,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487097</t>
+          <t>2026-03-13T04:08:49.151629</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3965,11 +4160,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4008,14 +4203,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487100</t>
+          <t>2026-03-13T04:08:49.151632</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4030,11 +4225,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4073,14 +4268,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487103</t>
+          <t>2026-03-13T04:08:49.151635</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4118,7 +4313,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4138,14 +4333,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487108</t>
+          <t>2026-03-13T04:08:49.151638</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4160,11 +4355,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4183,7 +4378,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4203,14 +4398,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487110</t>
+          <t>2026-03-13T04:08:49.151642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4225,11 +4420,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4248,7 +4443,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4268,14 +4463,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487113</t>
+          <t>2026-03-13T04:08:49.151644</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4290,11 +4485,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4313,7 +4508,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4333,14 +4528,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487116</t>
+          <t>2026-03-13T04:08:49.151647</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4355,11 +4550,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4378,7 +4573,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4398,14 +4593,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487119</t>
+          <t>2026-03-13T04:08:49.151650</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4420,11 +4615,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4443,7 +4638,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4463,14 +4658,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487122</t>
+          <t>2026-03-13T04:08:49.151653</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4485,11 +4680,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4508,7 +4703,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4528,14 +4723,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487125</t>
+          <t>2026-03-13T04:08:49.151656</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4550,11 +4745,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4573,7 +4768,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4593,14 +4788,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487127</t>
+          <t>2026-03-13T04:08:49.151659</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4615,11 +4810,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4638,7 +4833,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4658,14 +4853,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487130</t>
+          <t>2026-03-13T04:08:49.151662</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4680,11 +4875,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4703,7 +4898,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4723,14 +4918,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487133</t>
+          <t>2026-03-13T04:08:49.151665</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4745,11 +4940,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4768,7 +4963,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4788,14 +4983,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487137</t>
+          <t>2026-03-13T04:08:49.151667</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4810,11 +5005,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4833,7 +5028,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4853,14 +5048,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487140</t>
+          <t>2026-03-13T04:08:49.151670</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4875,11 +5070,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4898,7 +5093,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4918,14 +5113,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487143</t>
+          <t>2026-03-13T04:08:49.151673</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4940,11 +5135,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +5158,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4983,14 +5178,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487146</t>
+          <t>2026-03-13T04:08:49.151676</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5005,11 +5200,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5028,7 +5223,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5048,14 +5243,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487148</t>
+          <t>2026-03-13T04:08:49.151678</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5070,11 +5265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5093,7 +5288,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5113,14 +5308,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487151</t>
+          <t>2026-03-13T04:08:49.151681</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5135,11 +5330,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5158,7 +5353,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5178,14 +5373,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487154</t>
+          <t>2026-03-13T04:08:49.151684</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5223,7 +5418,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5243,14 +5438,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487156</t>
+          <t>2026-03-13T04:08:49.151687</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5265,11 +5460,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5308,14 +5503,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487159</t>
+          <t>2026-03-13T04:08:49.151689</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5330,11 +5525,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5353,7 +5548,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5373,14 +5568,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487162</t>
+          <t>2026-03-13T04:08:49.151692</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5395,11 +5590,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5418,7 +5613,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5438,14 +5633,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487165</t>
+          <t>2026-03-13T04:08:49.151695</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5460,11 +5655,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5483,7 +5678,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5503,14 +5698,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487167</t>
+          <t>2026-03-13T04:08:49.151698</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5525,11 +5720,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5743,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5568,14 +5763,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487170</t>
+          <t>2026-03-13T04:08:49.151701</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5590,11 +5785,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5613,7 +5808,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5633,14 +5828,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487173</t>
+          <t>2026-03-13T04:08:49.151704</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5678,7 +5873,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5698,14 +5893,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487175</t>
+          <t>2026-03-13T04:08:49.151707</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5743,7 +5938,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5763,14 +5958,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487178</t>
+          <t>2026-03-13T04:08:49.151710</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5808,7 +6003,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5828,14 +6023,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487181</t>
+          <t>2026-03-13T04:08:49.151712</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5873,7 +6068,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5893,14 +6088,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487183</t>
+          <t>2026-03-13T04:08:49.151716</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5938,7 +6133,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5958,14 +6153,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487186</t>
+          <t>2026-03-13T04:08:49.151718</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5980,11 +6175,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,14 +6218,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487189</t>
+          <t>2026-03-13T04:08:49.151721</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6045,11 +6240,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6068,7 +6263,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6088,14 +6283,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487192</t>
+          <t>2026-03-13T04:08:49.151724</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6110,11 +6305,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6133,7 +6328,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6153,7 +6348,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487195</t>
+          <t>2026-03-13T04:08:49.151727</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6241,7 +6436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6256,11 +6451,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6299,14 +6494,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099875</t>
+          <t>2026-03-13T04:08:49.903178</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6321,11 +6516,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6364,14 +6559,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099885</t>
+          <t>2026-03-13T04:08:49.903197</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6386,11 +6581,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6429,14 +6624,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099889</t>
+          <t>2026-03-13T04:08:49.903201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6451,11 +6646,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6474,7 +6669,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6494,14 +6689,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099892</t>
+          <t>2026-03-13T04:08:49.903204</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6516,11 +6711,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6539,7 +6734,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6559,14 +6754,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099895</t>
+          <t>2026-03-13T04:08:49.903207</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6581,11 +6776,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6604,7 +6799,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -6624,14 +6819,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099898</t>
+          <t>2026-03-13T04:08:49.903211</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6646,11 +6841,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6689,14 +6884,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099901</t>
+          <t>2026-03-13T04:08:49.903214</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6711,11 +6906,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6754,14 +6949,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099904</t>
+          <t>2026-03-13T04:08:49.903217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6776,11 +6971,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6819,14 +7014,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099907</t>
+          <t>2026-03-13T04:08:49.903220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6841,11 +7036,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6864,7 +7059,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6884,14 +7079,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099910</t>
+          <t>2026-03-13T04:08:49.903223</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6906,11 +7101,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6929,7 +7124,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -6949,14 +7144,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099912</t>
+          <t>2026-03-13T04:08:49.903226</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6971,11 +7166,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6994,7 +7189,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7014,14 +7209,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099915</t>
+          <t>2026-03-13T04:08:49.903228</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7036,11 +7231,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7079,14 +7274,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099918</t>
+          <t>2026-03-13T04:08:49.903231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7101,11 +7296,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7144,14 +7339,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099921</t>
+          <t>2026-03-13T04:08:49.903234</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7166,11 +7361,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7209,19 +7404,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099923</t>
+          <t>2026-03-13T04:08:49.903237</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7231,11 +7426,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7254,7 +7449,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7274,19 +7469,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099926</t>
+          <t>2026-03-13T04:08:49.903241</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7296,11 +7491,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7319,7 +7514,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7339,19 +7534,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099929</t>
+          <t>2026-03-13T04:08:49.903244</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7361,11 +7556,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7384,7 +7579,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7404,19 +7599,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099932</t>
+          <t>2026-03-13T04:08:49.903247</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7426,11 +7621,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7449,7 +7644,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7469,19 +7664,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099935</t>
+          <t>2026-03-13T04:08:49.903250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7514,7 +7709,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7534,14 +7729,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099938</t>
+          <t>2026-03-13T04:08:49.903253</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7579,7 +7774,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7599,19 +7794,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099941</t>
+          <t>2026-03-13T04:08:49.903256</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7621,11 +7816,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7644,7 +7839,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7664,14 +7859,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099944</t>
+          <t>2026-03-13T04:08:49.903259</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7686,11 +7881,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7709,7 +7904,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7729,19 +7924,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099947</t>
+          <t>2026-03-13T04:08:49.903262</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7751,11 +7946,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -7774,7 +7969,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7794,19 +7989,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099949</t>
+          <t>2026-03-13T04:08:49.903265</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7816,11 +8011,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -7859,19 +8054,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099952</t>
+          <t>2026-03-13T04:08:49.903268</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7881,11 +8076,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -7924,14 +8119,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099955</t>
+          <t>2026-03-13T04:08:49.903271</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7946,11 +8141,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -7989,14 +8184,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099958</t>
+          <t>2026-03-13T04:08:49.903274</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8011,11 +8206,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8034,7 +8229,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8054,14 +8249,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099960</t>
+          <t>2026-03-13T04:08:49.903277</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8076,11 +8271,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1384</v>
+        <v>1429</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8099,7 +8294,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8119,14 +8314,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099963</t>
+          <t>2026-03-13T04:08:49.903280</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8141,11 +8336,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8164,7 +8359,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8184,14 +8379,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099966</t>
+          <t>2026-03-13T04:08:49.903283</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8229,7 +8424,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8249,19 +8444,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099969</t>
+          <t>2026-03-13T04:08:49.903285</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8271,11 +8466,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8294,7 +8489,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8314,19 +8509,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099971</t>
+          <t>2026-03-13T04:08:49.903289</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8336,11 +8531,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8359,7 +8554,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8379,19 +8574,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099974</t>
+          <t>2026-03-13T04:08:49.903292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8401,11 +8596,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8444,19 +8639,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099977</t>
+          <t>2026-03-13T04:08:49.903295</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8466,11 +8661,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8489,7 +8684,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8509,72 +8704,267 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:08.099980</t>
+          <t>2026-03-13T04:08:49.903317</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903321</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903324</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903327</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E40" t="n">
         <v>1380</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>金条</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>gold_bar</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-03-12T04:10:08.099983</t>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-03-13T04:08:49.903330</t>
         </is>
       </c>
     </row>
@@ -8631,18 +9021,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1397.083333333333</v>
+        <v>1395.974358974359</v>
       </c>
     </row>
     <row r="3">
@@ -8661,14 +9051,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1584.1</v>
+        <v>1579.14</v>
       </c>
     </row>
     <row r="4">
@@ -8683,18 +9073,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1397.083333333333</v>
+        <v>1395.974358974359</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727099</t>
+          <t>2026-03-14T04:07:11.012501</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727128</t>
+          <t>2026-03-14T04:07:11.012514</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727135</t>
+          <t>2026-03-14T04:07:11.012519</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727141</t>
+          <t>2026-03-14T04:07:11.012522</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727147</t>
+          <t>2026-03-14T04:07:11.012525</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727153</t>
+          <t>2026-03-14T04:07:11.012528</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727159</t>
+          <t>2026-03-14T04:07:11.012531</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727171</t>
+          <t>2026-03-14T04:07:11.012535</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727177</t>
+          <t>2026-03-14T04:07:11.012538</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727183</t>
+          <t>2026-03-14T04:07:11.012544</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727189</t>
+          <t>2026-03-14T04:07:11.012547</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727195</t>
+          <t>2026-03-14T04:07:11.012550</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727201</t>
+          <t>2026-03-14T04:07:11.012553</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727206</t>
+          <t>2026-03-14T04:07:11.012556</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727212</t>
+          <t>2026-03-14T04:07:11.012559</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727217</t>
+          <t>2026-03-14T04:07:11.012562</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727223</t>
+          <t>2026-03-14T04:07:11.012565</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727231</t>
+          <t>2026-03-14T04:07:11.012567</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727237</t>
+          <t>2026-03-14T04:07:11.012570</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727243</t>
+          <t>2026-03-14T04:07:11.012575</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727248</t>
+          <t>2026-03-14T04:07:11.012578</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727253</t>
+          <t>2026-03-14T04:07:11.012581</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727257</t>
+          <t>2026-03-14T04:07:11.012584</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727262</t>
+          <t>2026-03-14T04:07:11.012587</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727266</t>
+          <t>2026-03-14T04:07:11.012589</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727271</t>
+          <t>2026-03-14T04:07:11.012592</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727277</t>
+          <t>2026-03-14T04:07:11.012595</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727283</t>
+          <t>2026-03-14T04:07:11.012598</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727286</t>
+          <t>2026-03-14T04:07:11.012601</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727289</t>
+          <t>2026-03-14T04:07:11.012605</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727292</t>
+          <t>2026-03-14T04:07:11.012608</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727294</t>
+          <t>2026-03-14T04:07:11.012611</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727297</t>
+          <t>2026-03-14T04:07:11.012614</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727300</t>
+          <t>2026-03-14T04:07:11.012617</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727303</t>
+          <t>2026-03-14T04:07:11.012619</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727306</t>
+          <t>2026-03-14T04:07:11.012622</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727308</t>
+          <t>2026-03-14T04:07:11.012625</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727311</t>
+          <t>2026-03-14T04:07:11.012628</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:47.727315</t>
+          <t>2026-03-14T04:07:11.012630</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1572</v>
+        <v>1538</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151563</t>
+          <t>2026-03-14T04:07:12.077976</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1538</v>
+        <v>1570</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151583</t>
+          <t>2026-03-14T04:07:12.077990</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151586</t>
+          <t>2026-03-14T04:07:12.077994</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151589</t>
+          <t>2026-03-14T04:07:12.077997</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151593</t>
+          <t>2026-03-14T04:07:12.078000</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151598</t>
+          <t>2026-03-14T04:07:12.078003</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151601</t>
+          <t>2026-03-14T04:07:12.078006</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151604</t>
+          <t>2026-03-14T04:07:12.078012</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151607</t>
+          <t>2026-03-14T04:07:12.078016</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151610</t>
+          <t>2026-03-14T04:07:12.078019</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1548</v>
+        <v>1584</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151613</t>
+          <t>2026-03-14T04:07:12.078022</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151616</t>
+          <t>2026-03-14T04:07:12.078025</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151619</t>
+          <t>2026-03-14T04:07:12.078030</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151622</t>
+          <t>2026-03-14T04:07:12.078032</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1548</v>
+        <v>1600</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151624</t>
+          <t>2026-03-14T04:07:12.078035</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151629</t>
+          <t>2026-03-14T04:07:12.078038</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1593</v>
+        <v>1548</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151632</t>
+          <t>2026-03-14T04:07:12.078041</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151635</t>
+          <t>2026-03-14T04:07:12.078046</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1548</v>
+        <v>1580</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151638</t>
+          <t>2026-03-14T04:07:12.078049</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151642</t>
+          <t>2026-03-14T04:07:12.078052</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151644</t>
+          <t>2026-03-14T04:07:12.078055</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151647</t>
+          <t>2026-03-14T04:07:12.078058</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151650</t>
+          <t>2026-03-14T04:07:12.078061</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151653</t>
+          <t>2026-03-14T04:07:12.078063</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151656</t>
+          <t>2026-03-14T04:07:12.078066</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1548</v>
+        <v>1562</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151659</t>
+          <t>2026-03-14T04:07:12.078069</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151662</t>
+          <t>2026-03-14T04:07:12.078072</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151665</t>
+          <t>2026-03-14T04:07:12.078076</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151667</t>
+          <t>2026-03-14T04:07:12.078079</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1573</v>
+        <v>1548</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151670</t>
+          <t>2026-03-14T04:07:12.078082</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151673</t>
+          <t>2026-03-14T04:07:12.078086</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1583</v>
+        <v>1555</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151676</t>
+          <t>2026-03-14T04:07:12.078088</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151678</t>
+          <t>2026-03-14T04:07:12.078091</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151681</t>
+          <t>2026-03-14T04:07:12.078094</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151684</t>
+          <t>2026-03-14T04:07:12.078097</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151687</t>
+          <t>2026-03-14T04:07:12.078099</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151689</t>
+          <t>2026-03-14T04:07:12.078102</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1577</v>
+        <v>1555</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151692</t>
+          <t>2026-03-14T04:07:12.078105</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151695</t>
+          <t>2026-03-14T04:07:12.078108</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151698</t>
+          <t>2026-03-14T04:07:12.078111</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1577</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151701</t>
+          <t>2026-03-14T04:07:12.078113</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151704</t>
+          <t>2026-03-14T04:07:12.078119</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151707</t>
+          <t>2026-03-14T04:07:12.078121</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1565</v>
+        <v>1596</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151710</t>
+          <t>2026-03-14T04:07:12.078124</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151712</t>
+          <t>2026-03-14T04:07:12.078127</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151716</t>
+          <t>2026-03-14T04:07:12.078130</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151718</t>
+          <t>2026-03-14T04:07:12.078133</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151721</t>
+          <t>2026-03-14T04:07:12.078135</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151724</t>
+          <t>2026-03-14T04:07:12.078138</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151727</t>
+          <t>2026-03-14T04:07:12.078141</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903178</t>
+          <t>2026-03-14T04:07:13.062721</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903197</t>
+          <t>2026-03-14T04:07:13.062735</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903201</t>
+          <t>2026-03-14T04:07:13.062739</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903204</t>
+          <t>2026-03-14T04:07:13.062742</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903207</t>
+          <t>2026-03-14T04:07:13.062744</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903211</t>
+          <t>2026-03-14T04:07:13.062764</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903214</t>
+          <t>2026-03-14T04:07:13.062767</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903217</t>
+          <t>2026-03-14T04:07:13.062778</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903220</t>
+          <t>2026-03-14T04:07:13.062781</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903223</t>
+          <t>2026-03-14T04:07:13.062784</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903226</t>
+          <t>2026-03-14T04:07:13.062787</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903228</t>
+          <t>2026-03-14T04:07:13.062790</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903231</t>
+          <t>2026-03-14T04:07:13.062792</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903234</t>
+          <t>2026-03-14T04:07:13.062795</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903237</t>
+          <t>2026-03-14T04:07:13.062798</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903241</t>
+          <t>2026-03-14T04:07:13.062800</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903244</t>
+          <t>2026-03-14T04:07:13.062803</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903247</t>
+          <t>2026-03-14T04:07:13.062807</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903250</t>
+          <t>2026-03-14T04:07:13.062810</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903253</t>
+          <t>2026-03-14T04:07:13.062813</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903256</t>
+          <t>2026-03-14T04:07:13.062816</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903259</t>
+          <t>2026-03-14T04:07:13.062818</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903262</t>
+          <t>2026-03-14T04:07:13.062821</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903265</t>
+          <t>2026-03-14T04:07:13.062824</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903268</t>
+          <t>2026-03-14T04:07:13.062828</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903271</t>
+          <t>2026-03-14T04:07:13.062832</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903274</t>
+          <t>2026-03-14T04:07:13.062835</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903277</t>
+          <t>2026-03-14T04:07:13.062839</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903280</t>
+          <t>2026-03-14T04:07:13.062842</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903283</t>
+          <t>2026-03-14T04:07:13.062844</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903285</t>
+          <t>2026-03-14T04:07:13.062847</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903289</t>
+          <t>2026-03-14T04:07:13.062850</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903292</t>
+          <t>2026-03-14T04:07:13.062853</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903295</t>
+          <t>2026-03-14T04:07:13.062856</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903317</t>
+          <t>2026-03-14T04:07:13.062859</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903321</t>
+          <t>2026-03-14T04:07:13.062862</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903324</t>
+          <t>2026-03-14T04:07:13.062864</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903327</t>
+          <t>2026-03-14T04:07:13.062868</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.903330</t>
+          <t>2026-03-14T04:07:13.062871</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1579.14</v>
+        <v>1578.64</v>
       </c>
     </row>
     <row r="4">

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012501</t>
+          <t>2026-03-15T04:29:47.143189</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012514</t>
+          <t>2026-03-15T04:29:47.143226</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012519</t>
+          <t>2026-03-15T04:29:47.143231</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012522</t>
+          <t>2026-03-15T04:29:47.143234</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012525</t>
+          <t>2026-03-15T04:29:47.143237</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012528</t>
+          <t>2026-03-15T04:29:47.143241</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012531</t>
+          <t>2026-03-15T04:29:47.143244</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012535</t>
+          <t>2026-03-15T04:29:47.143251</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012538</t>
+          <t>2026-03-15T04:29:47.143254</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012544</t>
+          <t>2026-03-15T04:29:47.143258</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012547</t>
+          <t>2026-03-15T04:29:47.143260</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012550</t>
+          <t>2026-03-15T04:29:47.143264</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012553</t>
+          <t>2026-03-15T04:29:47.143266</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012556</t>
+          <t>2026-03-15T04:29:47.143269</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012559</t>
+          <t>2026-03-15T04:29:47.143272</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012562</t>
+          <t>2026-03-15T04:29:47.143275</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012565</t>
+          <t>2026-03-15T04:29:47.143277</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012567</t>
+          <t>2026-03-15T04:29:47.143282</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012570</t>
+          <t>2026-03-15T04:29:47.143285</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012575</t>
+          <t>2026-03-15T04:29:47.143288</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012578</t>
+          <t>2026-03-15T04:29:47.143291</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012581</t>
+          <t>2026-03-15T04:29:47.143294</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012584</t>
+          <t>2026-03-15T04:29:47.143296</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012587</t>
+          <t>2026-03-15T04:29:47.143299</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012589</t>
+          <t>2026-03-15T04:29:47.143302</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012592</t>
+          <t>2026-03-15T04:29:47.143305</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012595</t>
+          <t>2026-03-15T04:29:47.143307</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012598</t>
+          <t>2026-03-15T04:29:47.143312</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012601</t>
+          <t>2026-03-15T04:29:47.143315</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012605</t>
+          <t>2026-03-15T04:29:47.143318</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012608</t>
+          <t>2026-03-15T04:29:47.143321</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012611</t>
+          <t>2026-03-15T04:29:47.143324</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012614</t>
+          <t>2026-03-15T04:29:47.143327</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012617</t>
+          <t>2026-03-15T04:29:47.143330</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012619</t>
+          <t>2026-03-15T04:29:47.143333</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012622</t>
+          <t>2026-03-15T04:29:47.143335</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012625</t>
+          <t>2026-03-15T04:29:47.143338</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012628</t>
+          <t>2026-03-15T04:29:47.143341</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:11.012630</t>
+          <t>2026-03-15T04:29:47.143344</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3105,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3163,14 +3163,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077976</t>
+          <t>2026-03-15T04:29:48.255151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3228,14 +3228,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077990</t>
+          <t>2026-03-15T04:29:48.255166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077994</t>
+          <t>2026-03-15T04:29:48.255170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3315,11 +3315,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3358,14 +3358,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077997</t>
+          <t>2026-03-15T04:29:48.255173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3380,11 +3380,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3423,14 +3423,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078000</t>
+          <t>2026-03-15T04:29:48.255176</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3445,11 +3445,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078003</t>
+          <t>2026-03-15T04:29:48.255182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3510,11 +3510,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078006</t>
+          <t>2026-03-15T04:29:48.255185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3575,11 +3575,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3618,14 +3618,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078012</t>
+          <t>2026-03-15T04:29:48.255188</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3640,11 +3640,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078016</t>
+          <t>2026-03-15T04:29:48.255191</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3748,14 +3748,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078019</t>
+          <t>2026-03-15T04:29:48.255212</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3770,11 +3770,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3813,14 +3813,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078022</t>
+          <t>2026-03-15T04:29:48.255216</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078025</t>
+          <t>2026-03-15T04:29:48.255219</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078030</t>
+          <t>2026-03-15T04:29:48.255222</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078032</t>
+          <t>2026-03-15T04:29:48.255224</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078035</t>
+          <t>2026-03-15T04:29:48.255227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078038</t>
+          <t>2026-03-15T04:29:48.255233</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078041</t>
+          <t>2026-03-15T04:29:48.255236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078046</t>
+          <t>2026-03-15T04:29:48.255239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078049</t>
+          <t>2026-03-15T04:29:48.255242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078052</t>
+          <t>2026-03-15T04:29:48.255245</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078055</t>
+          <t>2026-03-15T04:29:48.255248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078058</t>
+          <t>2026-03-15T04:29:48.255251</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078061</t>
+          <t>2026-03-15T04:29:48.255254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078063</t>
+          <t>2026-03-15T04:29:48.255256</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078066</t>
+          <t>2026-03-15T04:29:48.255260</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078069</t>
+          <t>2026-03-15T04:29:48.255266</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078072</t>
+          <t>2026-03-15T04:29:48.255269</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078076</t>
+          <t>2026-03-15T04:29:48.255273</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078079</t>
+          <t>2026-03-15T04:29:48.255276</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078082</t>
+          <t>2026-03-15T04:29:48.255279</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078086</t>
+          <t>2026-03-15T04:29:48.255282</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078088</t>
+          <t>2026-03-15T04:29:48.255285</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078091</t>
+          <t>2026-03-15T04:29:48.255287</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078094</t>
+          <t>2026-03-15T04:29:48.255290</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078097</t>
+          <t>2026-03-15T04:29:48.255293</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078099</t>
+          <t>2026-03-15T04:29:48.255296</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078102</t>
+          <t>2026-03-15T04:29:48.255298</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078105</t>
+          <t>2026-03-15T04:29:48.255301</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078108</t>
+          <t>2026-03-15T04:29:48.255304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078111</t>
+          <t>2026-03-15T04:29:48.255307</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078113</t>
+          <t>2026-03-15T04:29:48.255309</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078119</t>
+          <t>2026-03-15T04:29:48.255312</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078121</t>
+          <t>2026-03-15T04:29:48.255315</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078124</t>
+          <t>2026-03-15T04:29:48.255318</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078127</t>
+          <t>2026-03-15T04:29:48.255321</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078130</t>
+          <t>2026-03-15T04:29:48.255324</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078133</t>
+          <t>2026-03-15T04:29:48.255327</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078135</t>
+          <t>2026-03-15T04:29:48.255330</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078138</t>
+          <t>2026-03-15T04:29:48.255333</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078141</t>
+          <t>2026-03-15T04:29:48.255336</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062721</t>
+          <t>2026-03-15T04:29:49.276985</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062735</t>
+          <t>2026-03-15T04:29:49.277000</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062739</t>
+          <t>2026-03-15T04:29:49.277004</t>
         </is>
       </c>
     </row>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062742</t>
+          <t>2026-03-15T04:29:49.277007</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062744</t>
+          <t>2026-03-15T04:29:49.277010</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062764</t>
+          <t>2026-03-15T04:29:49.277022</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062767</t>
+          <t>2026-03-15T04:29:49.277025</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062778</t>
+          <t>2026-03-15T04:29:49.277028</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062781</t>
+          <t>2026-03-15T04:29:49.277031</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062784</t>
+          <t>2026-03-15T04:29:49.277034</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062787</t>
+          <t>2026-03-15T04:29:49.277037</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062790</t>
+          <t>2026-03-15T04:29:49.277040</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062792</t>
+          <t>2026-03-15T04:29:49.277043</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062795</t>
+          <t>2026-03-15T04:29:49.277045</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062798</t>
+          <t>2026-03-15T04:29:49.277048</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062800</t>
+          <t>2026-03-15T04:29:49.277052</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062803</t>
+          <t>2026-03-15T04:29:49.277054</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062807</t>
+          <t>2026-03-15T04:29:49.277057</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062810</t>
+          <t>2026-03-15T04:29:49.277060</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062813</t>
+          <t>2026-03-15T04:29:49.277063</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062816</t>
+          <t>2026-03-15T04:29:49.277066</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062818</t>
+          <t>2026-03-15T04:29:49.277069</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062821</t>
+          <t>2026-03-15T04:29:49.277072</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062824</t>
+          <t>2026-03-15T04:29:49.277075</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062828</t>
+          <t>2026-03-15T04:29:49.277078</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062832</t>
+          <t>2026-03-15T04:29:49.277081</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062835</t>
+          <t>2026-03-15T04:29:49.277084</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062839</t>
+          <t>2026-03-15T04:29:49.277087</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062842</t>
+          <t>2026-03-15T04:29:49.277090</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062844</t>
+          <t>2026-03-15T04:29:49.277093</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062847</t>
+          <t>2026-03-15T04:29:49.277095</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062850</t>
+          <t>2026-03-15T04:29:49.277099</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062853</t>
+          <t>2026-03-15T04:29:49.277102</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062856</t>
+          <t>2026-03-15T04:29:49.277105</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062859</t>
+          <t>2026-03-15T04:29:49.277108</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062862</t>
+          <t>2026-03-15T04:29:49.277111</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062864</t>
+          <t>2026-03-15T04:29:49.277113</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062868</t>
+          <t>2026-03-15T04:29:49.277116</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:13.062871</t>
+          <t>2026-03-15T04:29:49.277119</t>
         </is>
       </c>
     </row>
@@ -9051,14 +9051,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1578.64</v>
+        <v>1573.68</v>
       </c>
     </row>
     <row r="4">

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,19 +547,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143189</t>
+          <t>2026-03-16T04:36:48.961972</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143226</t>
+          <t>2026-03-16T04:36:48.961987</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,19 +677,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143231</t>
+          <t>2026-03-16T04:36:48.961991</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,19 +742,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143234</t>
+          <t>2026-03-16T04:36:48.961995</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,19 +807,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143237</t>
+          <t>2026-03-16T04:36:48.961998</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143241</t>
+          <t>2026-03-16T04:36:48.962001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143244</t>
+          <t>2026-03-16T04:36:48.962004</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,14 +1002,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143251</t>
+          <t>2026-03-16T04:36:48.962008</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143254</t>
+          <t>2026-03-16T04:36:48.962015</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143258</t>
+          <t>2026-03-16T04:36:48.962018</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143260</t>
+          <t>2026-03-16T04:36:48.962021</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143264</t>
+          <t>2026-03-16T04:36:48.962024</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143266</t>
+          <t>2026-03-16T04:36:48.962028</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143269</t>
+          <t>2026-03-16T04:36:48.962031</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143272</t>
+          <t>2026-03-16T04:36:48.962033</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143275</t>
+          <t>2026-03-16T04:36:48.962037</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143277</t>
+          <t>2026-03-16T04:36:48.962039</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1652,14 +1652,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143282</t>
+          <t>2026-03-16T04:36:48.962043</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,14 +1717,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143285</t>
+          <t>2026-03-16T04:36:48.962048</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143288</t>
+          <t>2026-03-16T04:36:48.962051</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,19 +1847,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143291</t>
+          <t>2026-03-16T04:36:48.962054</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,19 +1912,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143294</t>
+          <t>2026-03-16T04:36:48.962057</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,19 +1977,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143296</t>
+          <t>2026-03-16T04:36:48.962060</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143299</t>
+          <t>2026-03-16T04:36:48.962063</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143302</t>
+          <t>2026-03-16T04:36:48.962066</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143305</t>
+          <t>2026-03-16T04:36:48.962069</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143307</t>
+          <t>2026-03-16T04:36:48.962072</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2302,19 +2302,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143312</t>
+          <t>2026-03-16T04:36:48.962075</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2367,19 +2367,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143315</t>
+          <t>2026-03-16T04:36:48.962080</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143318</t>
+          <t>2026-03-16T04:36:48.962083</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,19 +2497,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143321</t>
+          <t>2026-03-16T04:36:48.962086</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143324</t>
+          <t>2026-03-16T04:36:48.962089</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143327</t>
+          <t>2026-03-16T04:36:48.962092</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,19 +2692,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143330</t>
+          <t>2026-03-16T04:36:48.962095</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,19 +2757,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143333</t>
+          <t>2026-03-16T04:36:48.962098</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,19 +2822,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143335</t>
+          <t>2026-03-16T04:36:48.962101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,19 +2887,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143338</t>
+          <t>2026-03-16T04:36:48.962104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2952,19 +2952,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143341</t>
+          <t>2026-03-16T04:36:48.962107</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3017,7 +3017,202 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:47.143344</t>
+          <t>2026-03-16T04:36:48.962112</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962115</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962118</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:48.962121</t>
         </is>
       </c>
     </row>
@@ -3105,12 +3300,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3120,11 +3315,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3143,7 +3338,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3163,19 +3358,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255151</t>
+          <t>2026-03-16T04:36:49.867488</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3185,11 +3380,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3208,7 +3403,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3228,14 +3423,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255166</t>
+          <t>2026-03-16T04:36:49.867502</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3273,7 +3468,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3293,19 +3488,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255170</t>
+          <t>2026-03-16T04:36:49.867506</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3315,11 +3510,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3338,7 +3533,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3358,19 +3553,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255173</t>
+          <t>2026-03-16T04:36:49.867509</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3403,7 +3598,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3423,19 +3618,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255176</t>
+          <t>2026-03-16T04:36:49.867512</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3445,11 +3640,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3488,19 +3683,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255182</t>
+          <t>2026-03-16T04:36:49.867515</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3510,11 +3705,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1580</v>
+        <v>1547</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3553,19 +3748,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255185</t>
+          <t>2026-03-16T04:36:49.867517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3575,11 +3770,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3618,19 +3813,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255188</t>
+          <t>2026-03-16T04:36:49.867520</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3640,11 +3835,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1538</v>
+        <v>1555</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3683,19 +3878,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255191</t>
+          <t>2026-03-16T04:36:49.867523</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3705,11 +3900,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1572</v>
+        <v>1557</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3748,19 +3943,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255212</t>
+          <t>2026-03-16T04:36:49.867526</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3770,11 +3965,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1578</v>
+        <v>1530</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3813,14 +4008,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255216</t>
+          <t>2026-03-16T04:36:49.867528</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3835,11 +4030,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3878,19 +4073,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255219</t>
+          <t>2026-03-16T04:36:49.867531</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3900,11 +4095,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3943,19 +4138,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255222</t>
+          <t>2026-03-16T04:36:49.867534</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3965,11 +4160,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4008,19 +4203,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255224</t>
+          <t>2026-03-16T04:36:49.867537</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4030,11 +4225,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1579</v>
+        <v>1538</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4073,19 +4268,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255227</t>
+          <t>2026-03-16T04:36:49.867540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4095,11 +4290,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4138,19 +4333,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255233</t>
+          <t>2026-03-16T04:36:49.867543</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4160,11 +4355,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1548</v>
+        <v>1570</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4183,7 +4378,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4203,19 +4398,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255236</t>
+          <t>2026-03-16T04:36:49.867546</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4225,11 +4420,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4268,19 +4463,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255239</t>
+          <t>2026-03-16T04:36:49.867549</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4290,11 +4485,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1593</v>
+        <v>1548</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4313,7 +4508,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4333,19 +4528,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255242</t>
+          <t>2026-03-16T04:36:49.867552</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4355,11 +4550,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4378,7 +4573,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4398,14 +4593,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255245</t>
+          <t>2026-03-16T04:36:49.867555</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4420,11 +4615,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4443,7 +4638,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4463,19 +4658,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255248</t>
+          <t>2026-03-16T04:36:49.867557</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4485,11 +4680,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1597</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4508,7 +4703,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -4528,19 +4723,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255251</t>
+          <t>2026-03-16T04:36:49.867560</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4550,11 +4745,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1597</v>
+        <v>1579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4573,7 +4768,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -4593,19 +4788,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255254</t>
+          <t>2026-03-16T04:36:49.867563</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4615,11 +4810,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1548</v>
+        <v>1584</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4638,7 +4833,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -4658,19 +4853,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255256</t>
+          <t>2026-03-16T04:36:49.867569</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4680,11 +4875,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4723,19 +4918,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255260</t>
+          <t>2026-03-16T04:36:49.867572</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4745,11 +4940,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>1548</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4768,7 +4963,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4788,19 +4983,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255266</t>
+          <t>2026-03-16T04:36:49.867574</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4810,11 +5005,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4853,14 +5048,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255269</t>
+          <t>2026-03-16T04:36:49.867577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4875,11 +5070,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4918,19 +5113,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255273</t>
+          <t>2026-03-16T04:36:49.867580</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4940,11 +5135,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1586</v>
+        <v>1597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4983,19 +5178,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255276</t>
+          <t>2026-03-16T04:36:49.867583</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5005,11 +5200,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1548</v>
+        <v>1599</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5028,7 +5223,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5048,14 +5243,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255279</t>
+          <t>2026-03-16T04:36:49.867585</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5070,11 +5265,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5093,7 +5288,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5113,19 +5308,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255282</t>
+          <t>2026-03-16T04:36:49.867588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5135,11 +5330,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1548</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5158,7 +5353,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5178,19 +5373,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255285</t>
+          <t>2026-03-16T04:36:49.867590</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5200,11 +5395,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1571</v>
+        <v>1586</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5223,7 +5418,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5243,19 +5438,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255287</t>
+          <t>2026-03-16T04:36:49.867594</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5265,11 +5460,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1573</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5288,7 +5483,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5308,19 +5503,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255290</t>
+          <t>2026-03-16T04:36:49.867601</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5330,11 +5525,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5353,7 +5548,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5373,19 +5568,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255293</t>
+          <t>2026-03-16T04:36:49.867604</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5395,11 +5590,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5418,7 +5613,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5438,19 +5633,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255296</t>
+          <t>2026-03-16T04:36:49.867607</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5460,11 +5655,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1590</v>
+        <v>1571</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5483,7 +5678,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5503,19 +5698,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255298</t>
+          <t>2026-03-16T04:36:49.867609</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5525,11 +5720,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1555</v>
+        <v>1571</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5548,7 +5743,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5568,19 +5763,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255301</t>
+          <t>2026-03-16T04:36:49.867612</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5590,11 +5785,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5613,7 +5808,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5633,19 +5828,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255304</t>
+          <t>2026-03-16T04:36:49.867615</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5655,11 +5850,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5678,7 +5873,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5698,19 +5893,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255307</t>
+          <t>2026-03-16T04:36:49.867617</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5720,11 +5915,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1588</v>
+        <v>1548</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5743,7 +5938,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5763,14 +5958,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255309</t>
+          <t>2026-03-16T04:36:49.867620</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5785,11 +5980,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5808,7 +6003,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5828,14 +6023,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255312</t>
+          <t>2026-03-16T04:36:49.867623</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5850,11 +6045,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5873,7 +6068,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5893,19 +6088,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255315</t>
+          <t>2026-03-16T04:36:49.867626</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5915,11 +6110,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1576</v>
+        <v>1555</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5938,7 +6133,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5958,19 +6153,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255318</t>
+          <t>2026-03-16T04:36:49.867631</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5980,11 +6175,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1577</v>
+        <v>1595</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6003,7 +6198,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6023,19 +6218,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255321</t>
+          <t>2026-03-16T04:36:49.867634</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6045,11 +6240,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6068,7 +6263,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6088,19 +6283,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255324</t>
+          <t>2026-03-16T04:36:49.867636</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6110,11 +6305,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6133,7 +6328,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6153,14 +6348,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255327</t>
+          <t>2026-03-16T04:36:49.867639</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6175,11 +6370,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6198,7 +6393,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6218,19 +6413,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255330</t>
+          <t>2026-03-16T04:36:49.867642</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6240,11 +6435,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1565</v>
+        <v>1576</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6263,7 +6458,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6283,19 +6478,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255333</t>
+          <t>2026-03-16T04:36:49.867645</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6305,11 +6500,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1590</v>
+        <v>1577</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6348,7 +6543,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255336</t>
+          <t>2026-03-16T04:36:49.867647</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6436,12 +6631,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6451,11 +6646,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6474,7 +6669,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6494,19 +6689,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.276985</t>
+          <t>2026-03-16T04:36:50.724674</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6516,11 +6711,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6539,7 +6734,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6559,19 +6754,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277000</t>
+          <t>2026-03-16T04:36:50.724688</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6581,11 +6776,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6604,7 +6799,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6624,19 +6819,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277004</t>
+          <t>2026-03-16T04:36:50.724693</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6646,11 +6841,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6689,19 +6884,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277007</t>
+          <t>2026-03-16T04:36:50.724698</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6711,11 +6906,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6754,19 +6949,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277010</t>
+          <t>2026-03-16T04:36:50.724701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6776,11 +6971,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6819,14 +7014,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277022</t>
+          <t>2026-03-16T04:36:50.724704</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6841,11 +7036,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -6864,7 +7059,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -6884,14 +7079,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277025</t>
+          <t>2026-03-16T04:36:50.724707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6906,11 +7101,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -6929,7 +7124,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6949,14 +7144,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277028</t>
+          <t>2026-03-16T04:36:50.724709</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6971,11 +7166,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -6994,7 +7189,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7014,14 +7209,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277031</t>
+          <t>2026-03-16T04:36:50.724712</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7036,11 +7231,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7079,14 +7274,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277034</t>
+          <t>2026-03-16T04:36:50.724715</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7101,11 +7296,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7144,14 +7339,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277037</t>
+          <t>2026-03-16T04:36:50.724718</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7166,11 +7361,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7209,14 +7404,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277040</t>
+          <t>2026-03-16T04:36:50.724720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7231,11 +7426,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7254,7 +7449,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7274,14 +7469,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277043</t>
+          <t>2026-03-16T04:36:50.724723</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7296,11 +7491,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7319,7 +7514,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7339,14 +7534,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277045</t>
+          <t>2026-03-16T04:36:50.724726</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7361,11 +7556,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7384,7 +7579,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7404,14 +7599,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277048</t>
+          <t>2026-03-16T04:36:50.724729</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7426,11 +7621,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7469,14 +7664,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277052</t>
+          <t>2026-03-16T04:36:50.724731</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7491,11 +7686,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7534,14 +7729,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277054</t>
+          <t>2026-03-16T04:36:50.724734</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7556,11 +7751,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7599,14 +7794,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277057</t>
+          <t>2026-03-16T04:36:50.724737</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7621,11 +7816,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7644,7 +7839,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -7664,14 +7859,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277060</t>
+          <t>2026-03-16T04:36:50.724740</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7686,11 +7881,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7709,7 +7904,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -7729,14 +7924,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277063</t>
+          <t>2026-03-16T04:36:50.724743</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7751,11 +7946,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7774,7 +7969,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7794,19 +7989,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277066</t>
+          <t>2026-03-16T04:36:50.724746</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7816,11 +8011,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -7839,7 +8034,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -7859,19 +8054,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277069</t>
+          <t>2026-03-16T04:36:50.724748</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7881,11 +8076,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -7904,7 +8099,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -7924,19 +8119,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277072</t>
+          <t>2026-03-16T04:36:50.724751</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7969,7 +8164,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -7989,19 +8184,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277075</t>
+          <t>2026-03-16T04:36:50.724754</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8011,11 +8206,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8034,7 +8229,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8054,14 +8249,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277078</t>
+          <t>2026-03-16T04:36:50.724757</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8076,11 +8271,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8099,7 +8294,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8119,19 +8314,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277081</t>
+          <t>2026-03-16T04:36:50.724760</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8141,11 +8336,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8164,7 +8359,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8184,14 +8379,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277084</t>
+          <t>2026-03-16T04:36:50.724762</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8206,11 +8401,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8249,19 +8444,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277087</t>
+          <t>2026-03-16T04:36:50.724765</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8271,11 +8466,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8314,19 +8509,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277090</t>
+          <t>2026-03-16T04:36:50.724768</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8336,11 +8531,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8379,19 +8574,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277093</t>
+          <t>2026-03-16T04:36:50.724771</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8401,11 +8596,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8424,7 +8619,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8444,19 +8639,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277095</t>
+          <t>2026-03-16T04:36:50.724774</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8466,11 +8661,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8489,7 +8684,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8509,14 +8704,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277099</t>
+          <t>2026-03-16T04:36:50.724777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8531,11 +8726,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8554,7 +8749,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8574,19 +8769,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277102</t>
+          <t>2026-03-16T04:36:50.724779</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8596,11 +8791,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8619,7 +8814,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8639,19 +8834,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277105</t>
+          <t>2026-03-16T04:36:50.724782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8661,11 +8856,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8684,7 +8879,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8704,19 +8899,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277108</t>
+          <t>2026-03-16T04:36:50.724785</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8726,11 +8921,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8749,7 +8944,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -8769,19 +8964,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277111</t>
+          <t>2026-03-16T04:36:50.724788</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8791,11 +8986,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -8814,7 +9009,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -8834,19 +9029,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277113</t>
+          <t>2026-03-16T04:36:50.724791</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8856,11 +9051,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -8899,19 +9094,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277116</t>
+          <t>2026-03-16T04:36:50.724793</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8964,7 +9159,202 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:49.277119</t>
+          <t>2026-03-16T04:36:50.724796</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724799</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724801</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-16T04:36:50.724804</t>
         </is>
       </c>
     </row>
@@ -9021,18 +9411,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1395.974358974359</v>
+        <v>1393.595238095238</v>
       </c>
     </row>
     <row r="3">
@@ -9051,14 +9441,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1573.68</v>
+        <v>1570.9</v>
       </c>
     </row>
     <row r="4">
@@ -9073,18 +9463,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1395.974358974359</v>
+        <v>1393.595238095238</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -547,19 +547,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961972</t>
+          <t>2026-03-17T04:14:32.873151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961987</t>
+          <t>2026-03-17T04:14:32.873167</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961991</t>
+          <t>2026-03-17T04:14:32.873172</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961995</t>
+          <t>2026-03-17T04:14:32.873175</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.961998</t>
+          <t>2026-03-17T04:14:32.873179</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,19 +872,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962001</t>
+          <t>2026-03-17T04:14:32.873182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962004</t>
+          <t>2026-03-17T04:14:32.873185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1002,19 +1002,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962008</t>
+          <t>2026-03-17T04:14:32.873189</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962015</t>
+          <t>2026-03-17T04:14:32.873192</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,19 +1132,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962018</t>
+          <t>2026-03-17T04:14:32.873195</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,19 +1197,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962021</t>
+          <t>2026-03-17T04:14:32.873201</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,19 +1262,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962024</t>
+          <t>2026-03-17T04:14:32.873204</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,19 +1327,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962028</t>
+          <t>2026-03-17T04:14:32.873207</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,19 +1392,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962031</t>
+          <t>2026-03-17T04:14:32.873210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1457,14 +1457,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962033</t>
+          <t>2026-03-17T04:14:32.873213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962037</t>
+          <t>2026-03-17T04:14:32.873216</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962039</t>
+          <t>2026-03-17T04:14:32.873219</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962043</t>
+          <t>2026-03-17T04:14:32.873222</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962048</t>
+          <t>2026-03-17T04:14:32.873225</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1782,19 +1782,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962051</t>
+          <t>2026-03-17T04:14:32.873227</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,19 +1847,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962054</t>
+          <t>2026-03-17T04:14:32.873232</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,19 +1912,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962057</t>
+          <t>2026-03-17T04:14:32.873235</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,19 +1977,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962060</t>
+          <t>2026-03-17T04:14:32.873238</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962063</t>
+          <t>2026-03-17T04:14:32.873241</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962066</t>
+          <t>2026-03-17T04:14:32.873244</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962069</t>
+          <t>2026-03-17T04:14:32.873247</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,19 +2237,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962072</t>
+          <t>2026-03-17T04:14:32.873250</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962075</t>
+          <t>2026-03-17T04:14:32.873253</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962080</t>
+          <t>2026-03-17T04:14:32.873255</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,14 +2432,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962083</t>
+          <t>2026-03-17T04:14:32.873258</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962086</t>
+          <t>2026-03-17T04:14:32.873263</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962089</t>
+          <t>2026-03-17T04:14:32.873266</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,19 +2627,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962092</t>
+          <t>2026-03-17T04:14:32.873269</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,19 +2692,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962095</t>
+          <t>2026-03-17T04:14:32.873274</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1380</v>
+        <v>1433</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,19 +2757,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962098</t>
+          <t>2026-03-17T04:14:32.873277</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962101</t>
+          <t>2026-03-17T04:14:32.873280</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962104</t>
+          <t>2026-03-17T04:14:32.873283</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962107</t>
+          <t>2026-03-17T04:14:32.873285</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962112</t>
+          <t>2026-03-17T04:14:32.873288</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3082,19 +3082,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962115</t>
+          <t>2026-03-17T04:14:32.873291</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3147,72 +3147,267 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:48.962118</t>
+          <t>2026-03-17T04:14:32.873296</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873299</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>1377</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>首饰黄金</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>jewelry</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-16T04:36:48.962121</t>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873302</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873305</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:32.873308</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3338,7 +3533,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3358,14 +3553,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867488</t>
+          <t>2026-03-17T04:14:33.716608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3423,14 +3618,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867502</t>
+          <t>2026-03-17T04:14:33.716622</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3445,11 +3640,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3468,7 +3663,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3488,14 +3683,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867506</t>
+          <t>2026-03-17T04:14:33.716625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3510,11 +3705,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3533,7 +3728,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3553,14 +3748,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867509</t>
+          <t>2026-03-17T04:14:33.716628</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3575,11 +3770,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3598,7 +3793,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3618,14 +3813,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867512</t>
+          <t>2026-03-17T04:14:33.716631</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3640,11 +3835,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3683,14 +3878,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867515</t>
+          <t>2026-03-17T04:14:33.716634</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3705,11 +3900,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3728,7 +3923,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3748,14 +3943,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867517</t>
+          <t>2026-03-17T04:14:33.716637</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3793,7 +3988,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -3813,14 +4008,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867520</t>
+          <t>2026-03-17T04:14:33.716640</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3858,7 +4053,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3878,14 +4073,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867523</t>
+          <t>2026-03-17T04:14:33.716643</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3923,7 +4118,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3943,14 +4138,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867526</t>
+          <t>2026-03-17T04:14:33.716646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3988,7 +4183,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4008,14 +4203,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867528</t>
+          <t>2026-03-17T04:14:33.716649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4030,11 +4225,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4073,14 +4268,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867531</t>
+          <t>2026-03-17T04:14:33.716652</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4095,11 +4290,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4138,14 +4333,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867534</t>
+          <t>2026-03-17T04:14:33.716655</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4160,11 +4355,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4203,14 +4398,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867537</t>
+          <t>2026-03-17T04:14:33.716658</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4225,11 +4420,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4268,14 +4463,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867540</t>
+          <t>2026-03-17T04:14:33.716661</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4290,11 +4485,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4333,14 +4528,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867543</t>
+          <t>2026-03-17T04:14:33.716664</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4355,11 +4550,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4398,14 +4593,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867546</t>
+          <t>2026-03-17T04:14:33.716666</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4420,11 +4615,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4463,14 +4658,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867549</t>
+          <t>2026-03-17T04:14:33.716669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4485,11 +4680,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4508,7 +4703,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4528,14 +4723,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867552</t>
+          <t>2026-03-17T04:14:33.716672</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4550,11 +4745,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4593,14 +4788,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867555</t>
+          <t>2026-03-17T04:14:33.716675</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4615,11 +4810,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4658,14 +4853,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867557</t>
+          <t>2026-03-17T04:14:33.716678</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4680,11 +4875,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4723,14 +4918,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867560</t>
+          <t>2026-03-17T04:14:33.716680</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4745,11 +4940,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4788,14 +4983,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867563</t>
+          <t>2026-03-17T04:14:33.716683</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4810,11 +5005,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4853,14 +5048,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867569</t>
+          <t>2026-03-17T04:14:33.716686</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4875,11 +5070,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4898,7 +5093,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -4918,14 +5113,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867572</t>
+          <t>2026-03-17T04:14:33.716688</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4983,14 +5178,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867574</t>
+          <t>2026-03-17T04:14:33.716694</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5005,11 +5200,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5028,7 +5223,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5048,14 +5243,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867577</t>
+          <t>2026-03-17T04:14:33.716705</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5070,11 +5265,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5093,7 +5288,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5113,14 +5308,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867580</t>
+          <t>2026-03-17T04:14:33.716710</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5135,11 +5330,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5158,7 +5353,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5178,14 +5373,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867583</t>
+          <t>2026-03-17T04:14:33.716717</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5200,11 +5395,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5223,7 +5418,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5243,14 +5438,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867585</t>
+          <t>2026-03-17T04:14:33.716723</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5265,11 +5460,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5308,14 +5503,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867588</t>
+          <t>2026-03-17T04:14:33.716730</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5330,11 +5525,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5373,14 +5568,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867590</t>
+          <t>2026-03-17T04:14:33.716733</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5395,11 +5590,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5438,14 +5633,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867594</t>
+          <t>2026-03-17T04:14:33.716736</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5460,11 +5655,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5503,14 +5698,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867601</t>
+          <t>2026-03-17T04:14:33.716739</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5525,11 +5720,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5568,14 +5763,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867604</t>
+          <t>2026-03-17T04:14:33.716742</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5633,14 +5828,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867607</t>
+          <t>2026-03-17T04:14:33.716745</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5655,11 +5850,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5678,7 +5873,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5698,14 +5893,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867609</t>
+          <t>2026-03-17T04:14:33.716748</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5720,11 +5915,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5743,7 +5938,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5763,14 +5958,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867612</t>
+          <t>2026-03-17T04:14:33.716750</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5785,11 +5980,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5808,7 +6003,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5828,14 +6023,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867615</t>
+          <t>2026-03-17T04:14:33.716753</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5850,11 +6045,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5873,7 +6068,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5893,14 +6088,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867617</t>
+          <t>2026-03-17T04:14:33.716756</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5938,7 +6133,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5958,14 +6153,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867620</t>
+          <t>2026-03-17T04:14:33.716759</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5980,11 +6175,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6003,7 +6198,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6023,14 +6218,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867623</t>
+          <t>2026-03-17T04:14:33.716762</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6045,11 +6240,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6068,7 +6263,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6088,14 +6283,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867626</t>
+          <t>2026-03-17T04:14:33.716765</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6110,11 +6305,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6133,7 +6328,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6153,14 +6348,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867631</t>
+          <t>2026-03-17T04:14:33.716768</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6175,11 +6370,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6198,7 +6393,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6218,14 +6413,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867634</t>
+          <t>2026-03-17T04:14:33.716771</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6240,11 +6435,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6263,7 +6458,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6283,14 +6478,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867636</t>
+          <t>2026-03-17T04:14:33.716774</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6305,11 +6500,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6328,7 +6523,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6348,14 +6543,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867639</t>
+          <t>2026-03-17T04:14:33.716776</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6370,11 +6565,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6393,7 +6588,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6413,14 +6608,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867642</t>
+          <t>2026-03-17T04:14:33.716779</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6435,11 +6630,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6458,7 +6653,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6478,14 +6673,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867645</t>
+          <t>2026-03-17T04:14:33.716782</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6500,11 +6695,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6523,7 +6718,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6543,7 +6738,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867647</t>
+          <t>2026-03-17T04:14:33.716785</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6631,12 +6826,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6646,11 +6841,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6669,7 +6864,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -6689,19 +6884,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724674</t>
+          <t>2026-03-17T04:14:34.479171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6711,11 +6906,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6734,7 +6929,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6754,19 +6949,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724688</t>
+          <t>2026-03-17T04:14:34.479184</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6776,11 +6971,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6799,7 +6994,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -6819,14 +7014,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724693</t>
+          <t>2026-03-17T04:14:34.479188</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6841,11 +7036,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6864,7 +7059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -6884,14 +7079,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724698</t>
+          <t>2026-03-17T04:14:34.479192</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6906,11 +7101,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -6929,7 +7124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -6949,14 +7144,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724701</t>
+          <t>2026-03-17T04:14:34.479195</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6971,11 +7166,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -6994,7 +7189,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7014,19 +7209,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724704</t>
+          <t>2026-03-17T04:14:34.479198</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7036,11 +7231,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7079,19 +7274,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724707</t>
+          <t>2026-03-17T04:14:34.479201</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7101,11 +7296,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1388</v>
+        <v>1380</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7144,19 +7339,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724709</t>
+          <t>2026-03-17T04:14:34.479204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7166,11 +7361,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1390</v>
+        <v>1383</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7209,14 +7404,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724712</t>
+          <t>2026-03-17T04:14:34.479207</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7231,11 +7426,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7254,7 +7449,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7274,19 +7469,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724715</t>
+          <t>2026-03-17T04:14:34.479210</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7296,11 +7491,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7319,7 +7514,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -7339,19 +7534,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724718</t>
+          <t>2026-03-17T04:14:34.479213</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7361,11 +7556,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7384,7 +7579,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7404,19 +7599,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724720</t>
+          <t>2026-03-17T04:14:34.479215</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7426,11 +7621,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7469,19 +7664,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724723</t>
+          <t>2026-03-17T04:14:34.479218</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7491,11 +7686,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7534,19 +7729,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724726</t>
+          <t>2026-03-17T04:14:34.479221</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7556,11 +7751,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7599,14 +7794,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724729</t>
+          <t>2026-03-17T04:14:34.479224</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7621,11 +7816,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7644,7 +7839,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -7664,14 +7859,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724731</t>
+          <t>2026-03-17T04:14:34.479227</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7686,11 +7881,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7709,7 +7904,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -7729,14 +7924,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724734</t>
+          <t>2026-03-17T04:14:34.479230</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7751,11 +7946,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7774,7 +7969,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7794,19 +7989,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724737</t>
+          <t>2026-03-17T04:14:34.479232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7816,11 +8011,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -7859,19 +8054,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724740</t>
+          <t>2026-03-17T04:14:34.479235</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7881,11 +8076,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -7924,19 +8119,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724743</t>
+          <t>2026-03-17T04:14:34.479238</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7946,11 +8141,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -7989,19 +8184,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724746</t>
+          <t>2026-03-17T04:14:34.479241</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8011,11 +8206,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8034,7 +8229,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8054,19 +8249,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724748</t>
+          <t>2026-03-17T04:14:34.479244</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8076,11 +8271,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8099,7 +8294,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8119,19 +8314,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724751</t>
+          <t>2026-03-17T04:14:34.479247</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8141,11 +8336,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8164,7 +8359,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8184,19 +8379,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724754</t>
+          <t>2026-03-17T04:14:34.479251</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8229,7 +8424,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8249,14 +8444,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724757</t>
+          <t>2026-03-17T04:14:34.479261</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8294,7 +8489,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8314,19 +8509,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724760</t>
+          <t>2026-03-17T04:14:34.479267</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8336,11 +8531,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8359,7 +8554,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8379,19 +8574,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724762</t>
+          <t>2026-03-17T04:14:34.479273</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8401,11 +8596,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8424,7 +8619,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8444,19 +8639,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724765</t>
+          <t>2026-03-17T04:14:34.479279</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8466,11 +8661,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8489,7 +8684,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8509,14 +8704,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724768</t>
+          <t>2026-03-17T04:14:34.479286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8531,11 +8726,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8554,7 +8749,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8574,14 +8769,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724771</t>
+          <t>2026-03-17T04:14:34.479292</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8596,11 +8791,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8639,14 +8834,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724774</t>
+          <t>2026-03-17T04:14:34.479298</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8661,11 +8856,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8704,14 +8899,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724777</t>
+          <t>2026-03-17T04:14:34.479303</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8726,11 +8921,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8769,19 +8964,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724779</t>
+          <t>2026-03-17T04:14:34.479309</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8791,11 +8986,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -8814,7 +9009,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -8834,19 +9029,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724782</t>
+          <t>2026-03-17T04:14:34.479316</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8856,11 +9051,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1380</v>
+        <v>1433</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -8879,7 +9074,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -8899,19 +9094,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724785</t>
+          <t>2026-03-17T04:14:34.479323</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8921,11 +9116,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -8944,7 +9139,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -8964,14 +9159,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724788</t>
+          <t>2026-03-17T04:14:34.479330</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9009,7 +9204,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9029,14 +9224,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724791</t>
+          <t>2026-03-17T04:14:34.479335</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9074,7 +9269,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9094,14 +9289,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724793</t>
+          <t>2026-03-17T04:14:34.479338</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9139,7 +9334,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9159,19 +9354,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724796</t>
+          <t>2026-03-17T04:14:34.479341</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9181,11 +9376,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9224,19 +9419,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724799</t>
+          <t>2026-03-17T04:14:34.479344</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9246,11 +9441,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9289,72 +9484,267 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:50.724801</t>
+          <t>2026-03-17T04:14:34.479347</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479350</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>1377</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>金条</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>gold_bar</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-03-16T04:36:50.724804</t>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479353</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479356</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1380.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1380</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-17T04:14:34.479359</t>
         </is>
       </c>
     </row>
@@ -9411,18 +9801,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1393.595238095238</v>
+        <v>1391.377777777778</v>
       </c>
     </row>
     <row r="3">
@@ -9441,14 +9831,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1570.9</v>
+        <v>1567.14</v>
       </c>
     </row>
     <row r="4">
@@ -9463,18 +9853,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1393.595238095238</v>
+        <v>1391.377777777778</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873151</t>
+          <t>2026-03-18T04:22:02.688081</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873167</t>
+          <t>2026-03-18T04:22:02.688096</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873172</t>
+          <t>2026-03-18T04:22:02.688101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873175</t>
+          <t>2026-03-18T04:22:02.688104</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873179</t>
+          <t>2026-03-18T04:22:02.688108</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,19 +872,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873182</t>
+          <t>2026-03-18T04:22:02.688111</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,19 +937,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873185</t>
+          <t>2026-03-18T04:22:02.688114</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873189</t>
+          <t>2026-03-18T04:22:02.688118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873192</t>
+          <t>2026-03-18T04:22:02.688121</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873195</t>
+          <t>2026-03-18T04:22:02.688124</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873201</t>
+          <t>2026-03-18T04:22:02.688131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873204</t>
+          <t>2026-03-18T04:22:02.688134</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873207</t>
+          <t>2026-03-18T04:22:02.688137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873210</t>
+          <t>2026-03-18T04:22:02.688140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873213</t>
+          <t>2026-03-18T04:22:02.688143</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873216</t>
+          <t>2026-03-18T04:22:02.688160</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873219</t>
+          <t>2026-03-18T04:22:02.688164</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873222</t>
+          <t>2026-03-18T04:22:02.688167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873225</t>
+          <t>2026-03-18T04:22:02.688170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,14 +1782,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873227</t>
+          <t>2026-03-18T04:22:02.688173</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873232</t>
+          <t>2026-03-18T04:22:02.688178</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873235</t>
+          <t>2026-03-18T04:22:02.688181</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873238</t>
+          <t>2026-03-18T04:22:02.688184</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2042,19 +2042,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873241</t>
+          <t>2026-03-18T04:22:02.688187</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873244</t>
+          <t>2026-03-18T04:22:02.688190</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873247</t>
+          <t>2026-03-18T04:22:02.688193</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873250</t>
+          <t>2026-03-18T04:22:02.688196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873253</t>
+          <t>2026-03-18T04:22:02.688199</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,19 +2367,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873255</t>
+          <t>2026-03-18T04:22:02.688202</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873258</t>
+          <t>2026-03-18T04:22:02.688205</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873263</t>
+          <t>2026-03-18T04:22:02.688210</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,19 +2562,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873266</t>
+          <t>2026-03-18T04:22:02.688213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,19 +2627,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873269</t>
+          <t>2026-03-18T04:22:02.688218</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2692,19 +2692,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873274</t>
+          <t>2026-03-18T04:22:02.688221</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2757,19 +2757,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873277</t>
+          <t>2026-03-18T04:22:02.688224</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2822,19 +2822,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873280</t>
+          <t>2026-03-18T04:22:02.688227</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,19 +2887,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873283</t>
+          <t>2026-03-18T04:22:02.688229</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,19 +2952,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873285</t>
+          <t>2026-03-18T04:22:02.688232</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873288</t>
+          <t>2026-03-18T04:22:02.688235</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873291</t>
+          <t>2026-03-18T04:22:02.688238</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3147,19 +3147,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873296</t>
+          <t>2026-03-18T04:22:02.688243</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3212,14 +3212,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873299</t>
+          <t>2026-03-18T04:22:02.688246</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3277,14 +3277,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873302</t>
+          <t>2026-03-18T04:22:02.688249</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3342,72 +3342,267 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:32.873305</t>
+          <t>2026-03-18T04:22:02.688252</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688255</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>1380</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>首饰黄金</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>jewelry</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-17T04:14:32.873308</t>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688258</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688261</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:02.688263</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3690,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3510,11 +3705,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3533,7 +3728,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3553,14 +3748,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716608</t>
+          <t>2026-03-18T04:22:03.547322</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3618,14 +3813,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716622</t>
+          <t>2026-03-18T04:22:03.547335</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3663,7 +3858,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3683,14 +3878,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716625</t>
+          <t>2026-03-18T04:22:03.547339</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3728,7 +3923,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3748,14 +3943,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716628</t>
+          <t>2026-03-18T04:22:03.547342</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3793,7 +3988,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -3813,14 +4008,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716631</t>
+          <t>2026-03-18T04:22:03.547345</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3835,11 +4030,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3878,14 +4073,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716634</t>
+          <t>2026-03-18T04:22:03.547348</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3923,7 +4118,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3943,14 +4138,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716637</t>
+          <t>2026-03-18T04:22:03.547351</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3965,11 +4160,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3988,7 +4183,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4008,14 +4203,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716640</t>
+          <t>2026-03-18T04:22:03.547354</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4030,11 +4225,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4053,7 +4248,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4073,14 +4268,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716643</t>
+          <t>2026-03-18T04:22:03.547357</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4095,11 +4290,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4118,7 +4313,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4138,14 +4333,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716646</t>
+          <t>2026-03-18T04:22:03.547361</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4203,14 +4398,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716649</t>
+          <t>2026-03-18T04:22:03.547364</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4225,11 +4420,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4268,14 +4463,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716652</t>
+          <t>2026-03-18T04:22:03.547367</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4313,7 +4508,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4333,14 +4528,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716655</t>
+          <t>2026-03-18T04:22:03.547370</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4378,7 +4573,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4398,14 +4593,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716658</t>
+          <t>2026-03-18T04:22:03.547373</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4443,7 +4638,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4463,14 +4658,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716661</t>
+          <t>2026-03-18T04:22:03.547376</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4485,11 +4680,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4508,7 +4703,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4528,14 +4723,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716664</t>
+          <t>2026-03-18T04:22:03.547379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4550,11 +4745,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4593,14 +4788,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716666</t>
+          <t>2026-03-18T04:22:03.547382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4638,7 +4833,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4658,14 +4853,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716669</t>
+          <t>2026-03-18T04:22:03.547385</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4680,11 +4875,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4723,14 +4918,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716672</t>
+          <t>2026-03-18T04:22:03.547388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4745,11 +4940,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4788,14 +4983,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716675</t>
+          <t>2026-03-18T04:22:03.547391</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4810,11 +5005,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4853,14 +5048,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716678</t>
+          <t>2026-03-18T04:22:03.547394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4875,11 +5070,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4918,14 +5113,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716680</t>
+          <t>2026-03-18T04:22:03.547397</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4940,11 +5135,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4983,14 +5178,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716683</t>
+          <t>2026-03-18T04:22:03.547399</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5005,11 +5200,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5048,14 +5243,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716686</t>
+          <t>2026-03-18T04:22:03.547402</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5070,11 +5265,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5113,14 +5308,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716688</t>
+          <t>2026-03-18T04:22:03.547405</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5135,11 +5330,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5158,7 +5353,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5178,14 +5373,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716694</t>
+          <t>2026-03-18T04:22:03.547408</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5200,11 +5395,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5243,14 +5438,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716705</t>
+          <t>2026-03-18T04:22:03.547410</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5265,11 +5460,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5308,14 +5503,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716710</t>
+          <t>2026-03-18T04:22:03.547413</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5330,11 +5525,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5373,14 +5568,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716717</t>
+          <t>2026-03-18T04:22:03.547416</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5395,11 +5590,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5438,14 +5633,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716723</t>
+          <t>2026-03-18T04:22:03.547419</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5460,11 +5655,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5483,7 +5678,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5503,14 +5698,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716730</t>
+          <t>2026-03-18T04:22:03.547421</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5525,11 +5720,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5548,7 +5743,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5568,14 +5763,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716733</t>
+          <t>2026-03-18T04:22:03.547424</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5590,11 +5785,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5613,7 +5808,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5633,14 +5828,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716736</t>
+          <t>2026-03-18T04:22:03.547427</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5655,11 +5850,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5678,7 +5873,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5698,14 +5893,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716739</t>
+          <t>2026-03-18T04:22:03.547430</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5720,11 +5915,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5743,7 +5938,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5763,14 +5958,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716742</t>
+          <t>2026-03-18T04:22:03.547432</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5828,14 +6023,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716745</t>
+          <t>2026-03-18T04:22:03.547435</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5850,11 +6045,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5893,14 +6088,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716748</t>
+          <t>2026-03-18T04:22:03.547438</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5915,11 +6110,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5958,14 +6153,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716750</t>
+          <t>2026-03-18T04:22:03.547441</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5980,11 +6175,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6023,14 +6218,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716753</t>
+          <t>2026-03-18T04:22:03.547444</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6045,11 +6240,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6088,14 +6283,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716756</t>
+          <t>2026-03-18T04:22:03.547446</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6153,14 +6348,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716759</t>
+          <t>2026-03-18T04:22:03.547449</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6175,11 +6370,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6218,14 +6413,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716762</t>
+          <t>2026-03-18T04:22:03.547452</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6240,11 +6435,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6263,7 +6458,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6283,14 +6478,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716765</t>
+          <t>2026-03-18T04:22:03.547455</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6328,7 +6523,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6348,14 +6543,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716768</t>
+          <t>2026-03-18T04:22:03.547458</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6370,11 +6565,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6393,7 +6588,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6413,14 +6608,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716771</t>
+          <t>2026-03-18T04:22:03.547461</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6435,11 +6630,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6458,7 +6653,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6478,14 +6673,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716774</t>
+          <t>2026-03-18T04:22:03.547464</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6500,11 +6695,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6523,7 +6718,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6543,14 +6738,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716776</t>
+          <t>2026-03-18T04:22:03.547466</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6565,11 +6760,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6588,7 +6783,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6608,14 +6803,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716779</t>
+          <t>2026-03-18T04:22:03.547469</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6630,11 +6825,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6653,7 +6848,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6673,14 +6868,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716782</t>
+          <t>2026-03-18T04:22:03.547472</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6695,11 +6890,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6718,7 +6913,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6738,7 +6933,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716785</t>
+          <t>2026-03-18T04:22:03.547475</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6826,12 +7021,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6841,11 +7036,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6884,14 +7079,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479171</t>
+          <t>2026-03-18T04:22:04.296379</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6929,7 +7124,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -6949,19 +7144,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479184</t>
+          <t>2026-03-18T04:22:04.296393</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6971,11 +7166,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6994,7 +7189,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7014,14 +7209,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479188</t>
+          <t>2026-03-18T04:22:04.296397</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7036,11 +7231,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7059,7 +7254,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7079,14 +7274,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479192</t>
+          <t>2026-03-18T04:22:04.296400</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7101,11 +7296,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7124,7 +7319,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7144,14 +7339,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479195</t>
+          <t>2026-03-18T04:22:04.296403</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7166,11 +7361,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7209,19 +7404,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479198</t>
+          <t>2026-03-18T04:22:04.296406</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7231,11 +7426,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1385</v>
+        <v>1363</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7254,7 +7449,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7274,19 +7469,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479201</t>
+          <t>2026-03-18T04:22:04.296409</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7296,11 +7491,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7319,7 +7514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7339,19 +7534,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479204</t>
+          <t>2026-03-18T04:22:04.296411</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7361,11 +7556,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1383</v>
+        <v>1360</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7384,7 +7579,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7404,14 +7599,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479207</t>
+          <t>2026-03-18T04:22:04.296414</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7426,11 +7621,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7469,14 +7664,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479210</t>
+          <t>2026-03-18T04:22:04.296423</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7491,11 +7686,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7534,14 +7729,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479213</t>
+          <t>2026-03-18T04:22:04.296430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7556,11 +7751,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7599,14 +7794,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479215</t>
+          <t>2026-03-18T04:22:04.296437</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7621,11 +7816,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7644,7 +7839,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7664,14 +7859,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479218</t>
+          <t>2026-03-18T04:22:04.296443</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7686,11 +7881,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7709,7 +7904,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7729,14 +7924,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479221</t>
+          <t>2026-03-18T04:22:04.296449</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7751,11 +7946,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7774,7 +7969,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7794,19 +7989,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479224</t>
+          <t>2026-03-18T04:22:04.296454</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7816,11 +8011,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -7859,14 +8054,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479227</t>
+          <t>2026-03-18T04:22:04.296459</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7881,11 +8076,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -7924,19 +8119,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479230</t>
+          <t>2026-03-18T04:22:04.296465</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7946,11 +8141,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -7989,19 +8184,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479232</t>
+          <t>2026-03-18T04:22:04.296472</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8011,11 +8206,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -8034,7 +8229,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8054,19 +8249,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479235</t>
+          <t>2026-03-18T04:22:04.296478</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8076,11 +8271,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1376</v>
+        <v>1390</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -8099,7 +8294,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -8119,14 +8314,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479238</t>
+          <t>2026-03-18T04:22:04.296481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8141,11 +8336,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1371</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -8164,7 +8359,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -8184,14 +8379,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479241</t>
+          <t>2026-03-18T04:22:04.296483</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8206,11 +8401,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8249,14 +8444,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479244</t>
+          <t>2026-03-18T04:22:04.296486</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8271,11 +8466,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8314,14 +8509,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479247</t>
+          <t>2026-03-18T04:22:04.296490</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8336,11 +8531,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8379,19 +8574,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479251</t>
+          <t>2026-03-18T04:22:04.296492</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8401,11 +8596,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8424,7 +8619,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8444,19 +8639,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479261</t>
+          <t>2026-03-18T04:22:04.296495</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8466,11 +8661,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8489,7 +8684,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8509,19 +8704,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479267</t>
+          <t>2026-03-18T04:22:04.296498</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8531,11 +8726,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8554,7 +8749,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8574,14 +8769,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479273</t>
+          <t>2026-03-18T04:22:04.296501</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8596,11 +8791,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8619,7 +8814,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8639,19 +8834,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479279</t>
+          <t>2026-03-18T04:22:04.296504</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8661,11 +8856,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8684,7 +8879,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8704,19 +8899,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479286</t>
+          <t>2026-03-18T04:22:04.296507</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8726,11 +8921,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8749,7 +8944,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8769,19 +8964,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479292</t>
+          <t>2026-03-18T04:22:04.296527</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8791,11 +8986,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1452</v>
+        <v>1400</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -8814,7 +9009,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -8834,14 +9029,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479298</t>
+          <t>2026-03-18T04:22:04.296531</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8856,11 +9051,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -8879,7 +9074,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -8899,19 +9094,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479303</t>
+          <t>2026-03-18T04:22:04.296533</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8921,11 +9116,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -8944,7 +9139,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -8964,19 +9159,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479309</t>
+          <t>2026-03-18T04:22:04.296536</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8986,11 +9181,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -9029,19 +9224,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479316</t>
+          <t>2026-03-18T04:22:04.296539</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -9051,11 +9246,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -9094,19 +9289,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479323</t>
+          <t>2026-03-18T04:22:04.296542</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9116,11 +9311,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -9159,19 +9354,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479330</t>
+          <t>2026-03-18T04:22:04.296545</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -9181,11 +9376,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9204,7 +9399,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9224,19 +9419,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479335</t>
+          <t>2026-03-18T04:22:04.296548</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9246,11 +9441,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9269,7 +9464,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9289,19 +9484,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479338</t>
+          <t>2026-03-18T04:22:04.296551</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9311,11 +9506,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9334,7 +9529,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9354,19 +9549,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479341</t>
+          <t>2026-03-18T04:22:04.296554</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9376,11 +9571,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9399,7 +9594,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -9419,14 +9614,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479344</t>
+          <t>2026-03-18T04:22:04.296557</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9464,7 +9659,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9484,19 +9679,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479347</t>
+          <t>2026-03-18T04:22:04.296560</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9506,11 +9701,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9529,7 +9724,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -9549,14 +9744,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479350</t>
+          <t>2026-03-18T04:22:04.296563</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9571,11 +9766,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -9594,7 +9789,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -9614,14 +9809,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479353</t>
+          <t>2026-03-18T04:22:04.296566</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9636,11 +9831,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -9679,72 +9874,267 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:34.479356</t>
+          <t>2026-03-18T04:22:04.296569</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296571</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>周大福</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>1380.00</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>1380</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>涨</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>金条</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>gold_bar</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-03-17T04:14:34.479359</t>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296574</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296577</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周生生</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1377.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>跌</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-18T04:22:04.296580</t>
         </is>
       </c>
     </row>
@@ -9801,18 +10191,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1391.377777777778</v>
+        <v>1389.375</v>
       </c>
     </row>
     <row r="3">
@@ -9831,14 +10221,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1567.14</v>
+        <v>1563.74</v>
       </c>
     </row>
     <row r="4">
@@ -9853,18 +10243,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1391.377777777778</v>
+        <v>1389.375</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688081</t>
+          <t>2026-03-19T04:21:07.605930</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688096</t>
+          <t>2026-03-19T04:21:07.605946</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688101</t>
+          <t>2026-03-19T04:21:07.605951</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688104</t>
+          <t>2026-03-19T04:21:07.605954</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,14 +807,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688108</t>
+          <t>2026-03-19T04:21:07.605958</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -872,19 +872,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688111</t>
+          <t>2026-03-19T04:21:07.605961</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,19 +937,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688114</t>
+          <t>2026-03-19T04:21:07.605964</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688118</t>
+          <t>2026-03-19T04:21:07.605970</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1067,14 +1067,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688121</t>
+          <t>2026-03-19T04:21:07.605973</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,14 +1132,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688124</t>
+          <t>2026-03-19T04:21:07.605977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,14 +1197,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688131</t>
+          <t>2026-03-19T04:21:07.605982</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688134</t>
+          <t>2026-03-19T04:21:07.605985</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688137</t>
+          <t>2026-03-19T04:21:07.605988</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688140</t>
+          <t>2026-03-19T04:21:07.605991</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1457,19 +1457,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688143</t>
+          <t>2026-03-19T04:21:07.605994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,19 +1522,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688160</t>
+          <t>2026-03-19T04:21:07.605997</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,19 +1587,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688164</t>
+          <t>2026-03-19T04:21:07.606000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688167</t>
+          <t>2026-03-19T04:21:07.606003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688170</t>
+          <t>2026-03-19T04:21:07.606006</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1782,19 +1782,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688173</t>
+          <t>2026-03-19T04:21:07.606009</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688178</t>
+          <t>2026-03-19T04:21:07.606014</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,19 +1912,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688181</t>
+          <t>2026-03-19T04:21:07.606017</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,19 +1977,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688184</t>
+          <t>2026-03-19T04:21:07.606020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,19 +2042,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688187</t>
+          <t>2026-03-19T04:21:07.606023</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,19 +2107,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688190</t>
+          <t>2026-03-19T04:21:07.606026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2172,19 +2172,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688193</t>
+          <t>2026-03-19T04:21:07.606029</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688196</t>
+          <t>2026-03-19T04:21:07.606032</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688199</t>
+          <t>2026-03-19T04:21:07.606035</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688202</t>
+          <t>2026-03-19T04:21:07.606038</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688205</t>
+          <t>2026-03-19T04:21:07.606041</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,19 +2497,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688210</t>
+          <t>2026-03-19T04:21:07.606043</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,19 +2562,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688213</t>
+          <t>2026-03-19T04:21:07.606046</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688218</t>
+          <t>2026-03-19T04:21:07.606049</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688221</t>
+          <t>2026-03-19T04:21:07.606052</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688224</t>
+          <t>2026-03-19T04:21:07.606055</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688227</t>
+          <t>2026-03-19T04:21:07.606058</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688229</t>
+          <t>2026-03-19T04:21:07.606061</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2952,19 +2952,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688232</t>
+          <t>2026-03-19T04:21:07.606064</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3017,19 +3017,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688235</t>
+          <t>2026-03-19T04:21:07.606066</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3082,19 +3082,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688238</t>
+          <t>2026-03-19T04:21:07.606069</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688243</t>
+          <t>2026-03-19T04:21:07.606074</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688246</t>
+          <t>2026-03-19T04:21:07.606077</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3277,19 +3277,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688249</t>
+          <t>2026-03-19T04:21:07.606080</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3342,19 +3342,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688252</t>
+          <t>2026-03-19T04:21:07.606083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3364,11 +3364,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3407,19 +3407,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688255</t>
+          <t>2026-03-19T04:21:07.606086</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688258</t>
+          <t>2026-03-19T04:21:07.606089</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3537,72 +3537,202 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:02.688261</t>
+          <t>2026-03-19T04:21:07.606092</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606094</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>1377</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>首饰黄金</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>jewelry</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-03-18T04:22:02.688263</t>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606097</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>首饰黄金</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>jewelry</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:07.606100</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3705,11 +3835,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3748,14 +3878,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547322</t>
+          <t>2026-03-19T04:21:08.539092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3770,11 +3900,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3793,7 +3923,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3813,14 +3943,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547335</t>
+          <t>2026-03-19T04:21:08.539112</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3835,11 +3965,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3858,7 +3988,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3878,14 +4008,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547339</t>
+          <t>2026-03-19T04:21:08.539118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3900,11 +4030,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3923,7 +4053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -3943,14 +4073,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547342</t>
+          <t>2026-03-19T04:21:08.539126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3965,11 +4095,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3988,7 +4118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4008,14 +4138,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547345</t>
+          <t>2026-03-19T04:21:08.539132</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4030,11 +4160,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4073,14 +4203,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547348</t>
+          <t>2026-03-19T04:21:08.539138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4095,11 +4225,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4118,7 +4248,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4138,14 +4268,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547351</t>
+          <t>2026-03-19T04:21:08.539144</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4183,7 +4313,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4203,14 +4333,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547354</t>
+          <t>2026-03-19T04:21:08.539148</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4248,7 +4378,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4268,14 +4398,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547357</t>
+          <t>2026-03-19T04:21:08.539151</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4313,7 +4443,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4333,14 +4463,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547361</t>
+          <t>2026-03-19T04:21:08.539154</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4398,14 +4528,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547364</t>
+          <t>2026-03-19T04:21:08.539157</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4420,11 +4550,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4463,14 +4593,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547367</t>
+          <t>2026-03-19T04:21:08.539160</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4485,11 +4615,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4508,7 +4638,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4528,14 +4658,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547370</t>
+          <t>2026-03-19T04:21:08.539163</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4550,11 +4680,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4573,7 +4703,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4593,14 +4723,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547373</t>
+          <t>2026-03-19T04:21:08.539166</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4658,14 +4788,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547376</t>
+          <t>2026-03-19T04:21:08.539169</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4703,7 +4833,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4723,14 +4853,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547379</t>
+          <t>2026-03-19T04:21:08.539172</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4745,11 +4875,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4788,14 +4918,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547382</t>
+          <t>2026-03-19T04:21:08.539175</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4810,11 +4940,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4833,7 +4963,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4853,14 +4983,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547385</t>
+          <t>2026-03-19T04:21:08.539178</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4898,7 +5028,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4918,14 +5048,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547388</t>
+          <t>2026-03-19T04:21:08.539181</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4963,7 +5093,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4983,14 +5113,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547391</t>
+          <t>2026-03-19T04:21:08.539184</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5028,7 +5158,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5048,14 +5178,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547394</t>
+          <t>2026-03-19T04:21:08.539187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5070,11 +5200,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -5113,14 +5243,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547397</t>
+          <t>2026-03-19T04:21:08.539189</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5135,11 +5265,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -5158,7 +5288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5178,14 +5308,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547399</t>
+          <t>2026-03-19T04:21:08.539193</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5223,7 +5353,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5243,14 +5373,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547402</t>
+          <t>2026-03-19T04:21:08.539195</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5265,11 +5395,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5308,14 +5438,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547405</t>
+          <t>2026-03-19T04:21:08.539198</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5330,11 +5460,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5373,14 +5503,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547408</t>
+          <t>2026-03-19T04:21:08.539201</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5395,11 +5525,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5438,14 +5568,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547410</t>
+          <t>2026-03-19T04:21:08.539204</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5460,11 +5590,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5503,14 +5633,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547413</t>
+          <t>2026-03-19T04:21:08.539207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5525,11 +5655,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5568,14 +5698,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547416</t>
+          <t>2026-03-19T04:21:08.539210</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5590,11 +5720,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5633,14 +5763,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547419</t>
+          <t>2026-03-19T04:21:08.539213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5655,11 +5785,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5698,14 +5828,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547421</t>
+          <t>2026-03-19T04:21:08.539215</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5720,11 +5850,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5763,14 +5893,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547424</t>
+          <t>2026-03-19T04:21:08.539218</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5785,11 +5915,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5828,14 +5958,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547427</t>
+          <t>2026-03-19T04:21:08.539221</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5850,11 +5980,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5893,14 +6023,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547430</t>
+          <t>2026-03-19T04:21:08.539224</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5915,11 +6045,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5958,14 +6088,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547432</t>
+          <t>2026-03-19T04:21:08.539227</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5980,11 +6110,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6003,7 +6133,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6023,14 +6153,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547435</t>
+          <t>2026-03-19T04:21:08.539230</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6045,11 +6175,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6068,7 +6198,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6088,14 +6218,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547438</t>
+          <t>2026-03-19T04:21:08.539233</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6110,11 +6240,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6133,7 +6263,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -6153,14 +6283,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547441</t>
+          <t>2026-03-19T04:21:08.539236</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6175,11 +6305,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6198,7 +6328,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6218,14 +6348,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547444</t>
+          <t>2026-03-19T04:21:08.539239</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6240,11 +6370,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6263,7 +6393,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6283,14 +6413,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547446</t>
+          <t>2026-03-19T04:21:08.539241</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6348,14 +6478,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547449</t>
+          <t>2026-03-19T04:21:08.539244</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6370,11 +6500,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6393,7 +6523,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6413,14 +6543,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547452</t>
+          <t>2026-03-19T04:21:08.539247</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6435,11 +6565,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6478,14 +6608,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547455</t>
+          <t>2026-03-19T04:21:08.539250</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6543,14 +6673,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547458</t>
+          <t>2026-03-19T04:21:08.539253</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6565,11 +6695,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6608,14 +6738,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547461</t>
+          <t>2026-03-19T04:21:08.539256</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6630,11 +6760,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6673,14 +6803,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547464</t>
+          <t>2026-03-19T04:21:08.539259</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6695,11 +6825,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6738,14 +6868,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547466</t>
+          <t>2026-03-19T04:21:08.539262</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6760,11 +6890,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6803,14 +6933,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547469</t>
+          <t>2026-03-19T04:21:08.539265</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6825,11 +6955,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6848,7 +6978,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6868,14 +6998,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547472</t>
+          <t>2026-03-19T04:21:08.539268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6890,11 +7020,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6913,7 +7043,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6933,7 +7063,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547475</t>
+          <t>2026-03-19T04:21:08.539271</t>
         </is>
       </c>
     </row>
@@ -6948,7 +7078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7021,12 +7151,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7036,11 +7166,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1358</v>
+        <v>1316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7079,14 +7209,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296379</t>
+          <t>2026-03-19T04:21:09.314166</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7101,11 +7231,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1361</v>
+        <v>1318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7124,7 +7254,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -7144,19 +7274,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296393</t>
+          <t>2026-03-19T04:21:09.314181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7166,11 +7296,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7189,7 +7319,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -7209,14 +7339,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296397</t>
+          <t>2026-03-19T04:21:09.314185</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7254,7 +7384,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7274,14 +7404,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296400</t>
+          <t>2026-03-19T04:21:09.314188</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7319,7 +7449,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7339,14 +7469,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296403</t>
+          <t>2026-03-19T04:21:09.314192</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7361,11 +7491,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7384,7 +7514,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -7404,19 +7534,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296406</t>
+          <t>2026-03-19T04:21:09.314195</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7426,11 +7556,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7449,7 +7579,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7469,19 +7599,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296409</t>
+          <t>2026-03-19T04:21:09.314198</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7491,11 +7621,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7514,7 +7644,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7534,19 +7664,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296411</t>
+          <t>2026-03-19T04:21:09.314201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7556,11 +7686,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7579,7 +7709,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -7599,14 +7729,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296414</t>
+          <t>2026-03-19T04:21:09.314204</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7621,11 +7751,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7644,7 +7774,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7664,14 +7794,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296423</t>
+          <t>2026-03-19T04:21:09.314207</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7686,11 +7816,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7709,7 +7839,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -7729,14 +7859,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296430</t>
+          <t>2026-03-19T04:21:09.314210</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7751,11 +7881,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7774,7 +7904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7794,14 +7924,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296437</t>
+          <t>2026-03-19T04:21:09.314213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7816,11 +7946,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1386</v>
+        <v>1380</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7859,14 +7989,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296443</t>
+          <t>2026-03-19T04:21:09.314216</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7881,11 +8011,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -7924,14 +8054,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296449</t>
+          <t>2026-03-19T04:21:09.314221</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7946,11 +8076,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -7989,19 +8119,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296454</t>
+          <t>2026-03-19T04:21:09.314227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8011,11 +8141,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -8034,7 +8164,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8054,19 +8184,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296459</t>
+          <t>2026-03-19T04:21:09.314232</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8076,11 +8206,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -8099,7 +8229,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8119,19 +8249,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296465</t>
+          <t>2026-03-19T04:21:09.314238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8141,11 +8271,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -8164,7 +8294,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8184,19 +8314,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296472</t>
+          <t>2026-03-19T04:21:09.314244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8206,11 +8336,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -8249,19 +8379,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296478</t>
+          <t>2026-03-19T04:21:09.314250</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8271,11 +8401,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -8314,19 +8444,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296481</t>
+          <t>2026-03-19T04:21:09.314257</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8336,11 +8466,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1401</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -8379,14 +8509,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296483</t>
+          <t>2026-03-19T04:21:09.314262</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8401,11 +8531,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8424,7 +8554,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8444,19 +8574,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296486</t>
+          <t>2026-03-19T04:21:09.314265</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8466,11 +8596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8489,7 +8619,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8509,19 +8639,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296490</t>
+          <t>2026-03-19T04:21:09.314269</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8531,11 +8661,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8554,7 +8684,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8574,19 +8704,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296492</t>
+          <t>2026-03-19T04:21:09.314272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8596,11 +8726,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8639,19 +8769,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296495</t>
+          <t>2026-03-19T04:21:09.314275</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8661,11 +8791,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8704,19 +8834,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296498</t>
+          <t>2026-03-19T04:21:09.314278</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8726,11 +8856,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8769,14 +8899,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296501</t>
+          <t>2026-03-19T04:21:09.314281</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8791,11 +8921,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8814,7 +8944,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8834,14 +8964,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296504</t>
+          <t>2026-03-19T04:21:09.314285</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8856,11 +8986,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -8879,7 +9009,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8899,14 +9029,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296507</t>
+          <t>2026-03-19T04:21:09.314288</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8921,11 +9051,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1403</v>
+        <v>1385</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -8944,7 +9074,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -8964,19 +9094,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296527</t>
+          <t>2026-03-19T04:21:09.314291</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8986,11 +9116,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -9009,7 +9139,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9029,19 +9159,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296531</t>
+          <t>2026-03-19T04:21:09.314294</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9074,7 +9204,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -9094,19 +9224,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296533</t>
+          <t>2026-03-19T04:21:09.314297</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9116,11 +9246,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -9139,7 +9269,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -9159,14 +9289,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296536</t>
+          <t>2026-03-19T04:21:09.314300</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9181,11 +9311,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -9204,7 +9334,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -9224,14 +9354,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296539</t>
+          <t>2026-03-19T04:21:09.314303</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9246,11 +9376,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -9269,7 +9399,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -9289,14 +9419,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296542</t>
+          <t>2026-03-19T04:21:09.314306</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9311,11 +9441,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -9334,7 +9464,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -9354,14 +9484,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296545</t>
+          <t>2026-03-19T04:21:09.314309</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9376,11 +9506,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1433</v>
+        <v>1452</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9419,19 +9549,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296548</t>
+          <t>2026-03-19T04:21:09.314312</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9441,11 +9571,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9484,19 +9614,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296551</t>
+          <t>2026-03-19T04:21:09.314316</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9506,11 +9636,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1429</v>
+        <v>1450</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9549,19 +9679,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296554</t>
+          <t>2026-03-19T04:21:09.314319</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9571,11 +9701,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1386</v>
+        <v>1429</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9594,7 +9724,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -9614,19 +9744,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296557</t>
+          <t>2026-03-19T04:21:09.314322</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9636,11 +9766,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9659,7 +9789,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -9679,14 +9809,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296560</t>
+          <t>2026-03-19T04:21:09.314325</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9701,11 +9831,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1380</v>
+        <v>1428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9724,7 +9854,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -9744,19 +9874,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296563</t>
+          <t>2026-03-19T04:21:09.314329</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9766,11 +9896,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -9789,7 +9919,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -9809,19 +9939,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296566</t>
+          <t>2026-03-19T04:21:09.314332</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9831,11 +9961,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -9854,7 +9984,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -9874,19 +10004,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296569</t>
+          <t>2026-03-19T04:21:09.314335</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9896,11 +10026,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -9919,7 +10049,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -9939,19 +10069,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296571</t>
+          <t>2026-03-19T04:21:09.314338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10004,14 +10134,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296574</t>
+          <t>2026-03-19T04:21:09.314341</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10026,11 +10156,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -10069,72 +10199,202 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:04.296577</t>
+          <t>2026-03-19T04:21:09.314344</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>周大福</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1386.00</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1386</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314355</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>周生生</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>金条金价(内地)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>1377.00</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E50" t="n">
         <v>1377</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>元/克</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>另计</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>跌</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>金条</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>gold_bar</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>新浪财经</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-03-18T04:22:04.296580</t>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314358</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>六福</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>金条金价(内地)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1378.00</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>元/克</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>另计</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>涨</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>金条</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gold_bar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-03-19T04:21:09.314361</t>
         </is>
       </c>
     </row>
@@ -10191,18 +10451,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1389.375</v>
+        <v>1385.08</v>
       </c>
     </row>
     <row r="3">
@@ -10221,14 +10481,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1563.74</v>
+        <v>1554.92</v>
       </c>
     </row>
     <row r="4">
@@ -10243,18 +10503,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1389.375</v>
+        <v>1385.08</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,19 +547,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605930</t>
+          <t>2026-03-20T04:10:43.744684</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605946</t>
+          <t>2026-03-20T04:10:43.744699</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1310</v>
+        <v>1269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,19 +677,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605951</t>
+          <t>2026-03-20T04:10:43.744704</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,19 +742,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605954</t>
+          <t>2026-03-20T04:10:43.744707</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -807,19 +807,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605958</t>
+          <t>2026-03-20T04:10:43.744710</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,14 +872,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605961</t>
+          <t>2026-03-20T04:10:43.744713</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,19 +937,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605964</t>
+          <t>2026-03-20T04:10:43.744717</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605970</t>
+          <t>2026-03-20T04:10:43.744721</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605973</t>
+          <t>2026-03-20T04:10:43.744724</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,19 +1132,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605977</t>
+          <t>2026-03-20T04:10:43.744727</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1197,19 +1197,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605982</t>
+          <t>2026-03-20T04:10:43.744733</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605985</t>
+          <t>2026-03-20T04:10:43.744736</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605988</t>
+          <t>2026-03-20T04:10:43.744739</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,14 +1392,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605991</t>
+          <t>2026-03-20T04:10:43.744742</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605994</t>
+          <t>2026-03-20T04:10:43.744745</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1522,19 +1522,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.605997</t>
+          <t>2026-03-20T04:10:43.744748</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606000</t>
+          <t>2026-03-20T04:10:43.744751</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606003</t>
+          <t>2026-03-20T04:10:43.744754</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606006</t>
+          <t>2026-03-20T04:10:43.744757</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1782,19 +1782,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606009</t>
+          <t>2026-03-20T04:10:43.744760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606014</t>
+          <t>2026-03-20T04:10:43.744765</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606017</t>
+          <t>2026-03-20T04:10:43.744768</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606020</t>
+          <t>2026-03-20T04:10:43.744771</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606023</t>
+          <t>2026-03-20T04:10:43.744774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606026</t>
+          <t>2026-03-20T04:10:43.744777</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2172,19 +2172,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606029</t>
+          <t>2026-03-20T04:10:43.744779</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2237,14 +2237,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606032</t>
+          <t>2026-03-20T04:10:43.744782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2302,14 +2302,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606035</t>
+          <t>2026-03-20T04:10:43.744785</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606038</t>
+          <t>2026-03-20T04:10:43.744788</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606041</t>
+          <t>2026-03-20T04:10:43.744791</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2497,19 +2497,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606043</t>
+          <t>2026-03-20T04:10:43.744794</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2562,19 +2562,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606046</t>
+          <t>2026-03-20T04:10:43.744797</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2627,14 +2627,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606049</t>
+          <t>2026-03-20T04:10:43.744799</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,14 +2692,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606052</t>
+          <t>2026-03-20T04:10:43.744802</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,14 +2757,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606055</t>
+          <t>2026-03-20T04:10:43.744805</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606058</t>
+          <t>2026-03-20T04:10:43.744808</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,19 +2887,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606061</t>
+          <t>2026-03-20T04:10:43.744811</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,19 +2952,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606064</t>
+          <t>2026-03-20T04:10:43.744814</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606066</t>
+          <t>2026-03-20T04:10:43.744816</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3082,19 +3082,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606069</t>
+          <t>2026-03-20T04:10:43.744819</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3147,19 +3147,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606074</t>
+          <t>2026-03-20T04:10:43.744824</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3212,14 +3212,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606077</t>
+          <t>2026-03-20T04:10:43.744827</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3277,19 +3277,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606080</t>
+          <t>2026-03-20T04:10:43.744830</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3342,19 +3342,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606083</t>
+          <t>2026-03-20T04:10:43.744833</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3364,11 +3364,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606086</t>
+          <t>2026-03-20T04:10:43.744836</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3472,19 +3472,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606089</t>
+          <t>2026-03-20T04:10:43.744839</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3537,19 +3537,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606092</t>
+          <t>2026-03-20T04:10:43.744841</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3559,11 +3559,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606094</t>
+          <t>2026-03-20T04:10:43.744844</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3624,11 +3624,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606097</t>
+          <t>2026-03-20T04:10:43.744847</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3689,11 +3689,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:07.606100</t>
+          <t>2026-03-20T04:10:43.744850</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539092</t>
+          <t>2026-03-20T04:10:45.580718</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539112</t>
+          <t>2026-03-20T04:10:45.580732</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539118</t>
+          <t>2026-03-20T04:10:45.580736</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539126</t>
+          <t>2026-03-20T04:10:45.580740</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539132</t>
+          <t>2026-03-20T04:10:45.580743</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539138</t>
+          <t>2026-03-20T04:10:45.580746</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539144</t>
+          <t>2026-03-20T04:10:45.580749</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539148</t>
+          <t>2026-03-20T04:10:45.580752</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539151</t>
+          <t>2026-03-20T04:10:45.580755</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539154</t>
+          <t>2026-03-20T04:10:45.580758</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539157</t>
+          <t>2026-03-20T04:10:45.580761</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539160</t>
+          <t>2026-03-20T04:10:45.580764</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539163</t>
+          <t>2026-03-20T04:10:45.580767</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539166</t>
+          <t>2026-03-20T04:10:45.580770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539169</t>
+          <t>2026-03-20T04:10:45.580773</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539172</t>
+          <t>2026-03-20T04:10:45.580775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539175</t>
+          <t>2026-03-20T04:10:45.580778</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539178</t>
+          <t>2026-03-20T04:10:45.580781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539181</t>
+          <t>2026-03-20T04:10:45.580784</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539184</t>
+          <t>2026-03-20T04:10:45.580787</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539187</t>
+          <t>2026-03-20T04:10:45.580789</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539189</t>
+          <t>2026-03-20T04:10:45.580792</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539193</t>
+          <t>2026-03-20T04:10:45.580795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539195</t>
+          <t>2026-03-20T04:10:45.580798</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539198</t>
+          <t>2026-03-20T04:10:45.580800</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539201</t>
+          <t>2026-03-20T04:10:45.580803</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539204</t>
+          <t>2026-03-20T04:10:45.580806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539207</t>
+          <t>2026-03-20T04:10:45.580809</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539210</t>
+          <t>2026-03-20T04:10:45.580812</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539213</t>
+          <t>2026-03-20T04:10:45.580814</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539215</t>
+          <t>2026-03-20T04:10:45.580817</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539218</t>
+          <t>2026-03-20T04:10:45.580820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539221</t>
+          <t>2026-03-20T04:10:45.580823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539224</t>
+          <t>2026-03-20T04:10:45.580826</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539227</t>
+          <t>2026-03-20T04:10:45.580828</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539230</t>
+          <t>2026-03-20T04:10:45.580831</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539233</t>
+          <t>2026-03-20T04:10:45.580834</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539236</t>
+          <t>2026-03-20T04:10:45.580836</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539239</t>
+          <t>2026-03-20T04:10:45.580839</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539241</t>
+          <t>2026-03-20T04:10:45.580842</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539244</t>
+          <t>2026-03-20T04:10:45.580845</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6543,14 +6543,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539247</t>
+          <t>2026-03-20T04:10:45.580847</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6565,11 +6565,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6608,14 +6608,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539250</t>
+          <t>2026-03-20T04:10:45.580850</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6673,14 +6673,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539253</t>
+          <t>2026-03-20T04:10:45.580853</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6695,11 +6695,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539256</t>
+          <t>2026-03-20T04:10:45.580856</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6803,14 +6803,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539259</t>
+          <t>2026-03-20T04:10:45.580859</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6825,11 +6825,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6868,14 +6868,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539262</t>
+          <t>2026-03-20T04:10:45.580861</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6890,11 +6890,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6933,14 +6933,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539265</t>
+          <t>2026-03-20T04:10:45.580864</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6955,11 +6955,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6998,14 +6998,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539268</t>
+          <t>2026-03-20T04:10:45.580867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7020,11 +7020,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539271</t>
+          <t>2026-03-20T04:10:45.580870</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1316</v>
+        <v>1268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7209,19 +7209,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314166</t>
+          <t>2026-03-20T04:10:46.395178</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7274,19 +7274,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314181</t>
+          <t>2026-03-20T04:10:46.395191</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1310</v>
+        <v>1269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7339,19 +7339,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314185</t>
+          <t>2026-03-20T04:10:46.395195</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1359</v>
+        <v>1310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -7404,19 +7404,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314188</t>
+          <t>2026-03-20T04:10:46.395198</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1361</v>
+        <v>1316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -7469,19 +7469,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314192</t>
+          <t>2026-03-20T04:10:46.395201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314195</t>
+          <t>2026-03-20T04:10:46.395204</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7599,19 +7599,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314198</t>
+          <t>2026-03-20T04:10:46.395207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7664,19 +7664,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314201</t>
+          <t>2026-03-20T04:10:46.395210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7729,19 +7729,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314204</t>
+          <t>2026-03-20T04:10:46.395213</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7794,19 +7794,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314207</t>
+          <t>2026-03-20T04:10:46.395216</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -7859,19 +7859,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314210</t>
+          <t>2026-03-20T04:10:46.395219</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314213</t>
+          <t>2026-03-20T04:10:46.395222</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1380</v>
+        <v>1360</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314216</t>
+          <t>2026-03-20T04:10:46.395224</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1385</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -8054,14 +8054,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314221</t>
+          <t>2026-03-20T04:10:46.395227</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -8119,19 +8119,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314227</t>
+          <t>2026-03-20T04:10:46.395230</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -8184,19 +8184,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314232</t>
+          <t>2026-03-20T04:10:46.395233</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314238</t>
+          <t>2026-03-20T04:10:46.395236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8271,11 +8271,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -8314,19 +8314,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314244</t>
+          <t>2026-03-20T04:10:46.395239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1404</v>
+        <v>1390</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -8379,19 +8379,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314250</t>
+          <t>2026-03-20T04:10:46.395242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1399</v>
+        <v>1386</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -8444,19 +8444,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314257</t>
+          <t>2026-03-20T04:10:46.395245</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314262</t>
+          <t>2026-03-20T04:10:46.395248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314265</t>
+          <t>2026-03-20T04:10:46.395251</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314269</t>
+          <t>2026-03-20T04:10:46.395254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314272</t>
+          <t>2026-03-20T04:10:46.395257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8726,11 +8726,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8769,19 +8769,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314275</t>
+          <t>2026-03-20T04:10:46.395259</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8791,11 +8791,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -8834,19 +8834,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314278</t>
+          <t>2026-03-20T04:10:46.395263</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -8856,11 +8856,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8899,14 +8899,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314281</t>
+          <t>2026-03-20T04:10:46.395265</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8921,11 +8921,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1382</v>
+        <v>1371</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314285</t>
+          <t>2026-03-20T04:10:46.395268</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8986,11 +8986,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1383</v>
+        <v>1376</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -9029,14 +9029,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314288</t>
+          <t>2026-03-20T04:10:46.395271</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9051,11 +9051,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -9094,19 +9094,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314291</t>
+          <t>2026-03-20T04:10:46.395274</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9116,11 +9116,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1403</v>
+        <v>1383</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -9159,19 +9159,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314294</t>
+          <t>2026-03-20T04:10:46.395276</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -9224,19 +9224,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314297</t>
+          <t>2026-03-20T04:10:46.395279</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9246,11 +9246,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314300</t>
+          <t>2026-03-20T04:10:46.395282</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -9354,14 +9354,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314303</t>
+          <t>2026-03-20T04:10:46.395284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9376,11 +9376,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314306</t>
+          <t>2026-03-20T04:10:46.395287</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314309</t>
+          <t>2026-03-20T04:10:46.395290</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9506,11 +9506,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1452</v>
+        <v>1403</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -9549,19 +9549,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314312</t>
+          <t>2026-03-20T04:10:46.395293</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9571,11 +9571,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -9614,19 +9614,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314316</t>
+          <t>2026-03-20T04:10:46.395296</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9636,11 +9636,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1450</v>
+        <v>1401</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -9679,19 +9679,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314319</t>
+          <t>2026-03-20T04:10:46.395299</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9701,11 +9701,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -9744,19 +9744,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314322</t>
+          <t>2026-03-20T04:10:46.395302</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9766,11 +9766,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -9809,19 +9809,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314325</t>
+          <t>2026-03-20T04:10:46.395304</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -9831,11 +9831,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -9874,14 +9874,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314329</t>
+          <t>2026-03-20T04:10:46.395307</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9896,11 +9896,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1386</v>
+        <v>1433</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -9939,19 +9939,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314332</t>
+          <t>2026-03-20T04:10:46.395310</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9961,11 +9961,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -10004,19 +10004,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314335</t>
+          <t>2026-03-20T04:10:46.395313</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10026,11 +10026,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1384</v>
+        <v>1428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -10069,14 +10069,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314338</t>
+          <t>2026-03-20T04:10:46.395315</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -10134,19 +10134,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314341</t>
+          <t>2026-03-20T04:10:46.395318</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10156,11 +10156,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -10199,19 +10199,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314344</t>
+          <t>2026-03-20T04:10:46.395321</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10221,11 +10221,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -10264,19 +10264,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314355</t>
+          <t>2026-03-20T04:10:46.395324</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10286,11 +10286,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1377.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1377</v>
+        <v>1384</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -10329,19 +10329,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314358</t>
+          <t>2026-03-20T04:10:46.395335</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10351,11 +10351,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:09.314361</t>
+          <t>2026-03-20T04:10:46.395338</t>
         </is>
       </c>
     </row>
@@ -10455,14 +10455,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1385.08</v>
+        <v>1378.34</v>
       </c>
     </row>
     <row r="3">
@@ -10481,14 +10481,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1554.92</v>
+        <v>1538.8</v>
       </c>
     </row>
     <row r="4">
@@ -10507,14 +10507,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1385.08</v>
+        <v>1378.34</v>
       </c>
     </row>
   </sheetData>

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744684</t>
+          <t>2026-03-21T04:01:59.791242</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744699</t>
+          <t>2026-03-21T04:01:59.791257</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744704</t>
+          <t>2026-03-21T04:01:59.791262</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744707</t>
+          <t>2026-03-21T04:01:59.791265</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744710</t>
+          <t>2026-03-21T04:01:59.791268</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744713</t>
+          <t>2026-03-21T04:01:59.791272</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744717</t>
+          <t>2026-03-21T04:01:59.791275</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744721</t>
+          <t>2026-03-21T04:01:59.791278</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744724</t>
+          <t>2026-03-21T04:01:59.791281</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744727</t>
+          <t>2026-03-21T04:01:59.791284</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744733</t>
+          <t>2026-03-21T04:01:59.791290</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744736</t>
+          <t>2026-03-21T04:01:59.791293</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744739</t>
+          <t>2026-03-21T04:01:59.791296</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744742</t>
+          <t>2026-03-21T04:01:59.791299</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744745</t>
+          <t>2026-03-21T04:01:59.791302</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744748</t>
+          <t>2026-03-21T04:01:59.791305</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744751</t>
+          <t>2026-03-21T04:01:59.791308</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744754</t>
+          <t>2026-03-21T04:01:59.791313</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744757</t>
+          <t>2026-03-21T04:01:59.791316</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744760</t>
+          <t>2026-03-21T04:01:59.791319</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744765</t>
+          <t>2026-03-21T04:01:59.791324</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744768</t>
+          <t>2026-03-21T04:01:59.791327</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744771</t>
+          <t>2026-03-21T04:01:59.791329</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744774</t>
+          <t>2026-03-21T04:01:59.791332</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744777</t>
+          <t>2026-03-21T04:01:59.791335</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744779</t>
+          <t>2026-03-21T04:01:59.791338</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744782</t>
+          <t>2026-03-21T04:01:59.791343</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744785</t>
+          <t>2026-03-21T04:01:59.791346</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744788</t>
+          <t>2026-03-21T04:01:59.791349</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744791</t>
+          <t>2026-03-21T04:01:59.791352</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744794</t>
+          <t>2026-03-21T04:01:59.791355</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744797</t>
+          <t>2026-03-21T04:01:59.791358</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744799</t>
+          <t>2026-03-21T04:01:59.791361</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744802</t>
+          <t>2026-03-21T04:01:59.791364</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744805</t>
+          <t>2026-03-21T04:01:59.791368</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744808</t>
+          <t>2026-03-21T04:01:59.791371</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744811</t>
+          <t>2026-03-21T04:01:59.791374</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744814</t>
+          <t>2026-03-21T04:01:59.791377</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744816</t>
+          <t>2026-03-21T04:01:59.791380</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744819</t>
+          <t>2026-03-21T04:01:59.791382</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744824</t>
+          <t>2026-03-21T04:01:59.791387</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744827</t>
+          <t>2026-03-21T04:01:59.791390</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744830</t>
+          <t>2026-03-21T04:01:59.791393</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744833</t>
+          <t>2026-03-21T04:01:59.791396</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744836</t>
+          <t>2026-03-21T04:01:59.791399</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744839</t>
+          <t>2026-03-21T04:01:59.791402</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744841</t>
+          <t>2026-03-21T04:01:59.791405</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744844</t>
+          <t>2026-03-21T04:01:59.791407</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744847</t>
+          <t>2026-03-21T04:01:59.791410</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:43.744850</t>
+          <t>2026-03-21T04:01:59.791413</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1443</v>
+        <v>1478</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580718</t>
+          <t>2026-03-21T04:02:00.565837</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1478</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580732</t>
+          <t>2026-03-21T04:02:00.565851</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580736</t>
+          <t>2026-03-21T04:02:00.565854</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580740</t>
+          <t>2026-03-21T04:02:00.565858</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580743</t>
+          <t>2026-03-21T04:02:00.565860</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580746</t>
+          <t>2026-03-21T04:02:00.565863</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1492</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580749</t>
+          <t>2026-03-21T04:02:00.565867</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580752</t>
+          <t>2026-03-21T04:02:00.565870</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580755</t>
+          <t>2026-03-21T04:02:00.565873</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>1492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580758</t>
+          <t>2026-03-21T04:02:00.565876</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580761</t>
+          <t>2026-03-21T04:02:00.565879</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580764</t>
+          <t>2026-03-21T04:02:00.565882</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580767</t>
+          <t>2026-03-21T04:02:00.565885</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580770</t>
+          <t>2026-03-21T04:02:00.565888</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1530</v>
+        <v>1547</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580773</t>
+          <t>2026-03-21T04:02:00.565891</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580775</t>
+          <t>2026-03-21T04:02:00.565894</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580778</t>
+          <t>2026-03-21T04:02:00.565899</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580781</t>
+          <t>2026-03-21T04:02:00.565902</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580784</t>
+          <t>2026-03-21T04:02:00.565905</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580787</t>
+          <t>2026-03-21T04:02:00.565908</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580789</t>
+          <t>2026-03-21T04:02:00.565911</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580792</t>
+          <t>2026-03-21T04:02:00.565913</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580795</t>
+          <t>2026-03-21T04:02:00.565916</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1549</v>
+        <v>1530</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580798</t>
+          <t>2026-03-21T04:02:00.565919</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580800</t>
+          <t>2026-03-21T04:02:00.565922</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580803</t>
+          <t>2026-03-21T04:02:00.565924</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580806</t>
+          <t>2026-03-21T04:02:00.565929</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580809</t>
+          <t>2026-03-21T04:02:00.565932</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580812</t>
+          <t>2026-03-21T04:02:00.565935</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1557</v>
+        <v>1530</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580814</t>
+          <t>2026-03-21T04:02:00.565938</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580817</t>
+          <t>2026-03-21T04:02:00.565941</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580820</t>
+          <t>2026-03-21T04:02:00.565944</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580823</t>
+          <t>2026-03-21T04:02:00.565946</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580826</t>
+          <t>2026-03-21T04:02:00.565949</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580828</t>
+          <t>2026-03-21T04:02:00.565952</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1530</v>
+        <v>1547</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580831</t>
+          <t>2026-03-21T04:02:00.565955</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580834</t>
+          <t>2026-03-21T04:02:00.565960</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1578</v>
+        <v>1538</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580836</t>
+          <t>2026-03-21T04:02:00.565963</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580839</t>
+          <t>2026-03-21T04:02:00.565965</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580842</t>
+          <t>2026-03-21T04:02:00.565968</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1538</v>
+        <v>1578</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580845</t>
+          <t>2026-03-21T04:02:00.565971</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580847</t>
+          <t>2026-03-21T04:02:00.565974</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580850</t>
+          <t>2026-03-21T04:02:00.565977</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6630,11 +6630,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1548</v>
+        <v>1579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580853</t>
+          <t>2026-03-21T04:02:00.565979</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6695,11 +6695,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580856</t>
+          <t>2026-03-21T04:02:00.565982</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580859</t>
+          <t>2026-03-21T04:02:00.565985</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6825,11 +6825,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1586</v>
+        <v>1548</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580861</t>
+          <t>2026-03-21T04:02:00.565988</t>
         </is>
       </c>
     </row>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580864</t>
+          <t>2026-03-21T04:02:00.565991</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6955,11 +6955,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1600</v>
+        <v>1548</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580867</t>
+          <t>2026-03-21T04:02:00.565994</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7020,11 +7020,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580870</t>
+          <t>2026-03-21T04:02:00.565997</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395178</t>
+          <t>2026-03-21T04:02:02.219418</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395191</t>
+          <t>2026-03-21T04:02:02.219439</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395195</t>
+          <t>2026-03-21T04:02:02.219445</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395198</t>
+          <t>2026-03-21T04:02:02.219452</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395201</t>
+          <t>2026-03-21T04:02:02.219473</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395204</t>
+          <t>2026-03-21T04:02:02.219477</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395207</t>
+          <t>2026-03-21T04:02:02.219480</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395210</t>
+          <t>2026-03-21T04:02:02.219483</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395213</t>
+          <t>2026-03-21T04:02:02.219486</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395216</t>
+          <t>2026-03-21T04:02:02.219489</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395219</t>
+          <t>2026-03-21T04:02:02.219492</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395222</t>
+          <t>2026-03-21T04:02:02.219495</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395224</t>
+          <t>2026-03-21T04:02:02.219498</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395227</t>
+          <t>2026-03-21T04:02:02.219501</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395230</t>
+          <t>2026-03-21T04:02:02.219504</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395233</t>
+          <t>2026-03-21T04:02:02.219507</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395236</t>
+          <t>2026-03-21T04:02:02.219510</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395239</t>
+          <t>2026-03-21T04:02:02.219513</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395242</t>
+          <t>2026-03-21T04:02:02.219516</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395245</t>
+          <t>2026-03-21T04:02:02.219519</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395248</t>
+          <t>2026-03-21T04:02:02.219522</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395251</t>
+          <t>2026-03-21T04:02:02.219525</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395254</t>
+          <t>2026-03-21T04:02:02.219528</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395257</t>
+          <t>2026-03-21T04:02:02.219531</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395259</t>
+          <t>2026-03-21T04:02:02.219534</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395263</t>
+          <t>2026-03-21T04:02:02.219537</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395265</t>
+          <t>2026-03-21T04:02:02.219540</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395268</t>
+          <t>2026-03-21T04:02:02.219543</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395271</t>
+          <t>2026-03-21T04:02:02.219546</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395274</t>
+          <t>2026-03-21T04:02:02.219549</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395276</t>
+          <t>2026-03-21T04:02:02.219552</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395279</t>
+          <t>2026-03-21T04:02:02.219554</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395282</t>
+          <t>2026-03-21T04:02:02.219557</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395284</t>
+          <t>2026-03-21T04:02:02.219560</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395287</t>
+          <t>2026-03-21T04:02:02.219563</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395290</t>
+          <t>2026-03-21T04:02:02.219566</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395293</t>
+          <t>2026-03-21T04:02:02.219569</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395296</t>
+          <t>2026-03-21T04:02:02.219574</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395299</t>
+          <t>2026-03-21T04:02:02.219578</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395302</t>
+          <t>2026-03-21T04:02:02.219581</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395304</t>
+          <t>2026-03-21T04:02:02.219585</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395307</t>
+          <t>2026-03-21T04:02:02.219588</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395310</t>
+          <t>2026-03-21T04:02:02.219590</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395313</t>
+          <t>2026-03-21T04:02:02.219593</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395315</t>
+          <t>2026-03-21T04:02:02.219596</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395318</t>
+          <t>2026-03-21T04:02:02.219599</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395321</t>
+          <t>2026-03-21T04:02:02.219602</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395324</t>
+          <t>2026-03-21T04:02:02.219605</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395335</t>
+          <t>2026-03-21T04:02:02.219608</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:46.395338</t>
+          <t>2026-03-21T04:02:02.219611</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1538.8</v>
+        <v>1537.68</v>
       </c>
     </row>
     <row r="4">

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791242</t>
+          <t>2026-03-22T04:16:38.321038</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791257</t>
+          <t>2026-03-22T04:16:38.321052</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791262</t>
+          <t>2026-03-22T04:16:38.321056</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791265</t>
+          <t>2026-03-22T04:16:38.321060</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791268</t>
+          <t>2026-03-22T04:16:38.321063</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791272</t>
+          <t>2026-03-22T04:16:38.321066</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791275</t>
+          <t>2026-03-22T04:16:38.321069</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791278</t>
+          <t>2026-03-22T04:16:38.321073</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791281</t>
+          <t>2026-03-22T04:16:38.321076</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791284</t>
+          <t>2026-03-22T04:16:38.321079</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791290</t>
+          <t>2026-03-22T04:16:38.321085</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791293</t>
+          <t>2026-03-22T04:16:38.321088</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791296</t>
+          <t>2026-03-22T04:16:38.321091</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791299</t>
+          <t>2026-03-22T04:16:38.321094</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791302</t>
+          <t>2026-03-22T04:16:38.321097</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791305</t>
+          <t>2026-03-22T04:16:38.321099</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791308</t>
+          <t>2026-03-22T04:16:38.321102</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791313</t>
+          <t>2026-03-22T04:16:38.321105</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791316</t>
+          <t>2026-03-22T04:16:38.321108</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791319</t>
+          <t>2026-03-22T04:16:38.321111</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791324</t>
+          <t>2026-03-22T04:16:38.321116</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791327</t>
+          <t>2026-03-22T04:16:38.321119</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791329</t>
+          <t>2026-03-22T04:16:38.321122</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791332</t>
+          <t>2026-03-22T04:16:38.321124</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791335</t>
+          <t>2026-03-22T04:16:38.321127</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791338</t>
+          <t>2026-03-22T04:16:38.321130</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791343</t>
+          <t>2026-03-22T04:16:38.321133</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791346</t>
+          <t>2026-03-22T04:16:38.321136</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791349</t>
+          <t>2026-03-22T04:16:38.321139</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791352</t>
+          <t>2026-03-22T04:16:38.321142</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791355</t>
+          <t>2026-03-22T04:16:38.321144</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791358</t>
+          <t>2026-03-22T04:16:38.321147</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791361</t>
+          <t>2026-03-22T04:16:38.321150</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791364</t>
+          <t>2026-03-22T04:16:38.321153</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791368</t>
+          <t>2026-03-22T04:16:38.321156</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791371</t>
+          <t>2026-03-22T04:16:38.321158</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791374</t>
+          <t>2026-03-22T04:16:38.321161</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791377</t>
+          <t>2026-03-22T04:16:38.321164</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791380</t>
+          <t>2026-03-22T04:16:38.321167</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791382</t>
+          <t>2026-03-22T04:16:38.321170</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791387</t>
+          <t>2026-03-22T04:16:38.321175</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791390</t>
+          <t>2026-03-22T04:16:38.321178</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791393</t>
+          <t>2026-03-22T04:16:38.321180</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791396</t>
+          <t>2026-03-22T04:16:38.321183</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791399</t>
+          <t>2026-03-22T04:16:38.321186</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791402</t>
+          <t>2026-03-22T04:16:38.321191</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791405</t>
+          <t>2026-03-22T04:16:38.321194</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791407</t>
+          <t>2026-03-22T04:16:38.321197</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791410</t>
+          <t>2026-03-22T04:16:38.321199</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:01:59.791413</t>
+          <t>2026-03-22T04:16:38.321202</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1478</v>
+        <v>1448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3878,14 +3878,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565837</t>
+          <t>2026-03-22T04:16:39.040919</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565851</t>
+          <t>2026-03-22T04:16:39.040931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4008,14 +4008,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565854</t>
+          <t>2026-03-22T04:16:39.040934</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4073,14 +4073,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565858</t>
+          <t>2026-03-22T04:16:39.040938</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565860</t>
+          <t>2026-03-22T04:16:39.040940</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565863</t>
+          <t>2026-03-22T04:16:39.040943</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4268,14 +4268,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565867</t>
+          <t>2026-03-22T04:16:39.040946</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565870</t>
+          <t>2026-03-22T04:16:39.040949</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4398,14 +4398,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565873</t>
+          <t>2026-03-22T04:16:39.040952</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4463,14 +4463,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565876</t>
+          <t>2026-03-22T04:16:39.040955</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565879</t>
+          <t>2026-03-22T04:16:39.040958</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4593,14 +4593,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565882</t>
+          <t>2026-03-22T04:16:39.040961</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565885</t>
+          <t>2026-03-22T04:16:39.040963</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4723,14 +4723,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565888</t>
+          <t>2026-03-22T04:16:39.040966</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565891</t>
+          <t>2026-03-22T04:16:39.040969</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565894</t>
+          <t>2026-03-22T04:16:39.040972</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -4918,14 +4918,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565899</t>
+          <t>2026-03-22T04:16:39.040975</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4983,14 +4983,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565902</t>
+          <t>2026-03-22T04:16:39.040978</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565905</t>
+          <t>2026-03-22T04:16:39.040981</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565908</t>
+          <t>2026-03-22T04:16:39.040983</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5178,14 +5178,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565911</t>
+          <t>2026-03-22T04:16:39.040986</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -5243,14 +5243,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565913</t>
+          <t>2026-03-22T04:16:39.040989</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5308,14 +5308,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565916</t>
+          <t>2026-03-22T04:16:39.040992</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565919</t>
+          <t>2026-03-22T04:16:39.040995</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5395,11 +5395,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5438,14 +5438,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565922</t>
+          <t>2026-03-22T04:16:39.040997</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -5503,14 +5503,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565924</t>
+          <t>2026-03-22T04:16:39.041000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565929</t>
+          <t>2026-03-22T04:16:39.041003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565932</t>
+          <t>2026-03-22T04:16:39.041006</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5698,14 +5698,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565935</t>
+          <t>2026-03-22T04:16:39.041008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565938</t>
+          <t>2026-03-22T04:16:39.041011</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5828,14 +5828,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565941</t>
+          <t>2026-03-22T04:16:39.041014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565944</t>
+          <t>2026-03-22T04:16:39.041017</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565946</t>
+          <t>2026-03-22T04:16:39.041019</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565949</t>
+          <t>2026-03-22T04:16:39.041022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6088,14 +6088,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565952</t>
+          <t>2026-03-22T04:16:39.041025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6153,14 +6153,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565955</t>
+          <t>2026-03-22T04:16:39.041028</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565960</t>
+          <t>2026-03-22T04:16:39.041031</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6283,14 +6283,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565963</t>
+          <t>2026-03-22T04:16:39.041033</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6305,11 +6305,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6348,14 +6348,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565965</t>
+          <t>2026-03-22T04:16:39.041036</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6413,14 +6413,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565968</t>
+          <t>2026-03-22T04:16:39.041039</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565971</t>
+          <t>2026-03-22T04:16:39.041042</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6543,14 +6543,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565974</t>
+          <t>2026-03-22T04:16:39.041045</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6565,11 +6565,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6608,14 +6608,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565977</t>
+          <t>2026-03-22T04:16:39.041050</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6630,11 +6630,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565979</t>
+          <t>2026-03-22T04:16:39.041053</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6695,11 +6695,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565982</t>
+          <t>2026-03-22T04:16:39.041056</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6803,14 +6803,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565985</t>
+          <t>2026-03-22T04:16:39.041059</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6825,11 +6825,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6868,14 +6868,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565988</t>
+          <t>2026-03-22T04:16:39.041062</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6890,11 +6890,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6933,14 +6933,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565991</t>
+          <t>2026-03-22T04:16:39.041064</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565994</t>
+          <t>2026-03-22T04:16:39.041067</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7020,11 +7020,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565997</t>
+          <t>2026-03-22T04:16:39.041070</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219418</t>
+          <t>2026-03-22T04:16:39.784371</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219439</t>
+          <t>2026-03-22T04:16:39.784384</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219445</t>
+          <t>2026-03-22T04:16:39.784387</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219452</t>
+          <t>2026-03-22T04:16:39.784391</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219473</t>
+          <t>2026-03-22T04:16:39.784394</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219477</t>
+          <t>2026-03-22T04:16:39.784397</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219480</t>
+          <t>2026-03-22T04:16:39.784400</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219483</t>
+          <t>2026-03-22T04:16:39.784403</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219486</t>
+          <t>2026-03-22T04:16:39.784406</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219489</t>
+          <t>2026-03-22T04:16:39.784409</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219492</t>
+          <t>2026-03-22T04:16:39.784412</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219495</t>
+          <t>2026-03-22T04:16:39.784415</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219498</t>
+          <t>2026-03-22T04:16:39.784417</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219501</t>
+          <t>2026-03-22T04:16:39.784420</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219504</t>
+          <t>2026-03-22T04:16:39.784423</t>
         </is>
       </c>
     </row>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219507</t>
+          <t>2026-03-22T04:16:39.784426</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219510</t>
+          <t>2026-03-22T04:16:39.784429</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219513</t>
+          <t>2026-03-22T04:16:39.784432</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219516</t>
+          <t>2026-03-22T04:16:39.784435</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219519</t>
+          <t>2026-03-22T04:16:39.784438</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219522</t>
+          <t>2026-03-22T04:16:39.784441</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219525</t>
+          <t>2026-03-22T04:16:39.784444</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219528</t>
+          <t>2026-03-22T04:16:39.784447</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219531</t>
+          <t>2026-03-22T04:16:39.784449</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219534</t>
+          <t>2026-03-22T04:16:39.784452</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219537</t>
+          <t>2026-03-22T04:16:39.784455</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219540</t>
+          <t>2026-03-22T04:16:39.784458</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219543</t>
+          <t>2026-03-22T04:16:39.784461</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219546</t>
+          <t>2026-03-22T04:16:39.784464</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219549</t>
+          <t>2026-03-22T04:16:39.784467</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219552</t>
+          <t>2026-03-22T04:16:39.784469</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219554</t>
+          <t>2026-03-22T04:16:39.784472</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219557</t>
+          <t>2026-03-22T04:16:39.784475</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219560</t>
+          <t>2026-03-22T04:16:39.784478</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219563</t>
+          <t>2026-03-22T04:16:39.784486</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219566</t>
+          <t>2026-03-22T04:16:39.784489</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219569</t>
+          <t>2026-03-22T04:16:39.784492</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219574</t>
+          <t>2026-03-22T04:16:39.784495</t>
         </is>
       </c>
     </row>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219578</t>
+          <t>2026-03-22T04:16:39.784498</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219581</t>
+          <t>2026-03-22T04:16:39.784501</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219585</t>
+          <t>2026-03-22T04:16:39.784504</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219588</t>
+          <t>2026-03-22T04:16:39.784507</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219590</t>
+          <t>2026-03-22T04:16:39.784509</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219593</t>
+          <t>2026-03-22T04:16:39.784512</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219596</t>
+          <t>2026-03-22T04:16:39.784515</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219599</t>
+          <t>2026-03-22T04:16:39.784518</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219602</t>
+          <t>2026-03-22T04:16:39.784521</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219605</t>
+          <t>2026-03-22T04:16:39.784524</t>
         </is>
       </c>
     </row>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219608</t>
+          <t>2026-03-22T04:16:39.784527</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:02.219611</t>
+          <t>2026-03-22T04:16:39.784529</t>
         </is>
       </c>
     </row>
@@ -10481,14 +10481,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1537.68</v>
+        <v>1516.62</v>
       </c>
     </row>
     <row r="4">

--- a/combined_gold_data.xlsx
+++ b/combined_gold_data.xlsx
@@ -489,12 +489,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -504,11 +504,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,14 +547,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321038</t>
+          <t>2026-03-23T04:26:07.613509</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -569,11 +569,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -612,19 +612,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321052</t>
+          <t>2026-03-23T04:26:07.613524</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -634,11 +634,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -677,14 +677,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321056</t>
+          <t>2026-03-23T04:26:07.613528</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -699,11 +699,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -742,19 +742,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321060</t>
+          <t>2026-03-23T04:26:07.613532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -764,11 +764,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -807,19 +807,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321063</t>
+          <t>2026-03-23T04:26:07.613535</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -829,11 +829,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -872,19 +872,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321066</t>
+          <t>2026-03-23T04:26:07.613538</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -894,11 +894,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -937,14 +937,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321069</t>
+          <t>2026-03-23T04:26:07.613541</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,11 +959,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1002,19 +1002,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321073</t>
+          <t>2026-03-23T04:26:07.613545</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,11 +1024,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321076</t>
+          <t>2026-03-23T04:26:07.613551</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1132,19 +1132,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321079</t>
+          <t>2026-03-23T04:26:07.613555</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321085</t>
+          <t>2026-03-23T04:26:07.613560</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1262,14 +1262,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321088</t>
+          <t>2026-03-23T04:26:07.613563</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1327,19 +1327,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321091</t>
+          <t>2026-03-23T04:26:07.613566</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1349,11 +1349,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1392,19 +1392,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321094</t>
+          <t>2026-03-23T04:26:07.613569</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321097</t>
+          <t>2026-03-23T04:26:07.613572</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1479,11 +1479,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1522,19 +1522,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321099</t>
+          <t>2026-03-23T04:26:07.613575</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1544,11 +1544,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1587,14 +1587,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321102</t>
+          <t>2026-03-23T04:26:07.613578</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1609,11 +1609,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1652,19 +1652,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321105</t>
+          <t>2026-03-23T04:26:07.613581</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1674,11 +1674,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321108</t>
+          <t>2026-03-23T04:26:07.613584</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1739,11 +1739,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1782,19 +1782,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321111</t>
+          <t>2026-03-23T04:26:07.613586</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1804,11 +1804,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1847,14 +1847,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321116</t>
+          <t>2026-03-23T04:26:07.613591</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1869,11 +1869,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1912,14 +1912,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321119</t>
+          <t>2026-03-23T04:26:07.613594</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1934,11 +1934,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1977,14 +1977,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321122</t>
+          <t>2026-03-23T04:26:07.613597</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1999,11 +1999,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321124</t>
+          <t>2026-03-23T04:26:07.613600</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321127</t>
+          <t>2026-03-23T04:26:07.613603</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2129,11 +2129,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2172,14 +2172,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321130</t>
+          <t>2026-03-23T04:26:07.613606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2194,11 +2194,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1388</v>
+        <v>1404</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2237,19 +2237,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321133</t>
+          <t>2026-03-23T04:26:07.613609</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2259,11 +2259,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1371.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2302,19 +2302,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321136</t>
+          <t>2026-03-23T04:26:07.613611</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2324,11 +2324,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1376.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1376</v>
+        <v>1388</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2367,19 +2367,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321139</t>
+          <t>2026-03-23T04:26:07.613614</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2389,11 +2389,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2432,19 +2432,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321142</t>
+          <t>2026-03-23T04:26:07.613617</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1371.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1383</v>
+        <v>1371</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2497,19 +2497,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321144</t>
+          <t>2026-03-23T04:26:07.613620</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2519,11 +2519,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1376.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1385</v>
+        <v>1376</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2562,19 +2562,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321147</t>
+          <t>2026-03-23T04:26:07.613623</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2584,11 +2584,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1382.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2627,19 +2627,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321150</t>
+          <t>2026-03-23T04:26:07.613626</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1403.00</t>
+          <t>1382.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1403</v>
+        <v>1382</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2692,19 +2692,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321153</t>
+          <t>2026-03-23T04:26:07.613628</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2714,11 +2714,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1401</v>
+        <v>1383</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2757,19 +2757,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321156</t>
+          <t>2026-03-23T04:26:07.613631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1401</v>
+        <v>1385</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2822,14 +2822,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321158</t>
+          <t>2026-03-23T04:26:07.613634</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2887,14 +2887,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321161</t>
+          <t>2026-03-23T04:26:07.613637</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321164</t>
+          <t>2026-03-23T04:26:07.613640</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321167</t>
+          <t>2026-03-23T04:26:07.613643</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3039,11 +3039,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1452.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1452</v>
+        <v>1401</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3082,14 +3082,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321170</t>
+          <t>2026-03-23T04:26:07.613645</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3104,11 +3104,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3147,19 +3147,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321175</t>
+          <t>2026-03-23T04:26:07.613650</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3169,11 +3169,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1403.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1450</v>
+        <v>1403</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321178</t>
+          <t>2026-03-23T04:26:07.613653</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1433</v>
+        <v>1450</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3277,19 +3277,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321180</t>
+          <t>2026-03-23T04:26:07.613656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3299,11 +3299,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1429.00</t>
+          <t>1452.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1429</v>
+        <v>1452</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3342,14 +3342,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321183</t>
+          <t>2026-03-23T04:26:07.613659</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3364,11 +3364,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1428</v>
+        <v>1450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3407,19 +3407,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321186</t>
+          <t>2026-03-23T04:26:07.613662</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3429,11 +3429,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1429.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1380</v>
+        <v>1429</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3472,19 +3472,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321191</t>
+          <t>2026-03-23T04:26:07.613665</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3494,11 +3494,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1386</v>
+        <v>1428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3537,19 +3537,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321194</t>
+          <t>2026-03-23T04:26:07.613668</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3559,11 +3559,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1384</v>
+        <v>1433</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3602,19 +3602,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321197</t>
+          <t>2026-03-23T04:26:07.613670</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3624,11 +3624,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1384.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321199</t>
+          <t>2026-03-23T04:26:07.613673</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3689,11 +3689,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1384.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:38.321202</t>
+          <t>2026-03-23T04:26:07.613676</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3835,11 +3835,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1448</v>
+        <v>1367</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3878,19 +3878,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040919</t>
+          <t>2026-03-23T04:26:08.383922</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3900,11 +3900,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1397</v>
+        <v>1418</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040931</t>
+          <t>2026-03-23T04:26:08.383935</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4008,19 +4008,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040934</t>
+          <t>2026-03-23T04:26:08.383939</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4030,11 +4030,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4073,19 +4073,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040938</t>
+          <t>2026-03-23T04:26:08.383942</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4138,19 +4138,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040940</t>
+          <t>2026-03-23T04:26:08.383946</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4160,11 +4160,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1395</v>
+        <v>1374</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -4203,19 +4203,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040943</t>
+          <t>2026-03-23T04:26:08.383949</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4225,11 +4225,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1447</v>
+        <v>1389</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4268,19 +4268,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040946</t>
+          <t>2026-03-23T04:26:08.383952</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4333,19 +4333,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040949</t>
+          <t>2026-03-23T04:26:08.383956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4355,11 +4355,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1478</v>
+        <v>1395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4398,19 +4398,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040952</t>
+          <t>2026-03-23T04:26:08.383959</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1443</v>
+        <v>1397</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -4463,19 +4463,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040955</t>
+          <t>2026-03-23T04:26:08.383962</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4485,11 +4485,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -4528,14 +4528,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040958</t>
+          <t>2026-03-23T04:26:08.383965</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4550,11 +4550,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -4593,19 +4593,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040961</t>
+          <t>2026-03-23T04:26:08.383967</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4615,11 +4615,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -4658,19 +4658,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040963</t>
+          <t>2026-03-23T04:26:08.383970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>1445</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4723,19 +4723,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040966</t>
+          <t>2026-03-23T04:26:08.383973</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4745,11 +4745,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4788,19 +4788,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040969</t>
+          <t>2026-03-23T04:26:08.383980</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4810,11 +4810,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1501</v>
+        <v>1443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4853,19 +4853,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040972</t>
+          <t>2026-03-23T04:26:08.383983</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1495</v>
+        <v>1445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4918,19 +4918,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040975</t>
+          <t>2026-03-23T04:26:08.383986</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4940,11 +4940,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1501</v>
+        <v>1447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040978</t>
+          <t>2026-03-23T04:26:08.383989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5005,11 +5005,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1550</v>
+        <v>1495</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5048,19 +5048,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040981</t>
+          <t>2026-03-23T04:26:08.383992</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5070,11 +5070,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1547</v>
+        <v>1501</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5113,14 +5113,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040983</t>
+          <t>2026-03-23T04:26:08.383995</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5135,11 +5135,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -5178,19 +5178,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040986</t>
+          <t>2026-03-23T04:26:08.383998</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5200,11 +5200,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1549</v>
+        <v>1498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -5243,19 +5243,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040989</t>
+          <t>2026-03-23T04:26:08.384000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5265,11 +5265,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1549</v>
+        <v>1492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -5308,19 +5308,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040992</t>
+          <t>2026-03-23T04:26:08.384003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5330,11 +5330,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1530</v>
+        <v>1501</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -5373,19 +5373,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040995</t>
+          <t>2026-03-23T04:26:08.384006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -5438,19 +5438,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040997</t>
+          <t>2026-03-23T04:26:08.384009</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5503,19 +5503,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041000</t>
+          <t>2026-03-23T04:26:08.384026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5525,11 +5525,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5568,14 +5568,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041003</t>
+          <t>2026-03-23T04:26:08.384029</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5633,19 +5633,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041006</t>
+          <t>2026-03-23T04:26:08.384032</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5655,11 +5655,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -5698,19 +5698,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041008</t>
+          <t>2026-03-23T04:26:08.384035</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5720,11 +5720,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1530</v>
+        <v>1551</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5763,14 +5763,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041011</t>
+          <t>2026-03-23T04:26:08.384038</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5785,11 +5785,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -5828,19 +5828,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041014</t>
+          <t>2026-03-23T04:26:08.384041</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5850,11 +5850,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5893,19 +5893,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041017</t>
+          <t>2026-03-23T04:26:08.384044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5915,11 +5915,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -5958,19 +5958,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041019</t>
+          <t>2026-03-23T04:26:08.384046</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5980,11 +5980,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1557</v>
+        <v>1550</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -6023,19 +6023,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041022</t>
+          <t>2026-03-23T04:26:08.384049</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6045,11 +6045,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1560</v>
+        <v>1549</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6088,19 +6088,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041025</t>
+          <t>2026-03-23T04:26:08.384052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6110,11 +6110,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -6153,19 +6153,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041028</t>
+          <t>2026-03-23T04:26:08.384055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6218,19 +6218,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041031</t>
+          <t>2026-03-23T04:26:08.384058</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1530</v>
+        <v>1555</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -6283,19 +6283,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041033</t>
+          <t>2026-03-23T04:26:08.384061</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -6348,19 +6348,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041036</t>
+          <t>2026-03-23T04:26:08.384064</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6370,11 +6370,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6413,19 +6413,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041039</t>
+          <t>2026-03-23T04:26:08.384066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6435,11 +6435,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1530</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6478,14 +6478,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041042</t>
+          <t>2026-03-23T04:26:08.384069</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6500,11 +6500,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041045</t>
+          <t>2026-03-23T04:26:08.384072</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6565,11 +6565,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6608,19 +6608,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041050</t>
+          <t>2026-03-23T04:26:08.384075</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6630,11 +6630,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1572</v>
+        <v>1530</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6673,19 +6673,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041053</t>
+          <t>2026-03-23T04:26:08.384077</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6695,11 +6695,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1578</v>
+        <v>1547</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6738,19 +6738,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041056</t>
+          <t>2026-03-23T04:26:08.384080</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6760,11 +6760,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1580</v>
+        <v>1555</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6803,19 +6803,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041059</t>
+          <t>2026-03-23T04:26:08.384083</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6825,11 +6825,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1538</v>
+        <v>1557</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6868,14 +6868,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041062</t>
+          <t>2026-03-23T04:26:08.384086</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6890,11 +6890,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6933,19 +6933,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041064</t>
+          <t>2026-03-23T04:26:08.384089</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6955,11 +6955,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1548</v>
+        <v>1572</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6998,19 +6998,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041067</t>
+          <t>2026-03-23T04:26:08.384092</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7020,11 +7020,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041070</t>
+          <t>2026-03-23T04:26:08.384094</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -7166,11 +7166,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1268.00</t>
+          <t>1206.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1268</v>
+        <v>1206</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -7209,14 +7209,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784371</t>
+          <t>2026-03-23T04:26:09.020068</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1267.00</t>
+          <t>1204.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1267</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -7274,19 +7274,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784384</t>
+          <t>2026-03-23T04:26:09.020088</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1269.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1269</v>
+        <v>1200</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784387</t>
+          <t>2026-03-23T04:26:09.020095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7361,11 +7361,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1310.00</t>
+          <t>1268.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1310</v>
+        <v>1268</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7404,19 +7404,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784391</t>
+          <t>2026-03-23T04:26:09.020100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7426,11 +7426,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1316.00</t>
+          <t>1269.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1316</v>
+        <v>1269</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7469,19 +7469,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784394</t>
+          <t>2026-03-23T04:26:09.020106</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7491,11 +7491,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1318.00</t>
+          <t>1267.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1318</v>
+        <v>1267</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7534,19 +7534,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784397</t>
+          <t>2026-03-23T04:26:09.020113</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1310.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1361</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -7599,14 +7599,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784400</t>
+          <t>2026-03-23T04:26:09.020120</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1316.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1359</v>
+        <v>1316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7664,19 +7664,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784403</t>
+          <t>2026-03-23T04:26:09.020123</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7686,11 +7686,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1358.00</t>
+          <t>1318.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1358</v>
+        <v>1318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -7729,19 +7729,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784406</t>
+          <t>2026-03-23T04:26:09.020125</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7751,11 +7751,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1359.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7794,19 +7794,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784409</t>
+          <t>2026-03-23T04:26:09.020128</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7816,11 +7816,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1358.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -7859,19 +7859,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784412</t>
+          <t>2026-03-23T04:26:09.020131</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1361.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -7924,14 +7924,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784415</t>
+          <t>2026-03-23T04:26:09.020134</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1360.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -7989,19 +7989,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784417</t>
+          <t>2026-03-23T04:26:09.020137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8011,11 +8011,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1359.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -8054,19 +8054,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784420</t>
+          <t>2026-03-23T04:26:09.020140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1363.00</t>
+          <t>1361.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -8119,19 +8119,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784423</t>
+          <t>2026-03-23T04:26:09.020143</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -8141,11 +8141,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1380.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1380</v>
+        <v>1365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8184,19 +8184,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784426</t>
+          <t>2026-03-23T04:26:09.020146</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1385.00</t>
+          <t>1360.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1385</v>
+        <v>1360</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784429</t>
+          <t>2026-03-23T04:26:09.020148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8271,11 +8271,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1383.00</t>
+          <t>1363.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1383</v>
+        <v>1363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -8314,19 +8314,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784432</t>
+          <t>2026-03-23T04:26:09.020151</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8336,11 +8336,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1380.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1390</v>
+        <v>1380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -8379,19 +8379,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784435</t>
+          <t>2026-03-23T04:26:09.020154</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8401,11 +8401,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1386.00</t>
+          <t>1383.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -8444,19 +8444,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784438</t>
+          <t>2026-03-23T04:26:09.020157</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1385.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784441</t>
+          <t>2026-03-23T04:26:09.020160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1388.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1399</v>
+        <v>1388</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8574,14 +8574,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784444</t>
+          <t>2026-03-23T04:26:09.020164</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1401.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1401</v>
+        <v>1390</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8639,14 +8639,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784447</t>
+          <t>2026-03-23T04:26:09.020167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8661,11 +8661,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1386.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1404</v>
+        <v>1386</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8704,14 +8704,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784449</t>
+          <t>2026-03-23T04:26:09.020169</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8726,11 +8726,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1388.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -8769,14 +8769,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784452</t>
+          <t>2026-03-23T04:26:09.020172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8791,11 +8791,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1401.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -8834,14 +8834,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.784455</t>
+          <t>2026-03-23T04:26:09.020175</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8856,11 +8856,11 @@
    